--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY249"/>
+  <dimension ref="A1:AY250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130237722</v>
+        <v>130237694</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445044</v>
+        <v>445036</v>
       </c>
       <c r="R2" t="n">
-        <v>6811281</v>
+        <v>6811601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130237694</v>
+        <v>130237722</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445036</v>
+        <v>445044</v>
       </c>
       <c r="R3" t="n">
-        <v>6811601</v>
+        <v>6811281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130237712</v>
+        <v>130237706</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445057</v>
+        <v>445093</v>
       </c>
       <c r="R4" t="n">
-        <v>6811437</v>
+        <v>6811481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237706</v>
+        <v>130237691</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445093</v>
+        <v>444991</v>
       </c>
       <c r="R5" t="n">
-        <v>6811481</v>
+        <v>6811568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237691</v>
+        <v>130237743</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>78937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,42 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444991</v>
+        <v>445095</v>
       </c>
       <c r="R6" t="n">
-        <v>6811568</v>
+        <v>6811230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130237743</v>
+        <v>130237745</v>
       </c>
       <c r="B7" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445095</v>
+        <v>444954</v>
       </c>
       <c r="R7" t="n">
-        <v>6811230</v>
+        <v>6811588</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130237745</v>
+        <v>130237712</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1300,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444954</v>
+        <v>445057</v>
       </c>
       <c r="R8" t="n">
-        <v>6811588</v>
+        <v>6811437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
         <v>130237777</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>130237749</v>
       </c>
       <c r="B10" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237663</v>
+        <v>130237692</v>
       </c>
       <c r="B11" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1599,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444954</v>
+        <v>445036</v>
       </c>
       <c r="R11" t="n">
-        <v>6811588</v>
+        <v>6811602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237692</v>
+        <v>130237738</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>78938</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,42 +1704,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445036</v>
+        <v>445081</v>
       </c>
       <c r="R12" t="n">
-        <v>6811602</v>
+        <v>6811319</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237724</v>
+        <v>130237663</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1801,42 +1801,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445064</v>
+        <v>444954</v>
       </c>
       <c r="R13" t="n">
-        <v>6811249</v>
+        <v>6811588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1890,7 @@
         <v>130237705</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237738</v>
+        <v>130237724</v>
       </c>
       <c r="B15" t="n">
-        <v>78853</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,34 +2003,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445081</v>
+        <v>445064</v>
       </c>
       <c r="R15" t="n">
-        <v>6811319</v>
+        <v>6811249</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,7 +2100,7 @@
         <v>130237733</v>
       </c>
       <c r="B16" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>130237763</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130237668</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130237736</v>
+        <v>130237778</v>
       </c>
       <c r="B19" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445078</v>
+        <v>445058</v>
       </c>
       <c r="R19" t="n">
-        <v>6811349</v>
+        <v>6811265</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130237693</v>
+        <v>130237714</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445027</v>
+        <v>445083</v>
       </c>
       <c r="R20" t="n">
-        <v>6811603</v>
+        <v>6811458</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237714</v>
+        <v>130237693</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445083</v>
+        <v>445027</v>
       </c>
       <c r="R21" t="n">
-        <v>6811458</v>
+        <v>6811603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130237778</v>
+        <v>130237667</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445058</v>
+        <v>445051</v>
       </c>
       <c r="R22" t="n">
-        <v>6811265</v>
+        <v>6811326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237761</v>
+        <v>130237736</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445019</v>
+        <v>445078</v>
       </c>
       <c r="R23" t="n">
-        <v>6811345</v>
+        <v>6811349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130237667</v>
+        <v>130237761</v>
       </c>
       <c r="B24" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445051</v>
+        <v>445019</v>
       </c>
       <c r="R24" t="n">
-        <v>6811326</v>
+        <v>6811345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237744</v>
+        <v>130237723</v>
       </c>
       <c r="B25" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,34 +2997,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445002</v>
+        <v>445063</v>
       </c>
       <c r="R25" t="n">
-        <v>6811503</v>
+        <v>6811256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3083,32 +3091,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237723</v>
+        <v>130237677</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>57016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,7 +3124,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3126,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445063</v>
+        <v>445025</v>
       </c>
       <c r="R26" t="n">
-        <v>6811256</v>
+        <v>6811296</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,53 +3196,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237677</v>
+        <v>130237744</v>
       </c>
       <c r="B27" t="n">
-        <v>56931</v>
+        <v>78937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445025</v>
+        <v>445002</v>
       </c>
       <c r="R27" t="n">
-        <v>6811296</v>
+        <v>6811503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,7 +3296,7 @@
         <v>130237757</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>130237715</v>
       </c>
       <c r="B29" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>130237739</v>
       </c>
       <c r="B30" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>130237748</v>
       </c>
       <c r="B31" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237765</v>
+        <v>130237737</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445089</v>
+        <v>445091</v>
       </c>
       <c r="R32" t="n">
-        <v>6811602</v>
+        <v>6811332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237737</v>
+        <v>130237765</v>
       </c>
       <c r="B33" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445091</v>
+        <v>445089</v>
       </c>
       <c r="R33" t="n">
-        <v>6811332</v>
+        <v>6811602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130237707</v>
+        <v>130237775</v>
       </c>
       <c r="B34" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3898,42 +3898,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445074</v>
+        <v>445075</v>
       </c>
       <c r="R34" t="n">
-        <v>6811505</v>
+        <v>6811342</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130237719</v>
+        <v>130237707</v>
       </c>
       <c r="B35" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,10 +4027,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445094</v>
+        <v>445074</v>
       </c>
       <c r="R35" t="n">
-        <v>6811360</v>
+        <v>6811505</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,10 +4089,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130237775</v>
+        <v>130237719</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,34 +4100,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445075</v>
+        <v>445094</v>
       </c>
       <c r="R36" t="n">
-        <v>6811342</v>
+        <v>6811360</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,53 +4194,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130237676</v>
+        <v>130237658</v>
       </c>
       <c r="B37" t="n">
-        <v>56931</v>
+        <v>79799</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445054</v>
+        <v>445098</v>
       </c>
       <c r="R37" t="n">
-        <v>6811606</v>
+        <v>6811287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4299,45 +4291,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130237658</v>
+        <v>130237676</v>
       </c>
       <c r="B38" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445098</v>
+        <v>445054</v>
       </c>
       <c r="R38" t="n">
-        <v>6811287</v>
+        <v>6811606</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,53 +4396,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130237675</v>
+        <v>130237670</v>
       </c>
       <c r="B39" t="n">
-        <v>56931</v>
+        <v>79799</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445000</v>
+        <v>445045</v>
       </c>
       <c r="R39" t="n">
-        <v>6811614</v>
+        <v>6811267</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4501,10 +4493,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130237670</v>
+        <v>130237764</v>
       </c>
       <c r="B40" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4504,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4528,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445045</v>
+        <v>445011</v>
       </c>
       <c r="R40" t="n">
-        <v>6811267</v>
+        <v>6811436</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,10 +4590,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130237764</v>
+        <v>130237669</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,21 +4601,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445011</v>
+        <v>445036</v>
       </c>
       <c r="R41" t="n">
-        <v>6811436</v>
+        <v>6811260</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4698,7 +4690,7 @@
         <v>130237779</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,45 +4784,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237669</v>
+        <v>130237675</v>
       </c>
       <c r="B43" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445036</v>
+        <v>445000</v>
       </c>
       <c r="R43" t="n">
-        <v>6811260</v>
+        <v>6811614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130237735</v>
+        <v>130237671</v>
       </c>
       <c r="B44" t="n">
-        <v>78853</v>
+        <v>79799</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444985</v>
+        <v>445066</v>
       </c>
       <c r="R44" t="n">
-        <v>6811589</v>
+        <v>6811213</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,49 +4986,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130237750</v>
+        <v>130237735</v>
       </c>
       <c r="B45" t="n">
-        <v>98833</v>
+        <v>78938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445085</v>
+        <v>444985</v>
       </c>
       <c r="R45" t="n">
-        <v>6811515</v>
+        <v>6811589</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5063,18 +5059,12 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ett hundratal plantor.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5093,45 +5083,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130237671</v>
+        <v>130237750</v>
       </c>
       <c r="B46" t="n">
-        <v>79714</v>
+        <v>98920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445066</v>
+        <v>445085</v>
       </c>
       <c r="R46" t="n">
-        <v>6811213</v>
+        <v>6811515</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5166,12 +5160,18 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett hundratal plantor.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237708</v>
+        <v>130237660</v>
       </c>
       <c r="B47" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,42 +5201,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445066</v>
+        <v>444997</v>
       </c>
       <c r="R47" t="n">
-        <v>6811502</v>
+        <v>6811440</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237780</v>
+        <v>130237734</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5306,34 +5298,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445066</v>
+        <v>444954</v>
       </c>
       <c r="R48" t="n">
-        <v>6811223</v>
+        <v>6811588</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5374,6 +5369,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5392,10 +5388,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237660</v>
+        <v>130237780</v>
       </c>
       <c r="B49" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5403,21 +5399,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5427,10 +5423,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R49" t="n">
-        <v>6811440</v>
+        <v>6811223</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5489,10 +5485,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130237734</v>
+        <v>130237708</v>
       </c>
       <c r="B50" t="n">
-        <v>78853</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5500,26 +5496,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5527,10 +5528,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444954</v>
+        <v>445066</v>
       </c>
       <c r="R50" t="n">
-        <v>6811588</v>
+        <v>6811502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5571,7 +5572,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>130237721</v>
       </c>
       <c r="B51" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>130237704</v>
       </c>
       <c r="B52" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>130237710</v>
       </c>
       <c r="B53" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>130237695</v>
       </c>
       <c r="B54" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>130237776</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130237661</v>
+        <v>130237762</v>
       </c>
       <c r="B56" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444987</v>
+        <v>445021</v>
       </c>
       <c r="R56" t="n">
-        <v>6811482</v>
+        <v>6811394</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130237762</v>
+        <v>130237661</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445021</v>
+        <v>444987</v>
       </c>
       <c r="R57" t="n">
-        <v>6811394</v>
+        <v>6811482</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,53 +6301,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237725</v>
+        <v>130237727</v>
       </c>
       <c r="B58" t="n">
-        <v>57738</v>
+        <v>97791</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445073</v>
+        <v>445095</v>
       </c>
       <c r="R58" t="n">
-        <v>6811522</v>
+        <v>6811427</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,32 +6398,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130237679</v>
+        <v>130237725</v>
       </c>
       <c r="B59" t="n">
-        <v>56931</v>
+        <v>57823</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,7 +6431,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6449,10 +6441,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445036</v>
+        <v>445073</v>
       </c>
       <c r="R59" t="n">
-        <v>6811277</v>
+        <v>6811522</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,32 +6503,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130237727</v>
+        <v>130237662</v>
       </c>
       <c r="B60" t="n">
-        <v>97704</v>
+        <v>79799</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6538,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445095</v>
+        <v>445002</v>
       </c>
       <c r="R60" t="n">
-        <v>6811427</v>
+        <v>6811503</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6611,7 +6603,7 @@
         <v>130237760</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6705,45 +6697,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130237662</v>
+        <v>130237679</v>
       </c>
       <c r="B62" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445002</v>
+        <v>445036</v>
       </c>
       <c r="R62" t="n">
-        <v>6811503</v>
+        <v>6811277</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237713</v>
+        <v>130237664</v>
       </c>
       <c r="B63" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,42 +6813,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445073</v>
+        <v>444968</v>
       </c>
       <c r="R63" t="n">
-        <v>6811446</v>
+        <v>6811605</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6910,7 +6902,7 @@
         <v>130237711</v>
       </c>
       <c r="B64" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7012,10 +7004,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237720</v>
+        <v>130237713</v>
       </c>
       <c r="B65" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7055,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445048</v>
+        <v>445073</v>
       </c>
       <c r="R65" t="n">
-        <v>6811299</v>
+        <v>6811446</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7117,10 +7109,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B66" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7150,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7160,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R66" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7222,10 +7214,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B67" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,34 +7225,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R67" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
         <v>130237774</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>130237698</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>130237699</v>
       </c>
       <c r="B70" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130237716</v>
+        <v>130237769</v>
       </c>
       <c r="B71" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7637,42 +7637,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445149</v>
+        <v>445114</v>
       </c>
       <c r="R71" t="n">
-        <v>6811433</v>
+        <v>6811610</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7734,7 +7726,7 @@
         <v>130237690</v>
       </c>
       <c r="B72" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7836,10 +7828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130237769</v>
+        <v>130237716</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7847,34 +7839,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445114</v>
+        <v>445149</v>
       </c>
       <c r="R73" t="n">
-        <v>6811610</v>
+        <v>6811433</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7936,7 +7936,7 @@
         <v>130237767</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>130237717</v>
       </c>
       <c r="B75" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8135,10 +8135,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130237697</v>
+        <v>130237766</v>
       </c>
       <c r="B76" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8146,31 +8146,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8178,10 +8173,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445124</v>
+        <v>445128</v>
       </c>
       <c r="R76" t="n">
-        <v>6811599</v>
+        <v>6811656</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,6 +8217,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8240,10 +8236,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130237766</v>
+        <v>130237697</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8251,26 +8247,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8278,10 +8279,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445128</v>
+        <v>445124</v>
       </c>
       <c r="R77" t="n">
-        <v>6811656</v>
+        <v>6811599</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8322,7 +8323,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>130237701</v>
       </c>
       <c r="B78" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>130237747</v>
       </c>
       <c r="B79" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>130237700</v>
       </c>
       <c r="B80" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>130237703</v>
       </c>
       <c r="B81" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>130237771</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>130237746</v>
       </c>
       <c r="B83" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>130237772</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>130237702</v>
       </c>
       <c r="B85" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>130237768</v>
       </c>
       <c r="B86" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>130237770</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>130237759</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>130237665</v>
       </c>
       <c r="B90" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>130237666</v>
       </c>
       <c r="B91" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>130237726</v>
       </c>
       <c r="B92" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>130237773</v>
       </c>
       <c r="B93" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>130237696</v>
       </c>
       <c r="B94" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10045,10 +10045,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130237718</v>
+        <v>130237758</v>
       </c>
       <c r="B95" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10056,42 +10056,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445116</v>
+        <v>445101</v>
       </c>
       <c r="R95" t="n">
-        <v>6811382</v>
+        <v>6811246</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10150,10 +10142,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237758</v>
+        <v>130237718</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10161,34 +10153,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445101</v>
+        <v>445116</v>
       </c>
       <c r="R96" t="n">
-        <v>6811246</v>
+        <v>6811382</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10250,7 +10250,7 @@
         <v>130237659</v>
       </c>
       <c r="B97" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>130250364</v>
       </c>
       <c r="B98" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>130250304</v>
       </c>
       <c r="B99" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>130250262</v>
       </c>
       <c r="B100" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>130250379</v>
       </c>
       <c r="B101" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>130250366</v>
       </c>
       <c r="B102" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>130250309</v>
       </c>
       <c r="B103" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>130250294</v>
       </c>
       <c r="B104" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11047,10 +11047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250343</v>
+        <v>130250267</v>
       </c>
       <c r="B105" t="n">
-        <v>78852</v>
+        <v>91728</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,34 +11058,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445471</v>
+        <v>445503</v>
       </c>
       <c r="R105" t="n">
-        <v>6811288</v>
+        <v>6811332</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11126,8 +11129,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11144,53 +11168,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130250270</v>
+        <v>130250343</v>
       </c>
       <c r="B106" t="n">
-        <v>56931</v>
+        <v>78937</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445426</v>
+        <v>445471</v>
       </c>
       <c r="R106" t="n">
-        <v>6811491</v>
+        <v>6811288</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11249,45 +11265,53 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130250373</v>
+        <v>130250270</v>
       </c>
       <c r="B107" t="n">
-        <v>79095</v>
+        <v>57016</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445554</v>
+        <v>445426</v>
       </c>
       <c r="R107" t="n">
-        <v>6811464</v>
+        <v>6811491</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11346,10 +11370,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130250267</v>
+        <v>130250373</v>
       </c>
       <c r="B108" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11357,37 +11381,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445503</v>
+        <v>445554</v>
       </c>
       <c r="R108" t="n">
-        <v>6811332</v>
+        <v>6811464</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11428,29 +11449,8 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -11470,7 +11470,7 @@
         <v>130250401</v>
       </c>
       <c r="B109" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>130250409</v>
       </c>
       <c r="B110" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>130250272</v>
       </c>
       <c r="B111" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>130250261</v>
       </c>
       <c r="B112" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>130250402</v>
       </c>
       <c r="B113" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>130250302</v>
       </c>
       <c r="B114" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>130250313</v>
       </c>
       <c r="B115" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>130250385</v>
       </c>
       <c r="B116" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>130250296</v>
       </c>
       <c r="B117" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>130250345</v>
       </c>
       <c r="B118" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>130250339</v>
       </c>
       <c r="B119" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>130250289</v>
       </c>
       <c r="B120" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>130250394</v>
       </c>
       <c r="B121" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>130250259</v>
       </c>
       <c r="B122" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>130250314</v>
       </c>
       <c r="B123" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>130250404</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>130250360</v>
       </c>
       <c r="B125" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>130250293</v>
       </c>
       <c r="B126" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>130250338</v>
       </c>
       <c r="B127" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>130250399</v>
       </c>
       <c r="B128" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>130250315</v>
       </c>
       <c r="B129" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>130250357</v>
       </c>
       <c r="B130" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>130250321</v>
       </c>
       <c r="B131" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>130250255</v>
       </c>
       <c r="B132" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>130250251</v>
       </c>
       <c r="B133" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>130250374</v>
       </c>
       <c r="B134" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>130250361</v>
       </c>
       <c r="B135" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>130250390</v>
       </c>
       <c r="B136" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>130250369</v>
       </c>
       <c r="B137" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>130250356</v>
       </c>
       <c r="B138" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>130250269</v>
       </c>
       <c r="B139" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>130250273</v>
       </c>
       <c r="B140" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>130250275</v>
       </c>
       <c r="B141" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>130250274</v>
       </c>
       <c r="B142" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>130250323</v>
       </c>
       <c r="B143" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>130250297</v>
       </c>
       <c r="B144" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>130250266</v>
       </c>
       <c r="B145" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>130250328</v>
       </c>
       <c r="B146" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>130250376</v>
       </c>
       <c r="B147" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>130250292</v>
       </c>
       <c r="B148" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>130250362</v>
       </c>
       <c r="B149" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>130250303</v>
       </c>
       <c r="B150" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>130250271</v>
       </c>
       <c r="B151" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>130250317</v>
       </c>
       <c r="B152" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>130250381</v>
       </c>
       <c r="B153" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>130250335</v>
       </c>
       <c r="B154" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>130250286</v>
       </c>
       <c r="B155" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>130250341</v>
       </c>
       <c r="B156" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>130250276</v>
       </c>
       <c r="B157" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>130250336</v>
       </c>
       <c r="B158" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>130250326</v>
       </c>
       <c r="B159" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>130250329</v>
       </c>
       <c r="B160" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>130250319</v>
       </c>
       <c r="B161" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>130250279</v>
       </c>
       <c r="B162" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>130250340</v>
       </c>
       <c r="B163" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>130250248</v>
       </c>
       <c r="B164" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>130250287</v>
       </c>
       <c r="B165" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>130250391</v>
       </c>
       <c r="B166" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>130250398</v>
       </c>
       <c r="B167" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>130250282</v>
       </c>
       <c r="B168" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>130250371</v>
       </c>
       <c r="B169" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>130250342</v>
       </c>
       <c r="B170" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>130250347</v>
       </c>
       <c r="B171" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>130250260</v>
       </c>
       <c r="B172" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>130250290</v>
       </c>
       <c r="B173" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>130250388</v>
       </c>
       <c r="B174" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>130250368</v>
       </c>
       <c r="B175" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>130250396</v>
       </c>
       <c r="B176" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>130250346</v>
       </c>
       <c r="B177" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>130250318</v>
       </c>
       <c r="B178" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>130250265</v>
       </c>
       <c r="B179" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250333</v>
+        <v>130250325</v>
       </c>
       <c r="B180" t="n">
-        <v>78852</v>
+        <v>78938</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445201</v>
+        <v>445457</v>
       </c>
       <c r="R180" t="n">
-        <v>6811621</v>
+        <v>6811516</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250344</v>
+        <v>130250333</v>
       </c>
       <c r="B181" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445358</v>
+        <v>445201</v>
       </c>
       <c r="R181" t="n">
-        <v>6811433</v>
+        <v>6811621</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,10 +18745,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250383</v>
+        <v>130250344</v>
       </c>
       <c r="B182" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18756,21 +18756,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18780,10 +18780,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445209</v>
+        <v>445358</v>
       </c>
       <c r="R182" t="n">
-        <v>6811451</v>
+        <v>6811433</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,10 +18842,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250325</v>
+        <v>130250383</v>
       </c>
       <c r="B183" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18853,21 +18853,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445457</v>
+        <v>445209</v>
       </c>
       <c r="R183" t="n">
-        <v>6811516</v>
+        <v>6811451</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18942,7 +18942,7 @@
         <v>130250311</v>
       </c>
       <c r="B184" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>130250406</v>
       </c>
       <c r="B185" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>130250377</v>
       </c>
       <c r="B186" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>130250284</v>
       </c>
       <c r="B187" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>130250268</v>
       </c>
       <c r="B188" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>130250257</v>
       </c>
       <c r="B189" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>130250312</v>
       </c>
       <c r="B191" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>130250306</v>
       </c>
       <c r="B192" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>130250363</v>
       </c>
       <c r="B193" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>130250327</v>
       </c>
       <c r="B194" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>130250250</v>
       </c>
       <c r="B195" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>130250370</v>
       </c>
       <c r="B196" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>130250298</v>
       </c>
       <c r="B197" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>130250300</v>
       </c>
       <c r="B198" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>130250355</v>
       </c>
       <c r="B199" t="n">
-        <v>57733</v>
+        <v>57818</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>130250277</v>
       </c>
       <c r="B200" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>130250395</v>
       </c>
       <c r="B201" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>130250256</v>
       </c>
       <c r="B202" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>130250386</v>
       </c>
       <c r="B203" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>130250291</v>
       </c>
       <c r="B204" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>130250281</v>
       </c>
       <c r="B205" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250392</v>
+        <v>130250280</v>
       </c>
       <c r="B206" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,34 +21182,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445487</v>
+        <v>445179</v>
       </c>
       <c r="R206" t="n">
-        <v>6811345</v>
+        <v>6811467</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21268,10 +21276,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250389</v>
+        <v>130250264</v>
       </c>
       <c r="B207" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21279,21 +21287,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21303,10 +21311,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445483</v>
+        <v>445315</v>
       </c>
       <c r="R207" t="n">
-        <v>6811288</v>
+        <v>6811230</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21365,10 +21373,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250367</v>
+        <v>130250254</v>
       </c>
       <c r="B208" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21376,21 +21384,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21400,10 +21408,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445376</v>
+        <v>445194</v>
       </c>
       <c r="R208" t="n">
-        <v>6811581</v>
+        <v>6811426</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21462,10 +21470,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250280</v>
+        <v>130250258</v>
       </c>
       <c r="B209" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21473,42 +21481,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445179</v>
+        <v>445470</v>
       </c>
       <c r="R209" t="n">
-        <v>6811467</v>
+        <v>6811435</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21567,10 +21567,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250264</v>
+        <v>130250310</v>
       </c>
       <c r="B210" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21578,34 +21578,42 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445315</v>
+        <v>445339</v>
       </c>
       <c r="R210" t="n">
-        <v>6811230</v>
+        <v>6811359</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21664,10 +21672,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250254</v>
+        <v>130250249</v>
       </c>
       <c r="B211" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21699,10 +21707,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445194</v>
+        <v>445200</v>
       </c>
       <c r="R211" t="n">
-        <v>6811426</v>
+        <v>6811598</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21761,10 +21769,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250258</v>
+        <v>130250305</v>
       </c>
       <c r="B212" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21772,34 +21780,42 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445470</v>
+        <v>445448</v>
       </c>
       <c r="R212" t="n">
-        <v>6811435</v>
+        <v>6811432</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21858,10 +21874,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250310</v>
+        <v>130250283</v>
       </c>
       <c r="B213" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21901,10 +21917,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445339</v>
+        <v>445303</v>
       </c>
       <c r="R213" t="n">
-        <v>6811359</v>
+        <v>6811621</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21963,10 +21979,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250249</v>
+        <v>130250392</v>
       </c>
       <c r="B214" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21974,21 +21990,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21998,10 +22014,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445200</v>
+        <v>445487</v>
       </c>
       <c r="R214" t="n">
-        <v>6811598</v>
+        <v>6811345</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,10 +22076,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250305</v>
+        <v>130250389</v>
       </c>
       <c r="B215" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22071,42 +22087,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445448</v>
+        <v>445483</v>
       </c>
       <c r="R215" t="n">
-        <v>6811432</v>
+        <v>6811288</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22165,10 +22173,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250283</v>
+        <v>130250367</v>
       </c>
       <c r="B216" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22176,42 +22184,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445303</v>
+        <v>445376</v>
       </c>
       <c r="R216" t="n">
-        <v>6811621</v>
+        <v>6811581</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22273,7 +22273,7 @@
         <v>130250247</v>
       </c>
       <c r="B217" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>130250308</v>
       </c>
       <c r="B218" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>130250348</v>
       </c>
       <c r="B219" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>130250253</v>
       </c>
       <c r="B220" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>130250252</v>
       </c>
       <c r="B221" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>130250387</v>
       </c>
       <c r="B222" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>130250307</v>
       </c>
       <c r="B223" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>130250299</v>
       </c>
       <c r="B224" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>130250334</v>
       </c>
       <c r="B225" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>130250400</v>
       </c>
       <c r="B226" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>130250358</v>
       </c>
       <c r="B227" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>130250263</v>
       </c>
       <c r="B228" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>130250382</v>
       </c>
       <c r="B229" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>130250372</v>
       </c>
       <c r="B230" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>130250285</v>
       </c>
       <c r="B231" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>130250393</v>
       </c>
       <c r="B232" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>130250380</v>
       </c>
       <c r="B233" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>130250324</v>
       </c>
       <c r="B234" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>130250408</v>
       </c>
       <c r="B235" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>130250301</v>
       </c>
       <c r="B236" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>130250288</v>
       </c>
       <c r="B237" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>130250316</v>
       </c>
       <c r="B238" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>130250246</v>
       </c>
       <c r="B239" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>130250405</v>
       </c>
       <c r="B240" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>130250397</v>
       </c>
       <c r="B241" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250384</v>
+        <v>130250337</v>
       </c>
       <c r="B242" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,21 +24766,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24790,10 +24790,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445209</v>
+        <v>445441</v>
       </c>
       <c r="R242" t="n">
-        <v>6811374</v>
+        <v>6811531</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24852,10 +24852,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250375</v>
+        <v>130250384</v>
       </c>
       <c r="B243" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24887,10 +24887,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445492</v>
+        <v>445209</v>
       </c>
       <c r="R243" t="n">
-        <v>6811496</v>
+        <v>6811374</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24949,10 +24949,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250378</v>
+        <v>130250375</v>
       </c>
       <c r="B244" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24984,10 +24984,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445421</v>
+        <v>445492</v>
       </c>
       <c r="R244" t="n">
-        <v>6811499</v>
+        <v>6811496</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25046,10 +25046,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250407</v>
+        <v>130250378</v>
       </c>
       <c r="B245" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25081,10 +25081,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445299</v>
+        <v>445421</v>
       </c>
       <c r="R245" t="n">
-        <v>6811253</v>
+        <v>6811499</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25143,10 +25143,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250403</v>
+        <v>130250407</v>
       </c>
       <c r="B246" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25178,10 +25178,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445337</v>
+        <v>445299</v>
       </c>
       <c r="R246" t="n">
-        <v>6811372</v>
+        <v>6811253</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25240,10 +25240,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250295</v>
+        <v>130250403</v>
       </c>
       <c r="B247" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25251,42 +25251,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445263</v>
+        <v>445337</v>
       </c>
       <c r="R247" t="n">
-        <v>6811480</v>
+        <v>6811372</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25345,10 +25337,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250359</v>
+        <v>130250295</v>
       </c>
       <c r="B248" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25356,34 +25348,42 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445161</v>
+        <v>445263</v>
       </c>
       <c r="R248" t="n">
-        <v>6811404</v>
+        <v>6811480</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25442,10 +25442,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250337</v>
+        <v>130250359</v>
       </c>
       <c r="B249" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25453,21 +25453,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25477,10 +25477,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445441</v>
+        <v>445161</v>
       </c>
       <c r="R249" t="n">
-        <v>6811531</v>
+        <v>6811404</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25536,6 +25536,111 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>130250353</v>
+      </c>
+      <c r="B250" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Gumpersbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>445347</v>
+      </c>
+      <c r="R250" t="n">
+        <v>6811352</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237777</v>
+        <v>130237738</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445058</v>
+        <v>445081</v>
       </c>
       <c r="R9" t="n">
-        <v>6811322</v>
+        <v>6811319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237749</v>
+        <v>130237777</v>
       </c>
       <c r="B10" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445027</v>
+        <v>445058</v>
       </c>
       <c r="R10" t="n">
-        <v>6811319</v>
+        <v>6811322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237705</v>
+        <v>130237749</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,42 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445092</v>
+        <v>445027</v>
       </c>
       <c r="R11" t="n">
-        <v>6811513</v>
+        <v>6811319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2000,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237738</v>
+        <v>130237705</v>
       </c>
       <c r="B15" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,34 +2003,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445081</v>
+        <v>445092</v>
       </c>
       <c r="R15" t="n">
-        <v>6811319</v>
+        <v>6811513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130237737</v>
+        <v>130237748</v>
       </c>
       <c r="B31" t="n">
-        <v>78938</v>
+        <v>78937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445091</v>
+        <v>445075</v>
       </c>
       <c r="R31" t="n">
-        <v>6811332</v>
+        <v>6811351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237748</v>
+        <v>130237765</v>
       </c>
       <c r="B32" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445075</v>
+        <v>445089</v>
       </c>
       <c r="R32" t="n">
-        <v>6811351</v>
+        <v>6811602</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237765</v>
+        <v>130237737</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445089</v>
+        <v>445091</v>
       </c>
       <c r="R33" t="n">
-        <v>6811602</v>
+        <v>6811332</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B63" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,34 +6813,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R63" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237713</v>
+        <v>130237664</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,42 +6918,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445073</v>
+        <v>444968</v>
       </c>
       <c r="R64" t="n">
-        <v>6811446</v>
+        <v>6811605</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237711</v>
+        <v>130237713</v>
       </c>
       <c r="B65" t="n">
         <v>57823</v>
@@ -7037,7 +7037,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445054</v>
+        <v>445073</v>
       </c>
       <c r="R65" t="n">
-        <v>6811454</v>
+        <v>6811446</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237720</v>
+        <v>130237711</v>
       </c>
       <c r="B66" t="n">
         <v>57823</v>
@@ -7142,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445048</v>
+        <v>445054</v>
       </c>
       <c r="R66" t="n">
-        <v>6811299</v>
+        <v>6811454</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B67" t="n">
         <v>57823</v>
@@ -7247,7 +7247,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R67" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250357</v>
+        <v>130250259</v>
       </c>
       <c r="B120" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12577,21 +12577,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445165</v>
+        <v>445441</v>
       </c>
       <c r="R120" t="n">
-        <v>6811302</v>
+        <v>6811433</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12663,7 +12663,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250394</v>
+        <v>130250404</v>
       </c>
       <c r="B121" t="n">
         <v>79180</v>
@@ -12692,19 +12692,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445495</v>
+        <v>445330</v>
       </c>
       <c r="R121" t="n">
-        <v>6811385</v>
+        <v>6811333</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12745,7 +12742,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12764,10 +12760,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250289</v>
+        <v>130250360</v>
       </c>
       <c r="B122" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12775,42 +12771,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445468</v>
+        <v>445194</v>
       </c>
       <c r="R122" t="n">
-        <v>6811500</v>
+        <v>6811530</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12869,10 +12857,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250314</v>
+        <v>130250338</v>
       </c>
       <c r="B123" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12880,42 +12868,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445322</v>
+        <v>445492</v>
       </c>
       <c r="R123" t="n">
-        <v>6811309</v>
+        <v>6811520</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12974,10 +12954,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250293</v>
+        <v>130250399</v>
       </c>
       <c r="B124" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12985,42 +12965,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445303</v>
+        <v>445416</v>
       </c>
       <c r="R124" t="n">
-        <v>6811490</v>
+        <v>6811445</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13079,10 +13051,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250315</v>
+        <v>130250357</v>
       </c>
       <c r="B125" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13090,42 +13062,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445317</v>
+        <v>445165</v>
       </c>
       <c r="R125" t="n">
-        <v>6811271</v>
+        <v>6811302</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13184,10 +13148,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250259</v>
+        <v>130250394</v>
       </c>
       <c r="B126" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13195,34 +13159,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445441</v>
+        <v>445495</v>
       </c>
       <c r="R126" t="n">
-        <v>6811433</v>
+        <v>6811385</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13263,6 +13230,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13281,10 +13249,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250404</v>
+        <v>130250289</v>
       </c>
       <c r="B127" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13292,34 +13260,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445330</v>
+        <v>445468</v>
       </c>
       <c r="R127" t="n">
-        <v>6811333</v>
+        <v>6811500</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13378,10 +13354,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250360</v>
+        <v>130250314</v>
       </c>
       <c r="B128" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13389,34 +13365,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445194</v>
+        <v>445322</v>
       </c>
       <c r="R128" t="n">
-        <v>6811530</v>
+        <v>6811309</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13475,10 +13459,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250338</v>
+        <v>130250293</v>
       </c>
       <c r="B129" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13486,34 +13470,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445492</v>
+        <v>445303</v>
       </c>
       <c r="R129" t="n">
-        <v>6811520</v>
+        <v>6811490</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13572,10 +13564,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250399</v>
+        <v>130250315</v>
       </c>
       <c r="B130" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13583,34 +13575,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445416</v>
+        <v>445317</v>
       </c>
       <c r="R130" t="n">
-        <v>6811445</v>
+        <v>6811271</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13863,10 +13863,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130250251</v>
+        <v>130250374</v>
       </c>
       <c r="B133" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13874,21 +13874,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>445494</v>
+        <v>445536</v>
       </c>
       <c r="R133" t="n">
-        <v>6811520</v>
+        <v>6811476</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13960,10 +13960,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130250361</v>
+        <v>130250251</v>
       </c>
       <c r="B134" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13971,21 +13971,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>445228</v>
+        <v>445494</v>
       </c>
       <c r="R134" t="n">
-        <v>6811593</v>
+        <v>6811520</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14057,7 +14057,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130250374</v>
+        <v>130250361</v>
       </c>
       <c r="B135" t="n">
         <v>79180</v>
@@ -14092,10 +14092,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>445536</v>
+        <v>445228</v>
       </c>
       <c r="R135" t="n">
-        <v>6811476</v>
+        <v>6811593</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14445,7 +14445,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130250273</v>
+        <v>130250269</v>
       </c>
       <c r="B139" t="n">
         <v>57016</v>
@@ -14488,10 +14488,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>445473</v>
+        <v>445426</v>
       </c>
       <c r="R139" t="n">
-        <v>6811354</v>
+        <v>6811568</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130250275</v>
+        <v>130250273</v>
       </c>
       <c r="B140" t="n">
         <v>57016</v>
@@ -14583,7 +14583,7 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>445379</v>
+        <v>445473</v>
       </c>
       <c r="R140" t="n">
-        <v>6811372</v>
+        <v>6811354</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14655,7 +14655,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130250269</v>
+        <v>130250275</v>
       </c>
       <c r="B141" t="n">
         <v>57016</v>
@@ -14688,7 +14688,7 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>445426</v>
+        <v>445379</v>
       </c>
       <c r="R141" t="n">
-        <v>6811568</v>
+        <v>6811372</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -19959,53 +19959,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130250355</v>
+        <v>130250250</v>
       </c>
       <c r="B194" t="n">
-        <v>57818</v>
+        <v>79799</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100110</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445443</v>
+        <v>445248</v>
       </c>
       <c r="R194" t="n">
-        <v>6811494</v>
+        <v>6811642</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20064,10 +20056,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250250</v>
+        <v>130250395</v>
       </c>
       <c r="B195" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20075,21 +20067,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20099,10 +20091,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445248</v>
+        <v>445507</v>
       </c>
       <c r="R195" t="n">
-        <v>6811642</v>
+        <v>6811412</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20161,10 +20153,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250395</v>
+        <v>130250256</v>
       </c>
       <c r="B196" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20172,21 +20164,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20196,10 +20188,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445507</v>
+        <v>445484</v>
       </c>
       <c r="R196" t="n">
-        <v>6811412</v>
+        <v>6811291</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20258,10 +20250,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250256</v>
+        <v>130250370</v>
       </c>
       <c r="B197" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20269,21 +20261,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20293,10 +20285,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445484</v>
+        <v>445542</v>
       </c>
       <c r="R197" t="n">
-        <v>6811291</v>
+        <v>6811532</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20355,7 +20347,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250370</v>
+        <v>130250386</v>
       </c>
       <c r="B198" t="n">
         <v>79180</v>
@@ -20390,10 +20382,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445542</v>
+        <v>445226</v>
       </c>
       <c r="R198" t="n">
-        <v>6811532</v>
+        <v>6811348</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20452,10 +20444,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250386</v>
+        <v>130250298</v>
       </c>
       <c r="B199" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20463,34 +20455,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445226</v>
+        <v>445232</v>
       </c>
       <c r="R199" t="n">
-        <v>6811348</v>
+        <v>6811448</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20549,7 +20549,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250298</v>
+        <v>130250300</v>
       </c>
       <c r="B200" t="n">
         <v>57823</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445232</v>
+        <v>445219</v>
       </c>
       <c r="R200" t="n">
-        <v>6811448</v>
+        <v>6811344</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20654,7 +20654,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250300</v>
+        <v>130250291</v>
       </c>
       <c r="B201" t="n">
         <v>57823</v>
@@ -20697,10 +20697,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445219</v>
+        <v>445385</v>
       </c>
       <c r="R201" t="n">
-        <v>6811344</v>
+        <v>6811504</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20759,7 +20759,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250291</v>
+        <v>130250281</v>
       </c>
       <c r="B202" t="n">
         <v>57823</v>
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445385</v>
+        <v>445205</v>
       </c>
       <c r="R202" t="n">
-        <v>6811504</v>
+        <v>6811619</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20864,32 +20864,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250281</v>
+        <v>130250277</v>
       </c>
       <c r="B203" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20897,7 +20897,7 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
@@ -20907,10 +20907,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445205</v>
+        <v>445202</v>
       </c>
       <c r="R203" t="n">
-        <v>6811619</v>
+        <v>6811655</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20969,10 +20969,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250277</v>
+        <v>130250355</v>
       </c>
       <c r="B204" t="n">
-        <v>57016</v>
+        <v>57818</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20980,21 +20980,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21002,7 +21002,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445202</v>
+        <v>445443</v>
       </c>
       <c r="R204" t="n">
-        <v>6811655</v>
+        <v>6811494</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250264</v>
+        <v>130250280</v>
       </c>
       <c r="B206" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,34 +21182,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445315</v>
+        <v>445179</v>
       </c>
       <c r="R206" t="n">
-        <v>6811230</v>
+        <v>6811467</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21268,10 +21276,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250254</v>
+        <v>130250283</v>
       </c>
       <c r="B207" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21279,34 +21287,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445194</v>
+        <v>445303</v>
       </c>
       <c r="R207" t="n">
-        <v>6811426</v>
+        <v>6811621</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21365,7 +21381,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250258</v>
+        <v>130250264</v>
       </c>
       <c r="B208" t="n">
         <v>79799</v>
@@ -21400,10 +21416,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445470</v>
+        <v>445315</v>
       </c>
       <c r="R208" t="n">
-        <v>6811435</v>
+        <v>6811230</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21462,7 +21478,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250249</v>
+        <v>130250254</v>
       </c>
       <c r="B209" t="n">
         <v>79799</v>
@@ -21497,10 +21513,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445200</v>
+        <v>445194</v>
       </c>
       <c r="R209" t="n">
-        <v>6811598</v>
+        <v>6811426</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21559,10 +21575,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250389</v>
+        <v>130250258</v>
       </c>
       <c r="B210" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21570,21 +21586,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21594,10 +21610,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445483</v>
+        <v>445470</v>
       </c>
       <c r="R210" t="n">
-        <v>6811288</v>
+        <v>6811435</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21656,10 +21672,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250367</v>
+        <v>130250249</v>
       </c>
       <c r="B211" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21667,21 +21683,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21691,10 +21707,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445376</v>
+        <v>445200</v>
       </c>
       <c r="R211" t="n">
-        <v>6811581</v>
+        <v>6811598</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21753,7 +21769,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250392</v>
+        <v>130250389</v>
       </c>
       <c r="B212" t="n">
         <v>79180</v>
@@ -21788,10 +21804,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445487</v>
+        <v>445483</v>
       </c>
       <c r="R212" t="n">
-        <v>6811345</v>
+        <v>6811288</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21850,10 +21866,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250280</v>
+        <v>130250367</v>
       </c>
       <c r="B213" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21861,42 +21877,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445179</v>
+        <v>445376</v>
       </c>
       <c r="R213" t="n">
-        <v>6811467</v>
+        <v>6811581</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21955,10 +21963,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250310</v>
+        <v>130250392</v>
       </c>
       <c r="B214" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21966,42 +21974,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445339</v>
+        <v>445487</v>
       </c>
       <c r="R214" t="n">
-        <v>6811359</v>
+        <v>6811345</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B215" t="n">
         <v>57823</v>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R215" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22165,7 +22165,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250283</v>
+        <v>130250305</v>
       </c>
       <c r="B216" t="n">
         <v>57823</v>
@@ -22208,10 +22208,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445303</v>
+        <v>445448</v>
       </c>
       <c r="R216" t="n">
-        <v>6811621</v>
+        <v>6811432</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250337</v>
+        <v>130250384</v>
       </c>
       <c r="B242" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,21 +24766,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24790,10 +24790,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445441</v>
+        <v>445209</v>
       </c>
       <c r="R242" t="n">
-        <v>6811531</v>
+        <v>6811374</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24852,7 +24852,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250378</v>
+        <v>130250375</v>
       </c>
       <c r="B243" t="n">
         <v>79180</v>
@@ -24887,10 +24887,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445421</v>
+        <v>445492</v>
       </c>
       <c r="R243" t="n">
-        <v>6811499</v>
+        <v>6811496</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24949,10 +24949,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250407</v>
+        <v>130250295</v>
       </c>
       <c r="B244" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24960,34 +24960,42 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445299</v>
+        <v>445263</v>
       </c>
       <c r="R244" t="n">
-        <v>6811253</v>
+        <v>6811480</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25046,10 +25054,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250403</v>
+        <v>130250337</v>
       </c>
       <c r="B245" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25057,21 +25065,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25081,10 +25089,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445337</v>
+        <v>445441</v>
       </c>
       <c r="R245" t="n">
-        <v>6811372</v>
+        <v>6811531</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25143,7 +25151,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250359</v>
+        <v>130250378</v>
       </c>
       <c r="B246" t="n">
         <v>79180</v>
@@ -25178,10 +25186,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445161</v>
+        <v>445421</v>
       </c>
       <c r="R246" t="n">
-        <v>6811404</v>
+        <v>6811499</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25240,7 +25248,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250384</v>
+        <v>130250407</v>
       </c>
       <c r="B247" t="n">
         <v>79180</v>
@@ -25275,10 +25283,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445209</v>
+        <v>445299</v>
       </c>
       <c r="R247" t="n">
-        <v>6811374</v>
+        <v>6811253</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25337,7 +25345,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250375</v>
+        <v>130250403</v>
       </c>
       <c r="B248" t="n">
         <v>79180</v>
@@ -25372,10 +25380,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445492</v>
+        <v>445337</v>
       </c>
       <c r="R248" t="n">
-        <v>6811496</v>
+        <v>6811372</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25434,10 +25442,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250295</v>
+        <v>130250359</v>
       </c>
       <c r="B249" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25445,42 +25453,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445263</v>
+        <v>445161</v>
       </c>
       <c r="R249" t="n">
-        <v>6811480</v>
+        <v>6811404</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -2582,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237693</v>
+        <v>130237667</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,42 +2593,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445027</v>
+        <v>445051</v>
       </c>
       <c r="R21" t="n">
-        <v>6811603</v>
+        <v>6811326</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130237714</v>
+        <v>130237736</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2698,42 +2690,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445083</v>
+        <v>445078</v>
       </c>
       <c r="R22" t="n">
-        <v>6811458</v>
+        <v>6811349</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2776,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237667</v>
+        <v>130237693</v>
       </c>
       <c r="B23" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,34 +2787,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445051</v>
+        <v>445027</v>
       </c>
       <c r="R23" t="n">
-        <v>6811326</v>
+        <v>6811603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130237736</v>
+        <v>130237714</v>
       </c>
       <c r="B24" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,34 +2892,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445078</v>
+        <v>445083</v>
       </c>
       <c r="R24" t="n">
-        <v>6811349</v>
+        <v>6811458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237744</v>
+        <v>130237723</v>
       </c>
       <c r="B25" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,34 +2997,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445002</v>
+        <v>445063</v>
       </c>
       <c r="R25" t="n">
-        <v>6811503</v>
+        <v>6811256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3083,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237723</v>
+        <v>130237744</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3094,42 +3102,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445063</v>
+        <v>445002</v>
       </c>
       <c r="R26" t="n">
-        <v>6811256</v>
+        <v>6811503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130237748</v>
+        <v>130237737</v>
       </c>
       <c r="B31" t="n">
-        <v>78937</v>
+        <v>78938</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445075</v>
+        <v>445091</v>
       </c>
       <c r="R31" t="n">
-        <v>6811351</v>
+        <v>6811332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237765</v>
+        <v>130237748</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445089</v>
+        <v>445075</v>
       </c>
       <c r="R32" t="n">
-        <v>6811602</v>
+        <v>6811351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237737</v>
+        <v>130237765</v>
       </c>
       <c r="B33" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445091</v>
+        <v>445089</v>
       </c>
       <c r="R33" t="n">
-        <v>6811332</v>
+        <v>6811602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237660</v>
+        <v>130237708</v>
       </c>
       <c r="B47" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,34 +5201,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R47" t="n">
-        <v>6811440</v>
+        <v>6811502</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237708</v>
+        <v>130237734</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,31 +5306,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5330,10 +5333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445066</v>
+        <v>444954</v>
       </c>
       <c r="R48" t="n">
-        <v>6811502</v>
+        <v>6811588</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5374,6 +5377,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5489,10 +5493,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130237734</v>
+        <v>130237660</v>
       </c>
       <c r="B50" t="n">
-        <v>78938</v>
+        <v>79799</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5500,37 +5504,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444954</v>
+        <v>444997</v>
       </c>
       <c r="R50" t="n">
-        <v>6811588</v>
+        <v>6811440</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5571,7 +5572,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6301,45 +6301,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237727</v>
+        <v>130237725</v>
       </c>
       <c r="B58" t="n">
-        <v>97791</v>
+        <v>57823</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445095</v>
+        <v>445073</v>
       </c>
       <c r="R58" t="n">
-        <v>6811427</v>
+        <v>6811522</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6592,53 +6600,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237725</v>
+        <v>130237727</v>
       </c>
       <c r="B61" t="n">
-        <v>57823</v>
+        <v>97791</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445073</v>
+        <v>445095</v>
       </c>
       <c r="R61" t="n">
-        <v>6811522</v>
+        <v>6811427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237709</v>
+        <v>130237664</v>
       </c>
       <c r="B63" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,42 +6813,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445058</v>
+        <v>444968</v>
       </c>
       <c r="R63" t="n">
-        <v>6811482</v>
+        <v>6811605</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237664</v>
+        <v>130237713</v>
       </c>
       <c r="B64" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,34 +6910,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444968</v>
+        <v>445073</v>
       </c>
       <c r="R64" t="n">
-        <v>6811605</v>
+        <v>6811446</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237713</v>
+        <v>130237711</v>
       </c>
       <c r="B65" t="n">
         <v>57823</v>
@@ -7037,7 +7037,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445073</v>
+        <v>445054</v>
       </c>
       <c r="R65" t="n">
-        <v>6811446</v>
+        <v>6811454</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237711</v>
+        <v>130237720</v>
       </c>
       <c r="B66" t="n">
         <v>57823</v>
@@ -7142,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445054</v>
+        <v>445048</v>
       </c>
       <c r="R66" t="n">
-        <v>6811454</v>
+        <v>6811299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237720</v>
+        <v>130237709</v>
       </c>
       <c r="B67" t="n">
         <v>57823</v>
@@ -7247,7 +7247,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445048</v>
+        <v>445058</v>
       </c>
       <c r="R67" t="n">
-        <v>6811299</v>
+        <v>6811482</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9940,7 +9940,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237696</v>
+        <v>130237718</v>
       </c>
       <c r="B94" t="n">
         <v>57823</v>
@@ -9983,10 +9983,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445118</v>
+        <v>445116</v>
       </c>
       <c r="R94" t="n">
-        <v>6811654</v>
+        <v>6811382</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237718</v>
+        <v>130237696</v>
       </c>
       <c r="B96" t="n">
         <v>57823</v>
@@ -10185,10 +10185,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445116</v>
+        <v>445118</v>
       </c>
       <c r="R96" t="n">
-        <v>6811382</v>
+        <v>6811654</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130250304</v>
+        <v>130250364</v>
       </c>
       <c r="B101" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10646,42 +10646,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445494</v>
+        <v>445309</v>
       </c>
       <c r="R101" t="n">
-        <v>6811338</v>
+        <v>6811605</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,7 +10732,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130250309</v>
+        <v>130250304</v>
       </c>
       <c r="B102" t="n">
         <v>57823</v>
@@ -10783,10 +10775,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445368</v>
+        <v>445494</v>
       </c>
       <c r="R102" t="n">
-        <v>6811354</v>
+        <v>6811338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10845,7 +10837,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130250294</v>
+        <v>130250309</v>
       </c>
       <c r="B103" t="n">
         <v>57823</v>
@@ -10888,10 +10880,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445280</v>
+        <v>445368</v>
       </c>
       <c r="R103" t="n">
-        <v>6811472</v>
+        <v>6811354</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10950,10 +10942,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130250364</v>
+        <v>130250294</v>
       </c>
       <c r="B104" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10961,34 +10953,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445309</v>
+        <v>445280</v>
       </c>
       <c r="R104" t="n">
-        <v>6811605</v>
+        <v>6811472</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130250385</v>
+        <v>130250313</v>
       </c>
       <c r="B115" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12076,34 +12076,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445210</v>
+        <v>445334</v>
       </c>
       <c r="R115" t="n">
-        <v>6811346</v>
+        <v>6811325</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12162,10 +12170,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130250345</v>
+        <v>130250296</v>
       </c>
       <c r="B116" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12173,34 +12181,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445339</v>
+        <v>445240</v>
       </c>
       <c r="R116" t="n">
-        <v>6811359</v>
+        <v>6811502</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12259,10 +12275,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130250339</v>
+        <v>130250385</v>
       </c>
       <c r="B117" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12270,21 +12286,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12294,10 +12310,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445457</v>
+        <v>445210</v>
       </c>
       <c r="R117" t="n">
-        <v>6811516</v>
+        <v>6811346</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12356,10 +12372,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130250313</v>
+        <v>130250345</v>
       </c>
       <c r="B118" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12367,42 +12383,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445334</v>
+        <v>445339</v>
       </c>
       <c r="R118" t="n">
-        <v>6811325</v>
+        <v>6811359</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12461,10 +12469,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130250296</v>
+        <v>130250339</v>
       </c>
       <c r="B119" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12472,42 +12480,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445240</v>
+        <v>445457</v>
       </c>
       <c r="R119" t="n">
-        <v>6811502</v>
+        <v>6811516</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250259</v>
+        <v>130250357</v>
       </c>
       <c r="B120" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12577,21 +12577,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445441</v>
+        <v>445165</v>
       </c>
       <c r="R120" t="n">
-        <v>6811433</v>
+        <v>6811302</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12663,7 +12663,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250404</v>
+        <v>130250394</v>
       </c>
       <c r="B121" t="n">
         <v>79180</v>
@@ -12692,16 +12692,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445330</v>
+        <v>445495</v>
       </c>
       <c r="R121" t="n">
-        <v>6811333</v>
+        <v>6811385</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12742,6 +12745,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12760,10 +12764,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250360</v>
+        <v>130250289</v>
       </c>
       <c r="B122" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12771,34 +12775,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445194</v>
+        <v>445468</v>
       </c>
       <c r="R122" t="n">
-        <v>6811530</v>
+        <v>6811500</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12857,10 +12869,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250338</v>
+        <v>130250314</v>
       </c>
       <c r="B123" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12868,34 +12880,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445492</v>
+        <v>445322</v>
       </c>
       <c r="R123" t="n">
-        <v>6811520</v>
+        <v>6811309</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12954,10 +12974,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250399</v>
+        <v>130250293</v>
       </c>
       <c r="B124" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12965,34 +12985,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445416</v>
+        <v>445303</v>
       </c>
       <c r="R124" t="n">
-        <v>6811445</v>
+        <v>6811490</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13051,10 +13079,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250357</v>
+        <v>130250315</v>
       </c>
       <c r="B125" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13062,34 +13090,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445165</v>
+        <v>445317</v>
       </c>
       <c r="R125" t="n">
-        <v>6811302</v>
+        <v>6811271</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13148,10 +13184,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250394</v>
+        <v>130250259</v>
       </c>
       <c r="B126" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13159,37 +13195,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445495</v>
+        <v>445441</v>
       </c>
       <c r="R126" t="n">
-        <v>6811385</v>
+        <v>6811433</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13230,7 +13263,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13249,10 +13281,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250289</v>
+        <v>130250404</v>
       </c>
       <c r="B127" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13260,42 +13292,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445468</v>
+        <v>445330</v>
       </c>
       <c r="R127" t="n">
-        <v>6811500</v>
+        <v>6811333</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13354,10 +13378,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250314</v>
+        <v>130250360</v>
       </c>
       <c r="B128" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13365,42 +13389,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445322</v>
+        <v>445194</v>
       </c>
       <c r="R128" t="n">
-        <v>6811309</v>
+        <v>6811530</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13459,10 +13475,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250293</v>
+        <v>130250338</v>
       </c>
       <c r="B129" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13470,42 +13486,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445303</v>
+        <v>445492</v>
       </c>
       <c r="R129" t="n">
-        <v>6811490</v>
+        <v>6811520</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13564,10 +13572,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250315</v>
+        <v>130250399</v>
       </c>
       <c r="B130" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13575,42 +13583,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445317</v>
+        <v>445416</v>
       </c>
       <c r="R130" t="n">
-        <v>6811271</v>
+        <v>6811445</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13863,10 +13863,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130250374</v>
+        <v>130250251</v>
       </c>
       <c r="B133" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13874,21 +13874,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>445536</v>
+        <v>445494</v>
       </c>
       <c r="R133" t="n">
-        <v>6811476</v>
+        <v>6811520</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13960,10 +13960,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130250251</v>
+        <v>130250361</v>
       </c>
       <c r="B134" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13971,21 +13971,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>445494</v>
+        <v>445228</v>
       </c>
       <c r="R134" t="n">
-        <v>6811520</v>
+        <v>6811593</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14057,7 +14057,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130250361</v>
+        <v>130250374</v>
       </c>
       <c r="B135" t="n">
         <v>79180</v>
@@ -14092,10 +14092,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>445228</v>
+        <v>445536</v>
       </c>
       <c r="R135" t="n">
-        <v>6811593</v>
+        <v>6811476</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14760,7 +14760,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130250362</v>
+        <v>130250376</v>
       </c>
       <c r="B142" t="n">
         <v>79180</v>
@@ -14789,16 +14789,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>445218</v>
+        <v>445462</v>
       </c>
       <c r="R142" t="n">
-        <v>6811594</v>
+        <v>6811495</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14839,6 +14842,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14857,10 +14861,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250297</v>
+        <v>130250362</v>
       </c>
       <c r="B143" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14868,42 +14872,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445239</v>
+        <v>445218</v>
       </c>
       <c r="R143" t="n">
-        <v>6811474</v>
+        <v>6811594</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14962,32 +14958,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250292</v>
+        <v>130250274</v>
       </c>
       <c r="B144" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14995,7 +14991,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -15005,10 +15001,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445384</v>
+        <v>445376</v>
       </c>
       <c r="R144" t="n">
-        <v>6811490</v>
+        <v>6811389</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15067,32 +15063,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250303</v>
+        <v>130250271</v>
       </c>
       <c r="B145" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15100,7 +15096,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -15110,10 +15106,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445389</v>
+        <v>445375</v>
       </c>
       <c r="R145" t="n">
-        <v>6811264</v>
+        <v>6811502</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15172,10 +15168,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250376</v>
+        <v>130250323</v>
       </c>
       <c r="B146" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15183,37 +15179,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445462</v>
+        <v>445371</v>
       </c>
       <c r="R146" t="n">
-        <v>6811495</v>
+        <v>6811594</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15254,7 +15247,6 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15273,53 +15265,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250274</v>
+        <v>130250328</v>
       </c>
       <c r="B147" t="n">
-        <v>57016</v>
+        <v>78938</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445376</v>
+        <v>445329</v>
       </c>
       <c r="R147" t="n">
-        <v>6811389</v>
+        <v>6811272</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15378,53 +15362,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250271</v>
+        <v>130250266</v>
       </c>
       <c r="B148" t="n">
-        <v>57016</v>
+        <v>79770</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445375</v>
+        <v>445580</v>
       </c>
       <c r="R148" t="n">
-        <v>6811502</v>
+        <v>6811443</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15483,10 +15459,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250323</v>
+        <v>130250297</v>
       </c>
       <c r="B149" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15494,34 +15470,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445371</v>
+        <v>445239</v>
       </c>
       <c r="R149" t="n">
-        <v>6811594</v>
+        <v>6811474</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15580,10 +15564,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130250328</v>
+        <v>130250292</v>
       </c>
       <c r="B150" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15591,34 +15575,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>445329</v>
+        <v>445384</v>
       </c>
       <c r="R150" t="n">
-        <v>6811272</v>
+        <v>6811490</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15677,10 +15669,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250266</v>
+        <v>130250303</v>
       </c>
       <c r="B151" t="n">
-        <v>79770</v>
+        <v>57823</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15688,34 +15680,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445580</v>
+        <v>445389</v>
       </c>
       <c r="R151" t="n">
-        <v>6811443</v>
+        <v>6811264</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250280</v>
+        <v>130250264</v>
       </c>
       <c r="B206" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,42 +21182,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445179</v>
+        <v>445315</v>
       </c>
       <c r="R206" t="n">
-        <v>6811467</v>
+        <v>6811230</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21276,10 +21268,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250283</v>
+        <v>130250254</v>
       </c>
       <c r="B207" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21287,42 +21279,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445303</v>
+        <v>445194</v>
       </c>
       <c r="R207" t="n">
-        <v>6811621</v>
+        <v>6811426</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21381,7 +21365,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250264</v>
+        <v>130250258</v>
       </c>
       <c r="B208" t="n">
         <v>79799</v>
@@ -21416,10 +21400,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445315</v>
+        <v>445470</v>
       </c>
       <c r="R208" t="n">
-        <v>6811230</v>
+        <v>6811435</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21478,7 +21462,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250254</v>
+        <v>130250249</v>
       </c>
       <c r="B209" t="n">
         <v>79799</v>
@@ -21513,10 +21497,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445194</v>
+        <v>445200</v>
       </c>
       <c r="R209" t="n">
-        <v>6811426</v>
+        <v>6811598</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21575,10 +21559,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250258</v>
+        <v>130250389</v>
       </c>
       <c r="B210" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21586,21 +21570,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21610,10 +21594,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445470</v>
+        <v>445483</v>
       </c>
       <c r="R210" t="n">
-        <v>6811435</v>
+        <v>6811288</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21672,10 +21656,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250249</v>
+        <v>130250367</v>
       </c>
       <c r="B211" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21683,21 +21667,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21707,10 +21691,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445200</v>
+        <v>445376</v>
       </c>
       <c r="R211" t="n">
-        <v>6811598</v>
+        <v>6811581</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21769,7 +21753,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250389</v>
+        <v>130250392</v>
       </c>
       <c r="B212" t="n">
         <v>79180</v>
@@ -21804,10 +21788,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445483</v>
+        <v>445487</v>
       </c>
       <c r="R212" t="n">
-        <v>6811288</v>
+        <v>6811345</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21866,10 +21850,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250367</v>
+        <v>130250310</v>
       </c>
       <c r="B213" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21877,34 +21861,42 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445376</v>
+        <v>445339</v>
       </c>
       <c r="R213" t="n">
-        <v>6811581</v>
+        <v>6811359</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21963,10 +21955,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250392</v>
+        <v>130250305</v>
       </c>
       <c r="B214" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21974,34 +21966,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445487</v>
+        <v>445448</v>
       </c>
       <c r="R214" t="n">
-        <v>6811345</v>
+        <v>6811432</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250310</v>
+        <v>130250280</v>
       </c>
       <c r="B215" t="n">
         <v>57823</v>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445339</v>
+        <v>445179</v>
       </c>
       <c r="R215" t="n">
-        <v>6811359</v>
+        <v>6811467</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22165,7 +22165,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250305</v>
+        <v>130250283</v>
       </c>
       <c r="B216" t="n">
         <v>57823</v>
@@ -22208,10 +22208,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445448</v>
+        <v>445303</v>
       </c>
       <c r="R216" t="n">
-        <v>6811432</v>
+        <v>6811621</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250384</v>
+        <v>130250337</v>
       </c>
       <c r="B242" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,21 +24766,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24790,10 +24790,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445209</v>
+        <v>445441</v>
       </c>
       <c r="R242" t="n">
-        <v>6811374</v>
+        <v>6811531</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24852,7 +24852,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250375</v>
+        <v>130250378</v>
       </c>
       <c r="B243" t="n">
         <v>79180</v>
@@ -24887,10 +24887,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445492</v>
+        <v>445421</v>
       </c>
       <c r="R243" t="n">
-        <v>6811496</v>
+        <v>6811499</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24949,10 +24949,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250295</v>
+        <v>130250407</v>
       </c>
       <c r="B244" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24960,42 +24960,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445263</v>
+        <v>445299</v>
       </c>
       <c r="R244" t="n">
-        <v>6811480</v>
+        <v>6811253</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25054,10 +25046,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250337</v>
+        <v>130250403</v>
       </c>
       <c r="B245" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25065,21 +25057,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25089,10 +25081,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445441</v>
+        <v>445337</v>
       </c>
       <c r="R245" t="n">
-        <v>6811531</v>
+        <v>6811372</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25151,7 +25143,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250378</v>
+        <v>130250359</v>
       </c>
       <c r="B246" t="n">
         <v>79180</v>
@@ -25186,10 +25178,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445421</v>
+        <v>445161</v>
       </c>
       <c r="R246" t="n">
-        <v>6811499</v>
+        <v>6811404</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25248,7 +25240,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250407</v>
+        <v>130250384</v>
       </c>
       <c r="B247" t="n">
         <v>79180</v>
@@ -25283,10 +25275,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445299</v>
+        <v>445209</v>
       </c>
       <c r="R247" t="n">
-        <v>6811253</v>
+        <v>6811374</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25345,7 +25337,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250403</v>
+        <v>130250375</v>
       </c>
       <c r="B248" t="n">
         <v>79180</v>
@@ -25380,10 +25372,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445337</v>
+        <v>445492</v>
       </c>
       <c r="R248" t="n">
-        <v>6811372</v>
+        <v>6811496</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25442,10 +25434,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250359</v>
+        <v>130250295</v>
       </c>
       <c r="B249" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25453,34 +25445,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445161</v>
+        <v>445263</v>
       </c>
       <c r="R249" t="n">
-        <v>6811404</v>
+        <v>6811480</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237738</v>
+        <v>130237777</v>
       </c>
       <c r="B9" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445081</v>
+        <v>445058</v>
       </c>
       <c r="R9" t="n">
-        <v>6811319</v>
+        <v>6811322</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237777</v>
+        <v>130237749</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445058</v>
+        <v>445027</v>
       </c>
       <c r="R10" t="n">
-        <v>6811322</v>
+        <v>6811319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237749</v>
+        <v>130237705</v>
       </c>
       <c r="B11" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1599,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445027</v>
+        <v>445092</v>
       </c>
       <c r="R11" t="n">
-        <v>6811319</v>
+        <v>6811513</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1992,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237705</v>
+        <v>130237738</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,42 +2011,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445092</v>
+        <v>445081</v>
       </c>
       <c r="R15" t="n">
-        <v>6811513</v>
+        <v>6811319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237667</v>
+        <v>130237693</v>
       </c>
       <c r="B21" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,34 +2593,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445051</v>
+        <v>445027</v>
       </c>
       <c r="R21" t="n">
-        <v>6811326</v>
+        <v>6811603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,10 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130237736</v>
+        <v>130237714</v>
       </c>
       <c r="B22" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2690,34 +2698,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445078</v>
+        <v>445083</v>
       </c>
       <c r="R22" t="n">
-        <v>6811349</v>
+        <v>6811458</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237693</v>
+        <v>130237667</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2787,42 +2803,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445027</v>
+        <v>445051</v>
       </c>
       <c r="R23" t="n">
-        <v>6811603</v>
+        <v>6811326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130237714</v>
+        <v>130237736</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2892,42 +2900,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445083</v>
+        <v>445078</v>
       </c>
       <c r="R24" t="n">
-        <v>6811458</v>
+        <v>6811349</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237723</v>
+        <v>130237744</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,42 +2997,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445063</v>
+        <v>445002</v>
       </c>
       <c r="R25" t="n">
-        <v>6811256</v>
+        <v>6811503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3083,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237744</v>
+        <v>130237723</v>
       </c>
       <c r="B26" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,34 +3094,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445002</v>
+        <v>445063</v>
       </c>
       <c r="R26" t="n">
-        <v>6811503</v>
+        <v>6811256</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130237715</v>
+        <v>130237739</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,31 +3401,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3433,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445094</v>
+        <v>445044</v>
       </c>
       <c r="R29" t="n">
-        <v>6811438</v>
+        <v>6811298</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,6 +3472,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3491,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130237739</v>
+        <v>130237715</v>
       </c>
       <c r="B30" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,26 +3502,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3533,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445044</v>
+        <v>445094</v>
       </c>
       <c r="R30" t="n">
-        <v>6811298</v>
+        <v>6811438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3577,7 +3578,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B63" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,34 +6813,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R63" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237713</v>
+        <v>130237664</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,42 +6918,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445073</v>
+        <v>444968</v>
       </c>
       <c r="R64" t="n">
-        <v>6811446</v>
+        <v>6811605</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237711</v>
+        <v>130237713</v>
       </c>
       <c r="B65" t="n">
         <v>57823</v>
@@ -7037,7 +7037,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445054</v>
+        <v>445073</v>
       </c>
       <c r="R65" t="n">
-        <v>6811454</v>
+        <v>6811446</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237720</v>
+        <v>130237711</v>
       </c>
       <c r="B66" t="n">
         <v>57823</v>
@@ -7142,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445048</v>
+        <v>445054</v>
       </c>
       <c r="R66" t="n">
-        <v>6811299</v>
+        <v>6811454</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B67" t="n">
         <v>57823</v>
@@ -7247,7 +7247,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R67" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8648,10 +8648,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130237703</v>
+        <v>130237771</v>
       </c>
       <c r="B81" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8659,42 +8659,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445132</v>
+        <v>445159</v>
       </c>
       <c r="R81" t="n">
-        <v>6811535</v>
+        <v>6811562</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8753,10 +8745,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130237771</v>
+        <v>130237746</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8764,21 +8756,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8788,10 +8780,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445159</v>
+        <v>445153</v>
       </c>
       <c r="R82" t="n">
-        <v>6811562</v>
+        <v>6811549</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8850,10 +8842,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130237746</v>
+        <v>130237703</v>
       </c>
       <c r="B83" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8861,34 +8853,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445153</v>
+        <v>445132</v>
       </c>
       <c r="R83" t="n">
-        <v>6811549</v>
+        <v>6811535</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130250364</v>
+        <v>130250304</v>
       </c>
       <c r="B101" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10646,34 +10646,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445309</v>
+        <v>445494</v>
       </c>
       <c r="R101" t="n">
-        <v>6811605</v>
+        <v>6811338</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10732,7 +10740,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130250304</v>
+        <v>130250309</v>
       </c>
       <c r="B102" t="n">
         <v>57823</v>
@@ -10775,10 +10783,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445494</v>
+        <v>445368</v>
       </c>
       <c r="R102" t="n">
-        <v>6811338</v>
+        <v>6811354</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10837,7 +10845,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130250309</v>
+        <v>130250294</v>
       </c>
       <c r="B103" t="n">
         <v>57823</v>
@@ -10880,10 +10888,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445368</v>
+        <v>445280</v>
       </c>
       <c r="R103" t="n">
-        <v>6811354</v>
+        <v>6811472</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10942,10 +10950,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130250294</v>
+        <v>130250364</v>
       </c>
       <c r="B104" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10953,42 +10961,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445280</v>
+        <v>445309</v>
       </c>
       <c r="R104" t="n">
-        <v>6811472</v>
+        <v>6811605</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130250313</v>
+        <v>130250385</v>
       </c>
       <c r="B115" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12076,42 +12076,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445334</v>
+        <v>445210</v>
       </c>
       <c r="R115" t="n">
-        <v>6811325</v>
+        <v>6811346</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12170,10 +12162,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130250296</v>
+        <v>130250345</v>
       </c>
       <c r="B116" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12181,42 +12173,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445240</v>
+        <v>445339</v>
       </c>
       <c r="R116" t="n">
-        <v>6811502</v>
+        <v>6811359</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12275,10 +12259,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130250385</v>
+        <v>130250339</v>
       </c>
       <c r="B117" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12286,21 +12270,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12310,10 +12294,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445210</v>
+        <v>445457</v>
       </c>
       <c r="R117" t="n">
-        <v>6811346</v>
+        <v>6811516</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12372,10 +12356,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130250345</v>
+        <v>130250313</v>
       </c>
       <c r="B118" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12383,34 +12367,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445339</v>
+        <v>445334</v>
       </c>
       <c r="R118" t="n">
-        <v>6811359</v>
+        <v>6811325</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12469,10 +12461,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130250339</v>
+        <v>130250296</v>
       </c>
       <c r="B119" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12480,34 +12472,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445457</v>
+        <v>445240</v>
       </c>
       <c r="R119" t="n">
-        <v>6811516</v>
+        <v>6811502</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250357</v>
+        <v>130250259</v>
       </c>
       <c r="B120" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12577,21 +12577,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445165</v>
+        <v>445441</v>
       </c>
       <c r="R120" t="n">
-        <v>6811302</v>
+        <v>6811433</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12663,7 +12663,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250394</v>
+        <v>130250404</v>
       </c>
       <c r="B121" t="n">
         <v>79180</v>
@@ -12692,19 +12692,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445495</v>
+        <v>445330</v>
       </c>
       <c r="R121" t="n">
-        <v>6811385</v>
+        <v>6811333</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12745,7 +12742,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12764,10 +12760,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250289</v>
+        <v>130250360</v>
       </c>
       <c r="B122" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12775,42 +12771,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445468</v>
+        <v>445194</v>
       </c>
       <c r="R122" t="n">
-        <v>6811500</v>
+        <v>6811530</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12869,10 +12857,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250314</v>
+        <v>130250338</v>
       </c>
       <c r="B123" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12880,42 +12868,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445322</v>
+        <v>445492</v>
       </c>
       <c r="R123" t="n">
-        <v>6811309</v>
+        <v>6811520</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12974,10 +12954,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250293</v>
+        <v>130250399</v>
       </c>
       <c r="B124" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12985,42 +12965,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445303</v>
+        <v>445416</v>
       </c>
       <c r="R124" t="n">
-        <v>6811490</v>
+        <v>6811445</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13079,10 +13051,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250315</v>
+        <v>130250357</v>
       </c>
       <c r="B125" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13090,42 +13062,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445317</v>
+        <v>445165</v>
       </c>
       <c r="R125" t="n">
-        <v>6811271</v>
+        <v>6811302</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13184,10 +13148,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250259</v>
+        <v>130250394</v>
       </c>
       <c r="B126" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13195,34 +13159,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445441</v>
+        <v>445495</v>
       </c>
       <c r="R126" t="n">
-        <v>6811433</v>
+        <v>6811385</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13263,6 +13230,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13281,10 +13249,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250404</v>
+        <v>130250289</v>
       </c>
       <c r="B127" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13292,34 +13260,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445330</v>
+        <v>445468</v>
       </c>
       <c r="R127" t="n">
-        <v>6811333</v>
+        <v>6811500</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13378,10 +13354,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250360</v>
+        <v>130250314</v>
       </c>
       <c r="B128" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13389,34 +13365,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445194</v>
+        <v>445322</v>
       </c>
       <c r="R128" t="n">
-        <v>6811530</v>
+        <v>6811309</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13475,10 +13459,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250338</v>
+        <v>130250293</v>
       </c>
       <c r="B129" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13486,34 +13470,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445492</v>
+        <v>445303</v>
       </c>
       <c r="R129" t="n">
-        <v>6811520</v>
+        <v>6811490</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13572,10 +13564,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250399</v>
+        <v>130250315</v>
       </c>
       <c r="B130" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13583,34 +13575,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445416</v>
+        <v>445317</v>
       </c>
       <c r="R130" t="n">
-        <v>6811445</v>
+        <v>6811271</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14445,7 +14445,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130250269</v>
+        <v>130250273</v>
       </c>
       <c r="B139" t="n">
         <v>57016</v>
@@ -14488,10 +14488,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>445426</v>
+        <v>445473</v>
       </c>
       <c r="R139" t="n">
-        <v>6811568</v>
+        <v>6811354</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130250273</v>
+        <v>130250275</v>
       </c>
       <c r="B140" t="n">
         <v>57016</v>
@@ -14583,7 +14583,7 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
@@ -14593,10 +14593,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>445473</v>
+        <v>445379</v>
       </c>
       <c r="R140" t="n">
-        <v>6811354</v>
+        <v>6811372</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14655,7 +14655,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130250275</v>
+        <v>130250269</v>
       </c>
       <c r="B141" t="n">
         <v>57016</v>
@@ -14688,7 +14688,7 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>445379</v>
+        <v>445426</v>
       </c>
       <c r="R141" t="n">
-        <v>6811372</v>
+        <v>6811568</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14760,7 +14760,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130250376</v>
+        <v>130250362</v>
       </c>
       <c r="B142" t="n">
         <v>79180</v>
@@ -14789,19 +14789,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>445462</v>
+        <v>445218</v>
       </c>
       <c r="R142" t="n">
-        <v>6811495</v>
+        <v>6811594</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,7 +14839,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14861,10 +14857,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250362</v>
+        <v>130250297</v>
       </c>
       <c r="B143" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14872,34 +14868,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445218</v>
+        <v>445239</v>
       </c>
       <c r="R143" t="n">
-        <v>6811594</v>
+        <v>6811474</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14958,32 +14962,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250274</v>
+        <v>130250292</v>
       </c>
       <c r="B144" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14991,7 +14995,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -15001,10 +15005,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445376</v>
+        <v>445384</v>
       </c>
       <c r="R144" t="n">
-        <v>6811389</v>
+        <v>6811490</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15063,32 +15067,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250271</v>
+        <v>130250303</v>
       </c>
       <c r="B145" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15096,7 +15100,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -15106,10 +15110,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445375</v>
+        <v>445389</v>
       </c>
       <c r="R145" t="n">
-        <v>6811502</v>
+        <v>6811264</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15168,10 +15172,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250323</v>
+        <v>130250376</v>
       </c>
       <c r="B146" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15179,34 +15183,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445371</v>
+        <v>445462</v>
       </c>
       <c r="R146" t="n">
-        <v>6811594</v>
+        <v>6811495</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15247,6 +15254,7 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -15265,45 +15273,53 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250328</v>
+        <v>130250274</v>
       </c>
       <c r="B147" t="n">
-        <v>78938</v>
+        <v>57016</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445329</v>
+        <v>445376</v>
       </c>
       <c r="R147" t="n">
-        <v>6811272</v>
+        <v>6811389</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15362,45 +15378,53 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250266</v>
+        <v>130250271</v>
       </c>
       <c r="B148" t="n">
-        <v>79770</v>
+        <v>57016</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445580</v>
+        <v>445375</v>
       </c>
       <c r="R148" t="n">
-        <v>6811443</v>
+        <v>6811502</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15459,10 +15483,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250297</v>
+        <v>130250323</v>
       </c>
       <c r="B149" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15470,42 +15494,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445239</v>
+        <v>445371</v>
       </c>
       <c r="R149" t="n">
-        <v>6811474</v>
+        <v>6811594</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15564,10 +15580,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130250292</v>
+        <v>130250328</v>
       </c>
       <c r="B150" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15575,42 +15591,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>445384</v>
+        <v>445329</v>
       </c>
       <c r="R150" t="n">
-        <v>6811490</v>
+        <v>6811272</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15669,10 +15677,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250303</v>
+        <v>130250266</v>
       </c>
       <c r="B151" t="n">
-        <v>57823</v>
+        <v>79770</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15680,42 +15688,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445389</v>
+        <v>445580</v>
       </c>
       <c r="R151" t="n">
-        <v>6811264</v>
+        <v>6811443</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17670,10 +17670,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130250388</v>
+        <v>130250347</v>
       </c>
       <c r="B171" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17681,21 +17681,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17705,10 +17705,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>445362</v>
+        <v>445334</v>
       </c>
       <c r="R171" t="n">
-        <v>6811289</v>
+        <v>6811304</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17767,10 +17767,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130250396</v>
+        <v>130250260</v>
       </c>
       <c r="B172" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17778,21 +17778,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17802,10 +17802,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>445480</v>
+        <v>445425</v>
       </c>
       <c r="R172" t="n">
-        <v>6811420</v>
+        <v>6811413</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17864,32 +17864,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130250318</v>
+        <v>130250368</v>
       </c>
       <c r="B173" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17899,10 +17899,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>445180</v>
+        <v>445385</v>
       </c>
       <c r="R173" t="n">
-        <v>6811418</v>
+        <v>6811579</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130250265</v>
+        <v>130250346</v>
       </c>
       <c r="B174" t="n">
-        <v>79770</v>
+        <v>78937</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>445586</v>
+        <v>445322</v>
       </c>
       <c r="R174" t="n">
-        <v>6811454</v>
+        <v>6811363</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18058,10 +18058,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130250347</v>
+        <v>130250388</v>
       </c>
       <c r="B175" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18069,21 +18069,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18093,10 +18093,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>445334</v>
+        <v>445362</v>
       </c>
       <c r="R175" t="n">
-        <v>6811304</v>
+        <v>6811289</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18155,10 +18155,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130250260</v>
+        <v>130250396</v>
       </c>
       <c r="B176" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18166,21 +18166,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18190,10 +18190,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>445425</v>
+        <v>445480</v>
       </c>
       <c r="R176" t="n">
-        <v>6811413</v>
+        <v>6811420</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18252,10 +18252,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250368</v>
+        <v>130250290</v>
       </c>
       <c r="B177" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18263,34 +18263,42 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445385</v>
+        <v>445457</v>
       </c>
       <c r="R177" t="n">
-        <v>6811579</v>
+        <v>6811507</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18349,32 +18357,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130250346</v>
+        <v>130250318</v>
       </c>
       <c r="B178" t="n">
-        <v>78937</v>
+        <v>97791</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18384,10 +18392,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>445322</v>
+        <v>445180</v>
       </c>
       <c r="R178" t="n">
-        <v>6811363</v>
+        <v>6811418</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18446,10 +18454,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130250290</v>
+        <v>130250265</v>
       </c>
       <c r="B179" t="n">
-        <v>57823</v>
+        <v>79770</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18457,42 +18465,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>445457</v>
+        <v>445586</v>
       </c>
       <c r="R179" t="n">
-        <v>6811507</v>
+        <v>6811454</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21850,7 +21850,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250310</v>
+        <v>130250280</v>
       </c>
       <c r="B213" t="n">
         <v>57823</v>
@@ -21893,10 +21893,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445339</v>
+        <v>445179</v>
       </c>
       <c r="R213" t="n">
-        <v>6811359</v>
+        <v>6811467</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21955,7 +21955,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B214" t="n">
         <v>57823</v>
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R214" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250280</v>
+        <v>130250305</v>
       </c>
       <c r="B215" t="n">
         <v>57823</v>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445179</v>
+        <v>445448</v>
       </c>
       <c r="R215" t="n">
-        <v>6811467</v>
+        <v>6811432</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250337</v>
+        <v>130250384</v>
       </c>
       <c r="B242" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,21 +24766,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -24790,10 +24790,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445441</v>
+        <v>445209</v>
       </c>
       <c r="R242" t="n">
-        <v>6811531</v>
+        <v>6811374</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24852,7 +24852,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250378</v>
+        <v>130250375</v>
       </c>
       <c r="B243" t="n">
         <v>79180</v>
@@ -24887,10 +24887,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445421</v>
+        <v>445492</v>
       </c>
       <c r="R243" t="n">
-        <v>6811499</v>
+        <v>6811496</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24949,10 +24949,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250407</v>
+        <v>130250295</v>
       </c>
       <c r="B244" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -24960,34 +24960,42 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445299</v>
+        <v>445263</v>
       </c>
       <c r="R244" t="n">
-        <v>6811253</v>
+        <v>6811480</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25046,10 +25054,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250403</v>
+        <v>130250337</v>
       </c>
       <c r="B245" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25057,21 +25065,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25081,10 +25089,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445337</v>
+        <v>445441</v>
       </c>
       <c r="R245" t="n">
-        <v>6811372</v>
+        <v>6811531</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25143,7 +25151,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250359</v>
+        <v>130250378</v>
       </c>
       <c r="B246" t="n">
         <v>79180</v>
@@ -25178,10 +25186,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445161</v>
+        <v>445421</v>
       </c>
       <c r="R246" t="n">
-        <v>6811404</v>
+        <v>6811499</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25240,7 +25248,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250384</v>
+        <v>130250407</v>
       </c>
       <c r="B247" t="n">
         <v>79180</v>
@@ -25275,10 +25283,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445209</v>
+        <v>445299</v>
       </c>
       <c r="R247" t="n">
-        <v>6811374</v>
+        <v>6811253</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25337,7 +25345,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250375</v>
+        <v>130250403</v>
       </c>
       <c r="B248" t="n">
         <v>79180</v>
@@ -25372,10 +25380,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445492</v>
+        <v>445337</v>
       </c>
       <c r="R248" t="n">
-        <v>6811496</v>
+        <v>6811372</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25434,10 +25442,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250295</v>
+        <v>130250359</v>
       </c>
       <c r="B249" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25445,42 +25453,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445263</v>
+        <v>445161</v>
       </c>
       <c r="R249" t="n">
-        <v>6811480</v>
+        <v>6811404</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237745</v>
+        <v>130237691</v>
       </c>
       <c r="B5" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,34 +993,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444954</v>
+        <v>444991</v>
       </c>
       <c r="R5" t="n">
-        <v>6811588</v>
+        <v>6811568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237691</v>
+        <v>130237706</v>
       </c>
       <c r="B6" t="n">
         <v>57849</v>
@@ -1122,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444991</v>
+        <v>445093</v>
       </c>
       <c r="R6" t="n">
-        <v>6811568</v>
+        <v>6811481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1192,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130237706</v>
+        <v>130237712</v>
       </c>
       <c r="B7" t="n">
         <v>57849</v>
@@ -1227,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445093</v>
+        <v>445057</v>
       </c>
       <c r="R7" t="n">
-        <v>6811481</v>
+        <v>6811437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130237712</v>
+        <v>130237745</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,42 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445057</v>
+        <v>444954</v>
       </c>
       <c r="R8" t="n">
-        <v>6811437</v>
+        <v>6811588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237724</v>
+        <v>130237738</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,42 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445064</v>
+        <v>445081</v>
       </c>
       <c r="R9" t="n">
-        <v>6811249</v>
+        <v>6811319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237692</v>
+        <v>130237777</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,42 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445036</v>
+        <v>445058</v>
       </c>
       <c r="R10" t="n">
-        <v>6811602</v>
+        <v>6811322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237705</v>
+        <v>130237749</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,42 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445092</v>
+        <v>445027</v>
       </c>
       <c r="R11" t="n">
-        <v>6811513</v>
+        <v>6811319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237738</v>
+        <v>130237663</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>79828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445081</v>
+        <v>444954</v>
       </c>
       <c r="R12" t="n">
-        <v>6811319</v>
+        <v>6811588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237777</v>
+        <v>130237724</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,34 +1793,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445058</v>
+        <v>445064</v>
       </c>
       <c r="R13" t="n">
-        <v>6811322</v>
+        <v>6811249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130237749</v>
+        <v>130237692</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,34 +1898,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445027</v>
+        <v>445036</v>
       </c>
       <c r="R14" t="n">
-        <v>6811319</v>
+        <v>6811602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237663</v>
+        <v>130237705</v>
       </c>
       <c r="B15" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,34 +2003,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444954</v>
+        <v>445092</v>
       </c>
       <c r="R15" t="n">
-        <v>6811588</v>
+        <v>6811513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2986,32 +2986,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237677</v>
+        <v>130237723</v>
       </c>
       <c r="B25" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445025</v>
+        <v>445063</v>
       </c>
       <c r="R25" t="n">
-        <v>6811296</v>
+        <v>6811256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,45 +3091,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237744</v>
+        <v>130237677</v>
       </c>
       <c r="B26" t="n">
-        <v>78966</v>
+        <v>57042</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445002</v>
+        <v>445025</v>
       </c>
       <c r="R26" t="n">
-        <v>6811503</v>
+        <v>6811296</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,10 +3196,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237723</v>
+        <v>130237744</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3199,42 +3207,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445063</v>
+        <v>445002</v>
       </c>
       <c r="R27" t="n">
-        <v>6811256</v>
+        <v>6811503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130237748</v>
+        <v>130237737</v>
       </c>
       <c r="B31" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445075</v>
+        <v>445091</v>
       </c>
       <c r="R31" t="n">
-        <v>6811351</v>
+        <v>6811332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237765</v>
+        <v>130237748</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445089</v>
+        <v>445075</v>
       </c>
       <c r="R32" t="n">
-        <v>6811602</v>
+        <v>6811351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237737</v>
+        <v>130237765</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445091</v>
+        <v>445089</v>
       </c>
       <c r="R33" t="n">
-        <v>6811332</v>
+        <v>6811602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -6406,53 +6406,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130237679</v>
+        <v>130237662</v>
       </c>
       <c r="B59" t="n">
-        <v>57042</v>
+        <v>79828</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445036</v>
+        <v>445002</v>
       </c>
       <c r="R59" t="n">
-        <v>6811277</v>
+        <v>6811503</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,10 +6503,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130237727</v>
+        <v>130237679</v>
       </c>
       <c r="B60" t="n">
-        <v>97820</v>
+        <v>57042</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6522,34 +6514,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445095</v>
+        <v>445036</v>
       </c>
       <c r="R60" t="n">
-        <v>6811427</v>
+        <v>6811277</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237760</v>
+        <v>130237727</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>97820</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445075</v>
+        <v>445095</v>
       </c>
       <c r="R61" t="n">
-        <v>6811319</v>
+        <v>6811427</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130237662</v>
+        <v>130237760</v>
       </c>
       <c r="B62" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6716,21 +6716,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445002</v>
+        <v>445075</v>
       </c>
       <c r="R62" t="n">
-        <v>6811503</v>
+        <v>6811319</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8648,10 +8648,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130237746</v>
+        <v>130237703</v>
       </c>
       <c r="B81" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8659,34 +8659,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445153</v>
+        <v>445132</v>
       </c>
       <c r="R81" t="n">
-        <v>6811549</v>
+        <v>6811535</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8745,10 +8753,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130237771</v>
+        <v>130237746</v>
       </c>
       <c r="B82" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8756,21 +8764,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8780,10 +8788,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445159</v>
+        <v>445153</v>
       </c>
       <c r="R82" t="n">
-        <v>6811562</v>
+        <v>6811549</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8842,10 +8850,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130237703</v>
+        <v>130237771</v>
       </c>
       <c r="B83" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8853,42 +8861,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445132</v>
+        <v>445159</v>
       </c>
       <c r="R83" t="n">
-        <v>6811535</v>
+        <v>6811562</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11047,32 +11047,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250270</v>
+        <v>130250302</v>
       </c>
       <c r="B105" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11080,7 +11080,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
@@ -11090,10 +11090,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445426</v>
+        <v>445239</v>
       </c>
       <c r="R105" t="n">
-        <v>6811491</v>
+        <v>6811358</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11152,42 +11152,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130250272</v>
+        <v>130250267</v>
       </c>
       <c r="B106" t="n">
-        <v>57042</v>
+        <v>91757</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11195,10 +11190,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445468</v>
+        <v>445503</v>
       </c>
       <c r="R106" t="n">
-        <v>6811258</v>
+        <v>6811332</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11239,8 +11234,29 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11839,37 +11855,42 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130250267</v>
+        <v>130250270</v>
       </c>
       <c r="B113" t="n">
-        <v>91757</v>
+        <v>57042</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -11877,10 +11898,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445503</v>
+        <v>445426</v>
       </c>
       <c r="R113" t="n">
-        <v>6811332</v>
+        <v>6811491</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11921,29 +11942,8 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -11960,32 +11960,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130250302</v>
+        <v>130250272</v>
       </c>
       <c r="B114" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11993,7 +11993,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445239</v>
+        <v>445468</v>
       </c>
       <c r="R114" t="n">
-        <v>6811358</v>
+        <v>6811258</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250333</v>
+        <v>130250325</v>
       </c>
       <c r="B180" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445201</v>
+        <v>445457</v>
       </c>
       <c r="R180" t="n">
-        <v>6811621</v>
+        <v>6811516</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250383</v>
+        <v>130250333</v>
       </c>
       <c r="B181" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,21 +18659,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445209</v>
+        <v>445201</v>
       </c>
       <c r="R181" t="n">
-        <v>6811451</v>
+        <v>6811621</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,7 +18745,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250406</v>
+        <v>130250383</v>
       </c>
       <c r="B182" t="n">
         <v>79209</v>
@@ -18780,10 +18780,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445341</v>
+        <v>445209</v>
       </c>
       <c r="R182" t="n">
-        <v>6811293</v>
+        <v>6811451</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,7 +18842,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250377</v>
+        <v>130250406</v>
       </c>
       <c r="B183" t="n">
         <v>79209</v>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445454</v>
+        <v>445341</v>
       </c>
       <c r="R183" t="n">
-        <v>6811502</v>
+        <v>6811293</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,10 +18939,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250344</v>
+        <v>130250377</v>
       </c>
       <c r="B184" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18950,21 +18950,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18974,10 +18974,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445358</v>
+        <v>445454</v>
       </c>
       <c r="R184" t="n">
-        <v>6811433</v>
+        <v>6811502</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19036,10 +19036,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250311</v>
+        <v>130250344</v>
       </c>
       <c r="B185" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19047,42 +19047,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445333</v>
+        <v>445358</v>
       </c>
       <c r="R185" t="n">
-        <v>6811358</v>
+        <v>6811433</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19141,7 +19133,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130250284</v>
+        <v>130250311</v>
       </c>
       <c r="B186" t="n">
         <v>57849</v>
@@ -19184,10 +19176,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>445310</v>
+        <v>445333</v>
       </c>
       <c r="R186" t="n">
-        <v>6811604</v>
+        <v>6811358</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19246,10 +19238,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>130250325</v>
+        <v>130250284</v>
       </c>
       <c r="B187" t="n">
-        <v>78967</v>
+        <v>57849</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19257,34 +19249,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>445457</v>
+        <v>445310</v>
       </c>
       <c r="R187" t="n">
-        <v>6811516</v>
+        <v>6811604</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19537,10 +19537,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130250268</v>
+        <v>130250312</v>
       </c>
       <c r="B190" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -19570,7 +19570,7 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
@@ -19580,10 +19580,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>445421</v>
+        <v>445324</v>
       </c>
       <c r="R190" t="n">
-        <v>6811460</v>
+        <v>6811362</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19642,7 +19642,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130250312</v>
+        <v>130250306</v>
       </c>
       <c r="B191" t="n">
         <v>57849</v>
@@ -19675,7 +19675,7 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -19685,10 +19685,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>445324</v>
+        <v>445401</v>
       </c>
       <c r="R191" t="n">
-        <v>6811362</v>
+        <v>6811439</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19747,10 +19747,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130250306</v>
+        <v>130250268</v>
       </c>
       <c r="B192" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19758,16 +19758,16 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19790,10 +19790,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>445401</v>
+        <v>445421</v>
       </c>
       <c r="R192" t="n">
-        <v>6811439</v>
+        <v>6811460</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22270,10 +22270,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130250308</v>
+        <v>130250253</v>
       </c>
       <c r="B217" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22281,42 +22281,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>445379</v>
+        <v>445543</v>
       </c>
       <c r="R217" t="n">
-        <v>6811376</v>
+        <v>6811480</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22375,10 +22367,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130250307</v>
+        <v>130250247</v>
       </c>
       <c r="B218" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22386,42 +22378,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>445373</v>
+        <v>445188</v>
       </c>
       <c r="R218" t="n">
-        <v>6811417</v>
+        <v>6811507</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22480,10 +22464,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130250299</v>
+        <v>130250252</v>
       </c>
       <c r="B219" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22491,42 +22475,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>445206</v>
+        <v>445586</v>
       </c>
       <c r="R219" t="n">
-        <v>6811400</v>
+        <v>6811454</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22585,10 +22561,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130250253</v>
+        <v>130250348</v>
       </c>
       <c r="B220" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22596,21 +22572,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22620,10 +22596,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>445543</v>
+        <v>445329</v>
       </c>
       <c r="R220" t="n">
-        <v>6811480</v>
+        <v>6811272</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22682,10 +22658,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130250247</v>
+        <v>130250387</v>
       </c>
       <c r="B221" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22693,21 +22669,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22717,10 +22693,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>445188</v>
+        <v>445238</v>
       </c>
       <c r="R221" t="n">
-        <v>6811507</v>
+        <v>6811310</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22779,10 +22755,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130250252</v>
+        <v>130250308</v>
       </c>
       <c r="B222" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22790,34 +22766,42 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>445586</v>
+        <v>445379</v>
       </c>
       <c r="R222" t="n">
-        <v>6811454</v>
+        <v>6811376</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22876,10 +22860,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130250348</v>
+        <v>130250307</v>
       </c>
       <c r="B223" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22887,34 +22871,42 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>445329</v>
+        <v>445373</v>
       </c>
       <c r="R223" t="n">
-        <v>6811272</v>
+        <v>6811417</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22973,10 +22965,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130250387</v>
+        <v>130250299</v>
       </c>
       <c r="B224" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22984,34 +22976,42 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>445238</v>
+        <v>445206</v>
       </c>
       <c r="R224" t="n">
-        <v>6811310</v>
+        <v>6811400</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130237694</v>
+        <v>130237722</v>
       </c>
       <c r="B2" t="n">
         <v>57849</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445036</v>
+        <v>445044</v>
       </c>
       <c r="R2" t="n">
-        <v>6811601</v>
+        <v>6811281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130237722</v>
+        <v>130237694</v>
       </c>
       <c r="B3" t="n">
         <v>57849</v>
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445044</v>
+        <v>445036</v>
       </c>
       <c r="R3" t="n">
-        <v>6811281</v>
+        <v>6811601</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130237743</v>
+        <v>130237706</v>
       </c>
       <c r="B4" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +896,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445095</v>
+        <v>445093</v>
       </c>
       <c r="R4" t="n">
-        <v>6811230</v>
+        <v>6811481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237691</v>
+        <v>130237743</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,42 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444991</v>
+        <v>445095</v>
       </c>
       <c r="R5" t="n">
-        <v>6811568</v>
+        <v>6811230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237706</v>
+        <v>130237745</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,42 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445093</v>
+        <v>444954</v>
       </c>
       <c r="R6" t="n">
-        <v>6811481</v>
+        <v>6811588</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1184,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130237712</v>
+        <v>130237691</v>
       </c>
       <c r="B7" t="n">
         <v>57849</v>
@@ -1235,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445057</v>
+        <v>444991</v>
       </c>
       <c r="R7" t="n">
-        <v>6811437</v>
+        <v>6811568</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130237745</v>
+        <v>130237712</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1300,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444954</v>
+        <v>445057</v>
       </c>
       <c r="R8" t="n">
-        <v>6811588</v>
+        <v>6811437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237738</v>
+        <v>130237777</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445081</v>
+        <v>445058</v>
       </c>
       <c r="R9" t="n">
-        <v>6811319</v>
+        <v>6811322</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237777</v>
+        <v>130237749</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445058</v>
+        <v>445027</v>
       </c>
       <c r="R10" t="n">
-        <v>6811322</v>
+        <v>6811319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237749</v>
+        <v>130237724</v>
       </c>
       <c r="B11" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1599,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445027</v>
+        <v>445064</v>
       </c>
       <c r="R11" t="n">
-        <v>6811319</v>
+        <v>6811249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1790,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237724</v>
+        <v>130237692</v>
       </c>
       <c r="B13" t="n">
         <v>57849</v>
@@ -1825,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445064</v>
+        <v>445036</v>
       </c>
       <c r="R13" t="n">
-        <v>6811249</v>
+        <v>6811602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1895,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130237692</v>
+        <v>130237705</v>
       </c>
       <c r="B14" t="n">
         <v>57849</v>
@@ -1930,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445036</v>
+        <v>445092</v>
       </c>
       <c r="R14" t="n">
-        <v>6811602</v>
+        <v>6811513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237705</v>
+        <v>130237738</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,42 +2011,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445092</v>
+        <v>445081</v>
       </c>
       <c r="R15" t="n">
-        <v>6811513</v>
+        <v>6811319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130237763</v>
+        <v>130237668</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445019</v>
+        <v>445044</v>
       </c>
       <c r="R16" t="n">
-        <v>6811423</v>
+        <v>6811305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130237668</v>
+        <v>130237763</v>
       </c>
       <c r="B17" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,21 +2205,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445044</v>
+        <v>445019</v>
       </c>
       <c r="R17" t="n">
-        <v>6811305</v>
+        <v>6811423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237667</v>
+        <v>130237693</v>
       </c>
       <c r="B21" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,34 +2593,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445051</v>
+        <v>445027</v>
       </c>
       <c r="R21" t="n">
-        <v>6811326</v>
+        <v>6811603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237693</v>
+        <v>130237667</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,42 +2803,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445027</v>
+        <v>445051</v>
       </c>
       <c r="R23" t="n">
-        <v>6811603</v>
+        <v>6811326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237723</v>
+        <v>130237744</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,42 +2997,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445063</v>
+        <v>445002</v>
       </c>
       <c r="R25" t="n">
-        <v>6811256</v>
+        <v>6811503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,32 +3083,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237677</v>
+        <v>130237723</v>
       </c>
       <c r="B26" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3124,7 +3116,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3134,10 +3126,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445025</v>
+        <v>445063</v>
       </c>
       <c r="R26" t="n">
-        <v>6811296</v>
+        <v>6811256</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,45 +3188,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237744</v>
+        <v>130237677</v>
       </c>
       <c r="B27" t="n">
-        <v>78966</v>
+        <v>57042</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445002</v>
+        <v>445025</v>
       </c>
       <c r="R27" t="n">
-        <v>6811503</v>
+        <v>6811296</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130237737</v>
+        <v>130237748</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78966</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445091</v>
+        <v>445075</v>
       </c>
       <c r="R31" t="n">
-        <v>6811332</v>
+        <v>6811351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237748</v>
+        <v>130237765</v>
       </c>
       <c r="B32" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445075</v>
+        <v>445089</v>
       </c>
       <c r="R32" t="n">
-        <v>6811351</v>
+        <v>6811602</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237765</v>
+        <v>130237737</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445089</v>
+        <v>445091</v>
       </c>
       <c r="R33" t="n">
-        <v>6811602</v>
+        <v>6811332</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130237764</v>
+        <v>130237669</v>
       </c>
       <c r="B40" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4504,21 +4504,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445011</v>
+        <v>445036</v>
       </c>
       <c r="R40" t="n">
-        <v>6811436</v>
+        <v>6811260</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,45 +4590,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130237779</v>
+        <v>130237675</v>
       </c>
       <c r="B41" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445067</v>
+        <v>445000</v>
       </c>
       <c r="R41" t="n">
-        <v>6811245</v>
+        <v>6811614</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4687,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130237669</v>
+        <v>130237764</v>
       </c>
       <c r="B42" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445036</v>
+        <v>445011</v>
       </c>
       <c r="R42" t="n">
-        <v>6811260</v>
+        <v>6811436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4784,53 +4792,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237675</v>
+        <v>130237779</v>
       </c>
       <c r="B43" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445000</v>
+        <v>445067</v>
       </c>
       <c r="R43" t="n">
-        <v>6811614</v>
+        <v>6811245</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
         <v>130237750</v>
       </c>
       <c r="B45" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237660</v>
+        <v>130237708</v>
       </c>
       <c r="B48" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,34 +5298,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R48" t="n">
-        <v>6811440</v>
+        <v>6811502</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,10 +5392,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237708</v>
+        <v>130237660</v>
       </c>
       <c r="B49" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,42 +5403,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445066</v>
+        <v>444997</v>
       </c>
       <c r="R49" t="n">
-        <v>6811502</v>
+        <v>6811440</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130237695</v>
+        <v>130237776</v>
       </c>
       <c r="B54" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,42 +5916,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445073</v>
+        <v>445092</v>
       </c>
       <c r="R54" t="n">
-        <v>6811597</v>
+        <v>6811332</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,7 +6002,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130237776</v>
+        <v>130237762</v>
       </c>
       <c r="B55" t="n">
         <v>79209</v>
@@ -6045,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445092</v>
+        <v>445021</v>
       </c>
       <c r="R55" t="n">
-        <v>6811332</v>
+        <v>6811394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6204,10 +6196,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130237762</v>
+        <v>130237695</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,34 +6207,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445021</v>
+        <v>445073</v>
       </c>
       <c r="R57" t="n">
-        <v>6811394</v>
+        <v>6811597</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237725</v>
+        <v>130237760</v>
       </c>
       <c r="B58" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6312,42 +6312,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445073</v>
+        <v>445075</v>
       </c>
       <c r="R58" t="n">
-        <v>6811522</v>
+        <v>6811319</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6503,32 +6495,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130237679</v>
+        <v>130237725</v>
       </c>
       <c r="B60" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,7 +6528,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6546,10 +6538,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445036</v>
+        <v>445073</v>
       </c>
       <c r="R60" t="n">
-        <v>6811277</v>
+        <v>6811522</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,10 +6600,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237727</v>
+        <v>130237679</v>
       </c>
       <c r="B61" t="n">
-        <v>97820</v>
+        <v>57042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,34 +6611,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445095</v>
+        <v>445036</v>
       </c>
       <c r="R61" t="n">
-        <v>6811427</v>
+        <v>6811277</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130237760</v>
+        <v>130237727</v>
       </c>
       <c r="B62" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445075</v>
+        <v>445095</v>
       </c>
       <c r="R62" t="n">
-        <v>6811319</v>
+        <v>6811427</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B63" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,34 +6813,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R63" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,7 +6907,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237713</v>
+        <v>130237711</v>
       </c>
       <c r="B64" t="n">
         <v>57849</v>
@@ -6932,7 +6940,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6942,10 +6950,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445073</v>
+        <v>445054</v>
       </c>
       <c r="R64" t="n">
-        <v>6811446</v>
+        <v>6811454</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +7012,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237720</v>
+        <v>130237713</v>
       </c>
       <c r="B65" t="n">
         <v>57849</v>
@@ -7047,10 +7055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445048</v>
+        <v>445073</v>
       </c>
       <c r="R65" t="n">
-        <v>6811299</v>
+        <v>6811446</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,7 +7117,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B66" t="n">
         <v>57849</v>
@@ -7142,7 +7150,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7152,10 +7160,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R66" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7214,10 +7222,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237711</v>
+        <v>130237664</v>
       </c>
       <c r="B67" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7225,42 +7233,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445054</v>
+        <v>444968</v>
       </c>
       <c r="R67" t="n">
-        <v>6811454</v>
+        <v>6811605</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7723,7 +7723,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130237690</v>
+        <v>130237716</v>
       </c>
       <c r="B72" t="n">
         <v>57849</v>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445103</v>
+        <v>445149</v>
       </c>
       <c r="R72" t="n">
-        <v>6811320</v>
+        <v>6811433</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130237716</v>
+        <v>130237690</v>
       </c>
       <c r="B73" t="n">
         <v>57849</v>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445149</v>
+        <v>445103</v>
       </c>
       <c r="R73" t="n">
-        <v>6811433</v>
+        <v>6811320</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8446,10 +8446,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130237700</v>
+        <v>130237747</v>
       </c>
       <c r="B79" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8457,42 +8457,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445131</v>
+        <v>445113</v>
       </c>
       <c r="R79" t="n">
-        <v>6811529</v>
+        <v>6811388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8551,10 +8543,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130237747</v>
+        <v>130237700</v>
       </c>
       <c r="B80" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8562,34 +8554,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445113</v>
+        <v>445131</v>
       </c>
       <c r="R80" t="n">
-        <v>6811388</v>
+        <v>6811529</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8648,10 +8648,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130237703</v>
+        <v>130237746</v>
       </c>
       <c r="B81" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8659,42 +8659,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445132</v>
+        <v>445153</v>
       </c>
       <c r="R81" t="n">
-        <v>6811535</v>
+        <v>6811549</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8753,10 +8745,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130237746</v>
+        <v>130237771</v>
       </c>
       <c r="B82" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8764,21 +8756,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8788,10 +8780,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445153</v>
+        <v>445159</v>
       </c>
       <c r="R82" t="n">
-        <v>6811549</v>
+        <v>6811562</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8850,10 +8842,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130237771</v>
+        <v>130237703</v>
       </c>
       <c r="B83" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8861,34 +8853,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445159</v>
+        <v>445132</v>
       </c>
       <c r="R83" t="n">
-        <v>6811562</v>
+        <v>6811535</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130237768</v>
+        <v>130237702</v>
       </c>
       <c r="B85" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9055,34 +9055,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445145</v>
+        <v>445137</v>
       </c>
       <c r="R85" t="n">
-        <v>6811638</v>
+        <v>6811505</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9141,10 +9149,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130237702</v>
+        <v>130237768</v>
       </c>
       <c r="B86" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9152,42 +9160,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445137</v>
+        <v>445145</v>
       </c>
       <c r="R86" t="n">
-        <v>6811505</v>
+        <v>6811638</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9744,7 +9744,7 @@
         <v>130237726</v>
       </c>
       <c r="B92" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237718</v>
+        <v>130237758</v>
       </c>
       <c r="B94" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9951,42 +9951,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445116</v>
+        <v>445101</v>
       </c>
       <c r="R94" t="n">
-        <v>6811382</v>
+        <v>6811246</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10150,10 +10142,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237758</v>
+        <v>130237718</v>
       </c>
       <c r="B96" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10161,34 +10153,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445101</v>
+        <v>445116</v>
       </c>
       <c r="R96" t="n">
-        <v>6811246</v>
+        <v>6811382</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10344,7 +10344,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130250379</v>
+        <v>130250364</v>
       </c>
       <c r="B98" t="n">
         <v>79209</v>
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445369</v>
+        <v>445309</v>
       </c>
       <c r="R98" t="n">
-        <v>6811508</v>
+        <v>6811605</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10441,10 +10441,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130250262</v>
+        <v>130250379</v>
       </c>
       <c r="B99" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10452,21 +10452,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445333</v>
+        <v>445369</v>
       </c>
       <c r="R99" t="n">
-        <v>6811312</v>
+        <v>6811508</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10635,10 +10635,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130250364</v>
+        <v>130250294</v>
       </c>
       <c r="B101" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10646,34 +10646,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445309</v>
+        <v>445280</v>
       </c>
       <c r="R101" t="n">
-        <v>6811605</v>
+        <v>6811472</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10732,10 +10740,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130250304</v>
+        <v>130250262</v>
       </c>
       <c r="B102" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10743,42 +10751,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445494</v>
+        <v>445333</v>
       </c>
       <c r="R102" t="n">
-        <v>6811338</v>
+        <v>6811312</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10837,7 +10837,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130250309</v>
+        <v>130250304</v>
       </c>
       <c r="B103" t="n">
         <v>57849</v>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445368</v>
+        <v>445494</v>
       </c>
       <c r="R103" t="n">
-        <v>6811354</v>
+        <v>6811338</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130250294</v>
+        <v>130250309</v>
       </c>
       <c r="B104" t="n">
         <v>57849</v>
@@ -10985,10 +10985,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445280</v>
+        <v>445368</v>
       </c>
       <c r="R104" t="n">
-        <v>6811472</v>
+        <v>6811354</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11047,10 +11047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250302</v>
+        <v>130250343</v>
       </c>
       <c r="B105" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,42 +11058,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445239</v>
+        <v>445471</v>
       </c>
       <c r="R105" t="n">
-        <v>6811358</v>
+        <v>6811288</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11152,10 +11144,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130250267</v>
+        <v>130250261</v>
       </c>
       <c r="B106" t="n">
-        <v>91757</v>
+        <v>79828</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11163,37 +11155,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445503</v>
+        <v>445339</v>
       </c>
       <c r="R106" t="n">
-        <v>6811332</v>
+        <v>6811359</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11234,29 +11223,8 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11273,10 +11241,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130250261</v>
+        <v>130250373</v>
       </c>
       <c r="B107" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11284,21 +11252,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11308,10 +11276,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445339</v>
+        <v>445554</v>
       </c>
       <c r="R107" t="n">
-        <v>6811359</v>
+        <v>6811464</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11370,10 +11338,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130250402</v>
+        <v>130250302</v>
       </c>
       <c r="B108" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11381,34 +11349,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445364</v>
+        <v>445239</v>
       </c>
       <c r="R108" t="n">
-        <v>6811345</v>
+        <v>6811358</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11467,45 +11443,53 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130250343</v>
+        <v>130250270</v>
       </c>
       <c r="B109" t="n">
-        <v>78966</v>
+        <v>57042</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445471</v>
+        <v>445426</v>
       </c>
       <c r="R109" t="n">
-        <v>6811288</v>
+        <v>6811491</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11564,45 +11548,53 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130250409</v>
+        <v>130250272</v>
       </c>
       <c r="B110" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445294</v>
+        <v>445468</v>
       </c>
       <c r="R110" t="n">
-        <v>6811231</v>
+        <v>6811258</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11758,7 +11750,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130250373</v>
+        <v>130250409</v>
       </c>
       <c r="B112" t="n">
         <v>79209</v>
@@ -11793,10 +11785,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445554</v>
+        <v>445294</v>
       </c>
       <c r="R112" t="n">
-        <v>6811464</v>
+        <v>6811231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11855,53 +11847,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130250270</v>
+        <v>130250402</v>
       </c>
       <c r="B113" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445426</v>
+        <v>445364</v>
       </c>
       <c r="R113" t="n">
-        <v>6811491</v>
+        <v>6811345</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11960,42 +11944,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130250272</v>
+        <v>130250267</v>
       </c>
       <c r="B114" t="n">
-        <v>57042</v>
+        <v>91758</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12003,10 +11982,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445468</v>
+        <v>445503</v>
       </c>
       <c r="R114" t="n">
-        <v>6811258</v>
+        <v>6811332</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12047,8 +12026,29 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12065,10 +12065,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130250345</v>
+        <v>130250296</v>
       </c>
       <c r="B115" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12076,34 +12076,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445339</v>
+        <v>445240</v>
       </c>
       <c r="R115" t="n">
-        <v>6811359</v>
+        <v>6811502</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12162,10 +12170,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130250339</v>
+        <v>130250313</v>
       </c>
       <c r="B116" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12173,34 +12181,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445457</v>
+        <v>445334</v>
       </c>
       <c r="R116" t="n">
-        <v>6811516</v>
+        <v>6811325</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12259,10 +12275,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130250385</v>
+        <v>130250339</v>
       </c>
       <c r="B117" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12270,21 +12286,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12294,10 +12310,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445210</v>
+        <v>445457</v>
       </c>
       <c r="R117" t="n">
-        <v>6811346</v>
+        <v>6811516</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12356,10 +12372,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130250313</v>
+        <v>130250345</v>
       </c>
       <c r="B118" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12367,42 +12383,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445334</v>
+        <v>445339</v>
       </c>
       <c r="R118" t="n">
-        <v>6811325</v>
+        <v>6811359</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12461,10 +12469,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130250296</v>
+        <v>130250385</v>
       </c>
       <c r="B119" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12472,42 +12480,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445240</v>
+        <v>445210</v>
       </c>
       <c r="R119" t="n">
-        <v>6811502</v>
+        <v>6811346</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,7 +12566,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250394</v>
+        <v>130250357</v>
       </c>
       <c r="B120" t="n">
         <v>79209</v>
@@ -12595,19 +12595,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445495</v>
+        <v>445165</v>
       </c>
       <c r="R120" t="n">
-        <v>6811385</v>
+        <v>6811302</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12648,7 +12645,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12667,10 +12663,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250404</v>
+        <v>130250289</v>
       </c>
       <c r="B121" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12678,34 +12674,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445330</v>
+        <v>445468</v>
       </c>
       <c r="R121" t="n">
-        <v>6811333</v>
+        <v>6811500</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12764,10 +12768,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250399</v>
+        <v>130250314</v>
       </c>
       <c r="B122" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12775,34 +12779,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445416</v>
+        <v>445322</v>
       </c>
       <c r="R122" t="n">
-        <v>6811445</v>
+        <v>6811309</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12861,10 +12873,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250338</v>
+        <v>130250315</v>
       </c>
       <c r="B123" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12872,34 +12884,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445492</v>
+        <v>445317</v>
       </c>
       <c r="R123" t="n">
-        <v>6811520</v>
+        <v>6811271</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12958,10 +12978,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250360</v>
+        <v>130250293</v>
       </c>
       <c r="B124" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12969,34 +12989,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445194</v>
+        <v>445303</v>
       </c>
       <c r="R124" t="n">
-        <v>6811530</v>
+        <v>6811490</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13055,10 +13083,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250259</v>
+        <v>130250338</v>
       </c>
       <c r="B125" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13066,21 +13094,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13118,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445441</v>
+        <v>445492</v>
       </c>
       <c r="R125" t="n">
-        <v>6811433</v>
+        <v>6811520</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13152,10 +13180,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250357</v>
+        <v>130250259</v>
       </c>
       <c r="B126" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13163,21 +13191,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13187,10 +13215,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445165</v>
+        <v>445441</v>
       </c>
       <c r="R126" t="n">
-        <v>6811302</v>
+        <v>6811433</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13249,10 +13277,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250289</v>
+        <v>130250394</v>
       </c>
       <c r="B127" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13260,31 +13288,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13292,10 +13315,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445468</v>
+        <v>445495</v>
       </c>
       <c r="R127" t="n">
-        <v>6811500</v>
+        <v>6811385</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13336,6 +13359,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13354,10 +13378,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250314</v>
+        <v>130250404</v>
       </c>
       <c r="B128" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13365,42 +13389,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445322</v>
+        <v>445330</v>
       </c>
       <c r="R128" t="n">
-        <v>6811309</v>
+        <v>6811333</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13459,10 +13475,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250293</v>
+        <v>130250360</v>
       </c>
       <c r="B129" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13470,42 +13486,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445303</v>
+        <v>445194</v>
       </c>
       <c r="R129" t="n">
-        <v>6811490</v>
+        <v>6811530</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13564,10 +13572,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250315</v>
+        <v>130250399</v>
       </c>
       <c r="B130" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13575,42 +13583,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445317</v>
+        <v>445416</v>
       </c>
       <c r="R130" t="n">
-        <v>6811271</v>
+        <v>6811445</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130250255</v>
+        <v>130250321</v>
       </c>
       <c r="B131" t="n">
-        <v>79828</v>
+        <v>78967</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13680,21 +13680,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13704,10 +13704,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>445480</v>
+        <v>445326</v>
       </c>
       <c r="R131" t="n">
-        <v>6811273</v>
+        <v>6811613</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130250321</v>
+        <v>130250255</v>
       </c>
       <c r="B132" t="n">
-        <v>78967</v>
+        <v>79828</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13777,21 +13777,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>445326</v>
+        <v>445480</v>
       </c>
       <c r="R132" t="n">
-        <v>6811613</v>
+        <v>6811273</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13863,10 +13863,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130250361</v>
+        <v>130250251</v>
       </c>
       <c r="B133" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13874,21 +13874,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13898,10 +13898,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>445228</v>
+        <v>445494</v>
       </c>
       <c r="R133" t="n">
-        <v>6811593</v>
+        <v>6811520</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13960,10 +13960,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130250251</v>
+        <v>130250374</v>
       </c>
       <c r="B134" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13971,21 +13971,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>445494</v>
+        <v>445536</v>
       </c>
       <c r="R134" t="n">
-        <v>6811520</v>
+        <v>6811476</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14057,7 +14057,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130250374</v>
+        <v>130250361</v>
       </c>
       <c r="B135" t="n">
         <v>79209</v>
@@ -14092,10 +14092,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>445536</v>
+        <v>445228</v>
       </c>
       <c r="R135" t="n">
-        <v>6811476</v>
+        <v>6811593</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130250369</v>
+        <v>130250390</v>
       </c>
       <c r="B136" t="n">
         <v>79209</v>
@@ -14189,10 +14189,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>445518</v>
+        <v>445492</v>
       </c>
       <c r="R136" t="n">
-        <v>6811539</v>
+        <v>6811299</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14251,7 +14251,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130250356</v>
+        <v>130250369</v>
       </c>
       <c r="B137" t="n">
         <v>79209</v>
@@ -14286,10 +14286,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>445227</v>
+        <v>445518</v>
       </c>
       <c r="R137" t="n">
-        <v>6811254</v>
+        <v>6811539</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14348,7 +14348,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130250390</v>
+        <v>130250356</v>
       </c>
       <c r="B138" t="n">
         <v>79209</v>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>445492</v>
+        <v>445227</v>
       </c>
       <c r="R138" t="n">
-        <v>6811299</v>
+        <v>6811254</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14861,10 +14861,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250362</v>
+        <v>130250303</v>
       </c>
       <c r="B143" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14872,34 +14872,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445218</v>
+        <v>445389</v>
       </c>
       <c r="R143" t="n">
-        <v>6811594</v>
+        <v>6811264</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14958,32 +14966,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250297</v>
+        <v>130250271</v>
       </c>
       <c r="B144" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14991,7 +14999,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -15001,10 +15009,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445239</v>
+        <v>445375</v>
       </c>
       <c r="R144" t="n">
-        <v>6811474</v>
+        <v>6811502</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15063,10 +15071,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250292</v>
+        <v>130250362</v>
       </c>
       <c r="B145" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15074,42 +15082,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445384</v>
+        <v>445218</v>
       </c>
       <c r="R145" t="n">
-        <v>6811490</v>
+        <v>6811594</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15168,7 +15168,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250303</v>
+        <v>130250297</v>
       </c>
       <c r="B146" t="n">
         <v>57849</v>
@@ -15211,10 +15211,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445389</v>
+        <v>445239</v>
       </c>
       <c r="R146" t="n">
-        <v>6811264</v>
+        <v>6811474</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15273,32 +15273,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250274</v>
+        <v>130250292</v>
       </c>
       <c r="B147" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15306,7 +15306,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -15316,10 +15316,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445376</v>
+        <v>445384</v>
       </c>
       <c r="R147" t="n">
-        <v>6811389</v>
+        <v>6811490</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15378,53 +15378,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250271</v>
+        <v>130250323</v>
       </c>
       <c r="B148" t="n">
-        <v>57042</v>
+        <v>78967</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445375</v>
+        <v>445371</v>
       </c>
       <c r="R148" t="n">
-        <v>6811502</v>
+        <v>6811594</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15483,7 +15475,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250323</v>
+        <v>130250328</v>
       </c>
       <c r="B149" t="n">
         <v>78967</v>
@@ -15518,10 +15510,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445371</v>
+        <v>445329</v>
       </c>
       <c r="R149" t="n">
-        <v>6811594</v>
+        <v>6811272</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15580,10 +15572,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130250328</v>
+        <v>130250266</v>
       </c>
       <c r="B150" t="n">
-        <v>78967</v>
+        <v>79799</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15591,21 +15583,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15615,10 +15607,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>445329</v>
+        <v>445580</v>
       </c>
       <c r="R150" t="n">
-        <v>6811272</v>
+        <v>6811443</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15677,45 +15669,53 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250266</v>
+        <v>130250274</v>
       </c>
       <c r="B151" t="n">
-        <v>79799</v>
+        <v>57042</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445580</v>
+        <v>445376</v>
       </c>
       <c r="R151" t="n">
-        <v>6811443</v>
+        <v>6811389</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15774,49 +15774,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130250319</v>
+        <v>130250335</v>
       </c>
       <c r="B152" t="n">
-        <v>97826</v>
+        <v>78966</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>445554</v>
+        <v>445372</v>
       </c>
       <c r="R152" t="n">
-        <v>6811457</v>
+        <v>6811595</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15857,7 +15853,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15876,10 +15871,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130250326</v>
+        <v>130250341</v>
       </c>
       <c r="B153" t="n">
-        <v>78967</v>
+        <v>78966</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15887,21 +15882,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15911,10 +15906,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>445235</v>
+        <v>445383</v>
       </c>
       <c r="R153" t="n">
-        <v>6811325</v>
+        <v>6811286</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15973,10 +15968,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130250329</v>
+        <v>130250336</v>
       </c>
       <c r="B154" t="n">
-        <v>78967</v>
+        <v>78966</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15984,21 +15979,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16008,10 +16003,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>445323</v>
+        <v>445413</v>
       </c>
       <c r="R154" t="n">
-        <v>6811270</v>
+        <v>6811568</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16070,10 +16065,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130250335</v>
+        <v>130250381</v>
       </c>
       <c r="B155" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16081,21 +16076,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16105,10 +16100,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>445372</v>
+        <v>445351</v>
       </c>
       <c r="R155" t="n">
-        <v>6811595</v>
+        <v>6811495</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16167,10 +16162,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250341</v>
+        <v>130250326</v>
       </c>
       <c r="B156" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16178,21 +16173,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16202,10 +16197,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445383</v>
+        <v>445235</v>
       </c>
       <c r="R156" t="n">
-        <v>6811286</v>
+        <v>6811325</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16264,10 +16259,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130250336</v>
+        <v>130250329</v>
       </c>
       <c r="B157" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16275,21 +16270,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16299,10 +16294,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445413</v>
+        <v>445323</v>
       </c>
       <c r="R157" t="n">
-        <v>6811568</v>
+        <v>6811270</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16361,10 +16356,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130250381</v>
+        <v>130250317</v>
       </c>
       <c r="B158" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16372,34 +16367,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445351</v>
+        <v>445487</v>
       </c>
       <c r="R158" t="n">
-        <v>6811495</v>
+        <v>6811335</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16458,32 +16461,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130250317</v>
+        <v>130250276</v>
       </c>
       <c r="B159" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16491,7 +16494,7 @@
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
@@ -16501,10 +16504,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445487</v>
+        <v>445328</v>
       </c>
       <c r="R159" t="n">
-        <v>6811335</v>
+        <v>6811392</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16668,10 +16671,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250276</v>
+        <v>130250319</v>
       </c>
       <c r="B161" t="n">
-        <v>57042</v>
+        <v>97827</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16679,31 +16682,27 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -16711,10 +16710,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445328</v>
+        <v>445554</v>
       </c>
       <c r="R161" t="n">
-        <v>6811392</v>
+        <v>6811457</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16755,6 +16754,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16773,7 +16773,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130250398</v>
+        <v>130250391</v>
       </c>
       <c r="B162" t="n">
         <v>79209</v>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>445426</v>
+        <v>445499</v>
       </c>
       <c r="R162" t="n">
-        <v>6811434</v>
+        <v>6811328</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16870,7 +16870,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130250391</v>
+        <v>130250398</v>
       </c>
       <c r="B163" t="n">
         <v>79209</v>
@@ -16905,10 +16905,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>445499</v>
+        <v>445426</v>
       </c>
       <c r="R163" t="n">
-        <v>6811328</v>
+        <v>6811434</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16967,10 +16967,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130250340</v>
+        <v>130250371</v>
       </c>
       <c r="B164" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16978,21 +16978,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>445366</v>
+        <v>445588</v>
       </c>
       <c r="R164" t="n">
-        <v>6811298</v>
+        <v>6811455</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17064,10 +17064,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130250248</v>
+        <v>130250279</v>
       </c>
       <c r="B165" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17075,34 +17075,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>445243</v>
+        <v>445165</v>
       </c>
       <c r="R165" t="n">
-        <v>6811593</v>
+        <v>6811426</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17161,10 +17169,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130250371</v>
+        <v>130250287</v>
       </c>
       <c r="B166" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17172,34 +17180,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>445588</v>
+        <v>445575</v>
       </c>
       <c r="R166" t="n">
-        <v>6811455</v>
+        <v>6811437</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17258,10 +17274,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130250342</v>
+        <v>130250282</v>
       </c>
       <c r="B167" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17269,34 +17285,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>445390</v>
+        <v>445213</v>
       </c>
       <c r="R167" t="n">
-        <v>6811275</v>
+        <v>6811666</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17355,10 +17379,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130250279</v>
+        <v>130250342</v>
       </c>
       <c r="B168" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17366,42 +17390,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>445165</v>
+        <v>445390</v>
       </c>
       <c r="R168" t="n">
-        <v>6811426</v>
+        <v>6811275</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17460,10 +17476,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130250287</v>
+        <v>130250248</v>
       </c>
       <c r="B169" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17471,42 +17487,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>445575</v>
+        <v>445243</v>
       </c>
       <c r="R169" t="n">
-        <v>6811437</v>
+        <v>6811593</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17565,10 +17573,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130250282</v>
+        <v>130250340</v>
       </c>
       <c r="B170" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17576,42 +17584,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>445213</v>
+        <v>445366</v>
       </c>
       <c r="R170" t="n">
-        <v>6811666</v>
+        <v>6811298</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17670,10 +17670,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130250265</v>
+        <v>130250347</v>
       </c>
       <c r="B171" t="n">
-        <v>79799</v>
+        <v>78966</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17681,21 +17681,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17705,10 +17705,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>445586</v>
+        <v>445334</v>
       </c>
       <c r="R171" t="n">
-        <v>6811454</v>
+        <v>6811304</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17767,32 +17767,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130250318</v>
+        <v>130250260</v>
       </c>
       <c r="B172" t="n">
-        <v>97820</v>
+        <v>79828</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17802,10 +17802,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>445180</v>
+        <v>445425</v>
       </c>
       <c r="R172" t="n">
-        <v>6811418</v>
+        <v>6811413</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17864,10 +17864,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130250388</v>
+        <v>130250346</v>
       </c>
       <c r="B173" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17875,21 +17875,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17899,10 +17899,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>445362</v>
+        <v>445322</v>
       </c>
       <c r="R173" t="n">
-        <v>6811289</v>
+        <v>6811363</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130250347</v>
+        <v>130250388</v>
       </c>
       <c r="B174" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>445334</v>
+        <v>445362</v>
       </c>
       <c r="R174" t="n">
-        <v>6811304</v>
+        <v>6811289</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18155,10 +18155,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130250346</v>
+        <v>130250396</v>
       </c>
       <c r="B176" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18166,21 +18166,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18190,10 +18190,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>445322</v>
+        <v>445480</v>
       </c>
       <c r="R176" t="n">
-        <v>6811363</v>
+        <v>6811420</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18252,10 +18252,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250260</v>
+        <v>130250290</v>
       </c>
       <c r="B177" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18263,34 +18263,42 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445425</v>
+        <v>445457</v>
       </c>
       <c r="R177" t="n">
-        <v>6811413</v>
+        <v>6811507</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18349,32 +18357,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130250396</v>
+        <v>130250318</v>
       </c>
       <c r="B178" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18384,10 +18392,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>445480</v>
+        <v>445180</v>
       </c>
       <c r="R178" t="n">
-        <v>6811420</v>
+        <v>6811418</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18446,10 +18454,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130250290</v>
+        <v>130250265</v>
       </c>
       <c r="B179" t="n">
-        <v>57849</v>
+        <v>79799</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18457,42 +18465,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>445457</v>
+        <v>445586</v>
       </c>
       <c r="R179" t="n">
-        <v>6811507</v>
+        <v>6811454</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250333</v>
+        <v>130250383</v>
       </c>
       <c r="B181" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,21 +18659,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445201</v>
+        <v>445209</v>
       </c>
       <c r="R181" t="n">
-        <v>6811621</v>
+        <v>6811451</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,7 +18745,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250383</v>
+        <v>130250406</v>
       </c>
       <c r="B182" t="n">
         <v>79209</v>
@@ -18780,10 +18780,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445209</v>
+        <v>445341</v>
       </c>
       <c r="R182" t="n">
-        <v>6811451</v>
+        <v>6811293</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,7 +18842,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250406</v>
+        <v>130250377</v>
       </c>
       <c r="B183" t="n">
         <v>79209</v>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445341</v>
+        <v>445454</v>
       </c>
       <c r="R183" t="n">
-        <v>6811293</v>
+        <v>6811502</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,10 +18939,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250377</v>
+        <v>130250284</v>
       </c>
       <c r="B184" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18950,34 +18950,42 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445454</v>
+        <v>445310</v>
       </c>
       <c r="R184" t="n">
-        <v>6811502</v>
+        <v>6811604</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19036,7 +19044,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250344</v>
+        <v>130250333</v>
       </c>
       <c r="B185" t="n">
         <v>78966</v>
@@ -19071,10 +19079,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445358</v>
+        <v>445201</v>
       </c>
       <c r="R185" t="n">
-        <v>6811433</v>
+        <v>6811621</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19133,10 +19141,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130250311</v>
+        <v>130250344</v>
       </c>
       <c r="B186" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19144,42 +19152,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>445333</v>
+        <v>445358</v>
       </c>
       <c r="R186" t="n">
-        <v>6811358</v>
+        <v>6811433</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>130250284</v>
+        <v>130250311</v>
       </c>
       <c r="B187" t="n">
         <v>57849</v>
@@ -19281,10 +19281,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>445310</v>
+        <v>445333</v>
       </c>
       <c r="R187" t="n">
-        <v>6811604</v>
+        <v>6811358</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19343,10 +19343,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>130250363</v>
+        <v>130250257</v>
       </c>
       <c r="B188" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19354,21 +19354,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19378,10 +19378,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>445229</v>
+        <v>445474</v>
       </c>
       <c r="R188" t="n">
-        <v>6811687</v>
+        <v>6811433</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19440,10 +19440,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>130250257</v>
+        <v>130250363</v>
       </c>
       <c r="B189" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19451,21 +19451,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>445474</v>
+        <v>445229</v>
       </c>
       <c r="R189" t="n">
-        <v>6811433</v>
+        <v>6811687</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130250300</v>
+        <v>130250256</v>
       </c>
       <c r="B194" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19970,42 +19970,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445219</v>
+        <v>445484</v>
       </c>
       <c r="R194" t="n">
-        <v>6811344</v>
+        <v>6811291</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20064,10 +20056,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250291</v>
+        <v>130250250</v>
       </c>
       <c r="B195" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20075,42 +20067,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445385</v>
+        <v>445248</v>
       </c>
       <c r="R195" t="n">
-        <v>6811504</v>
+        <v>6811642</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20169,10 +20153,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250281</v>
+        <v>130250370</v>
       </c>
       <c r="B196" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20180,42 +20164,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445205</v>
+        <v>445542</v>
       </c>
       <c r="R196" t="n">
-        <v>6811619</v>
+        <v>6811532</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20274,53 +20250,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250355</v>
+        <v>130250395</v>
       </c>
       <c r="B197" t="n">
-        <v>57844</v>
+        <v>79209</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445443</v>
+        <v>445507</v>
       </c>
       <c r="R197" t="n">
-        <v>6811494</v>
+        <v>6811412</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20379,10 +20347,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250327</v>
+        <v>130250386</v>
       </c>
       <c r="B198" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20390,21 +20358,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20414,10 +20382,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445390</v>
+        <v>445226</v>
       </c>
       <c r="R198" t="n">
-        <v>6811275</v>
+        <v>6811348</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20476,45 +20444,53 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250370</v>
+        <v>130250277</v>
       </c>
       <c r="B199" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445542</v>
+        <v>445202</v>
       </c>
       <c r="R199" t="n">
-        <v>6811532</v>
+        <v>6811655</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20573,45 +20549,53 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250250</v>
+        <v>130250355</v>
       </c>
       <c r="B200" t="n">
-        <v>79828</v>
+        <v>57844</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6453</v>
+        <v>100110</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445248</v>
+        <v>445443</v>
       </c>
       <c r="R200" t="n">
-        <v>6811642</v>
+        <v>6811494</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20670,10 +20654,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250386</v>
+        <v>130250327</v>
       </c>
       <c r="B201" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20681,21 +20665,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20705,10 +20689,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445226</v>
+        <v>445390</v>
       </c>
       <c r="R201" t="n">
-        <v>6811348</v>
+        <v>6811275</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20767,10 +20751,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250256</v>
+        <v>130250300</v>
       </c>
       <c r="B202" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20778,34 +20762,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445484</v>
+        <v>445219</v>
       </c>
       <c r="R202" t="n">
-        <v>6811291</v>
+        <v>6811344</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20864,10 +20856,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250395</v>
+        <v>130250298</v>
       </c>
       <c r="B203" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20875,34 +20867,42 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445507</v>
+        <v>445232</v>
       </c>
       <c r="R203" t="n">
-        <v>6811412</v>
+        <v>6811448</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20961,32 +20961,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250277</v>
+        <v>130250291</v>
       </c>
       <c r="B204" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20994,7 +20994,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -21004,10 +21004,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445202</v>
+        <v>445385</v>
       </c>
       <c r="R204" t="n">
-        <v>6811655</v>
+        <v>6811504</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21066,7 +21066,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130250298</v>
+        <v>130250281</v>
       </c>
       <c r="B205" t="n">
         <v>57849</v>
@@ -21109,10 +21109,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>445232</v>
+        <v>445205</v>
       </c>
       <c r="R205" t="n">
-        <v>6811448</v>
+        <v>6811619</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250367</v>
+        <v>130250264</v>
       </c>
       <c r="B206" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,21 +21182,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21206,10 +21206,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445376</v>
+        <v>445315</v>
       </c>
       <c r="R206" t="n">
-        <v>6811581</v>
+        <v>6811230</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21268,7 +21268,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250258</v>
+        <v>130250249</v>
       </c>
       <c r="B207" t="n">
         <v>79828</v>
@@ -21303,10 +21303,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445470</v>
+        <v>445200</v>
       </c>
       <c r="R207" t="n">
-        <v>6811435</v>
+        <v>6811598</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21365,7 +21365,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250249</v>
+        <v>130250258</v>
       </c>
       <c r="B208" t="n">
         <v>79828</v>
@@ -21400,10 +21400,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445200</v>
+        <v>445470</v>
       </c>
       <c r="R208" t="n">
-        <v>6811598</v>
+        <v>6811435</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21559,10 +21559,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250392</v>
+        <v>130250280</v>
       </c>
       <c r="B210" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21570,34 +21570,42 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445487</v>
+        <v>445179</v>
       </c>
       <c r="R210" t="n">
-        <v>6811345</v>
+        <v>6811467</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21656,10 +21664,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250264</v>
+        <v>130250283</v>
       </c>
       <c r="B211" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21667,34 +21675,42 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445315</v>
+        <v>445303</v>
       </c>
       <c r="R211" t="n">
-        <v>6811230</v>
+        <v>6811621</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21753,7 +21769,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250389</v>
+        <v>130250392</v>
       </c>
       <c r="B212" t="n">
         <v>79209</v>
@@ -21788,10 +21804,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445483</v>
+        <v>445487</v>
       </c>
       <c r="R212" t="n">
-        <v>6811288</v>
+        <v>6811345</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21850,10 +21866,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250280</v>
+        <v>130250389</v>
       </c>
       <c r="B213" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21861,42 +21877,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445179</v>
+        <v>445483</v>
       </c>
       <c r="R213" t="n">
-        <v>6811467</v>
+        <v>6811288</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21955,10 +21963,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250310</v>
+        <v>130250367</v>
       </c>
       <c r="B214" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21966,42 +21974,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445339</v>
+        <v>445376</v>
       </c>
       <c r="R214" t="n">
-        <v>6811359</v>
+        <v>6811581</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B215" t="n">
         <v>57849</v>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R215" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22165,7 +22165,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250283</v>
+        <v>130250305</v>
       </c>
       <c r="B216" t="n">
         <v>57849</v>
@@ -22208,10 +22208,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445303</v>
+        <v>445448</v>
       </c>
       <c r="R216" t="n">
-        <v>6811621</v>
+        <v>6811432</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22270,10 +22270,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130250253</v>
+        <v>130250387</v>
       </c>
       <c r="B217" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22281,21 +22281,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22305,10 +22305,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>445543</v>
+        <v>445238</v>
       </c>
       <c r="R217" t="n">
-        <v>6811480</v>
+        <v>6811310</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22367,7 +22367,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130250247</v>
+        <v>130250252</v>
       </c>
       <c r="B218" t="n">
         <v>79828</v>
@@ -22402,10 +22402,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>445188</v>
+        <v>445586</v>
       </c>
       <c r="R218" t="n">
-        <v>6811507</v>
+        <v>6811454</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22464,7 +22464,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130250252</v>
+        <v>130250247</v>
       </c>
       <c r="B219" t="n">
         <v>79828</v>
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>445586</v>
+        <v>445188</v>
       </c>
       <c r="R219" t="n">
-        <v>6811454</v>
+        <v>6811507</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22561,10 +22561,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130250348</v>
+        <v>130250253</v>
       </c>
       <c r="B220" t="n">
-        <v>78966</v>
+        <v>79828</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22572,21 +22572,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>445329</v>
+        <v>445543</v>
       </c>
       <c r="R220" t="n">
-        <v>6811272</v>
+        <v>6811480</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22658,10 +22658,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130250387</v>
+        <v>130250348</v>
       </c>
       <c r="B221" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22669,21 +22669,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22693,10 +22693,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>445238</v>
+        <v>445329</v>
       </c>
       <c r="R221" t="n">
-        <v>6811310</v>
+        <v>6811272</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23070,7 +23070,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130250372</v>
+        <v>130250400</v>
       </c>
       <c r="B225" t="n">
         <v>79209</v>
@@ -23099,19 +23099,16 @@
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>445578</v>
+        <v>445401</v>
       </c>
       <c r="R225" t="n">
-        <v>6811455</v>
+        <v>6811451</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23152,7 +23149,6 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
-      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
@@ -23171,7 +23167,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130250400</v>
+        <v>130250358</v>
       </c>
       <c r="B226" t="n">
         <v>79209</v>
@@ -23206,10 +23202,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>445401</v>
+        <v>445154</v>
       </c>
       <c r="R226" t="n">
-        <v>6811451</v>
+        <v>6811359</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23268,7 +23264,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130250358</v>
+        <v>130250382</v>
       </c>
       <c r="B227" t="n">
         <v>79209</v>
@@ -23303,10 +23299,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>445154</v>
+        <v>445218</v>
       </c>
       <c r="R227" t="n">
-        <v>6811359</v>
+        <v>6811435</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23365,10 +23361,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130250263</v>
+        <v>130250372</v>
       </c>
       <c r="B228" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23376,34 +23372,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>445321</v>
+        <v>445578</v>
       </c>
       <c r="R228" t="n">
-        <v>6811263</v>
+        <v>6811455</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23444,6 +23443,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23462,10 +23462,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130250382</v>
+        <v>130250285</v>
       </c>
       <c r="B229" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23473,34 +23473,42 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>445218</v>
+        <v>445439</v>
       </c>
       <c r="R229" t="n">
-        <v>6811435</v>
+        <v>6811539</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23559,10 +23567,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130250334</v>
+        <v>130250263</v>
       </c>
       <c r="B230" t="n">
-        <v>78966</v>
+        <v>79828</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23570,21 +23578,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23594,10 +23602,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>445266</v>
+        <v>445321</v>
       </c>
       <c r="R230" t="n">
-        <v>6811642</v>
+        <v>6811263</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23656,10 +23664,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>130250285</v>
+        <v>130250334</v>
       </c>
       <c r="B231" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23667,42 +23675,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>445439</v>
+        <v>445266</v>
       </c>
       <c r="R231" t="n">
-        <v>6811539</v>
+        <v>6811642</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130250246</v>
+        <v>130250324</v>
       </c>
       <c r="B232" t="n">
-        <v>79828</v>
+        <v>78967</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23772,21 +23772,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23796,10 +23796,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>445182</v>
+        <v>445465</v>
       </c>
       <c r="R232" t="n">
-        <v>6811329</v>
+        <v>6811533</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23858,7 +23858,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130250380</v>
+        <v>130250397</v>
       </c>
       <c r="B233" t="n">
         <v>79209</v>
@@ -23893,10 +23893,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>445369</v>
+        <v>445441</v>
       </c>
       <c r="R233" t="n">
-        <v>6811486</v>
+        <v>6811411</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23955,10 +23955,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130250393</v>
+        <v>130250288</v>
       </c>
       <c r="B234" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23966,34 +23966,42 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445477</v>
+        <v>445564</v>
       </c>
       <c r="R234" t="n">
-        <v>6811356</v>
+        <v>6811446</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24052,10 +24060,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130250405</v>
+        <v>130250301</v>
       </c>
       <c r="B235" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24063,34 +24071,42 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>445324</v>
+        <v>445222</v>
       </c>
       <c r="R235" t="n">
-        <v>6811291</v>
+        <v>6811352</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24149,10 +24165,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130250397</v>
+        <v>130250246</v>
       </c>
       <c r="B236" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24160,21 +24176,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24184,10 +24200,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>445441</v>
+        <v>445182</v>
       </c>
       <c r="R236" t="n">
-        <v>6811411</v>
+        <v>6811329</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24246,7 +24262,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130250408</v>
+        <v>130250393</v>
       </c>
       <c r="B237" t="n">
         <v>79209</v>
@@ -24281,10 +24297,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>445323</v>
+        <v>445477</v>
       </c>
       <c r="R237" t="n">
-        <v>6811251</v>
+        <v>6811356</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24343,10 +24359,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130250301</v>
+        <v>130250380</v>
       </c>
       <c r="B238" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24354,42 +24370,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>445222</v>
+        <v>445369</v>
       </c>
       <c r="R238" t="n">
-        <v>6811352</v>
+        <v>6811486</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24448,10 +24456,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130250288</v>
+        <v>130250408</v>
       </c>
       <c r="B239" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24459,42 +24467,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>445564</v>
+        <v>445323</v>
       </c>
       <c r="R239" t="n">
-        <v>6811446</v>
+        <v>6811251</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24553,10 +24553,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130250316</v>
+        <v>130250405</v>
       </c>
       <c r="B240" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24564,42 +24564,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>445524</v>
+        <v>445324</v>
       </c>
       <c r="R240" t="n">
-        <v>6811486</v>
+        <v>6811291</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24658,10 +24650,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>130250324</v>
+        <v>130250316</v>
       </c>
       <c r="B241" t="n">
-        <v>78967</v>
+        <v>57849</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24669,34 +24661,42 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>445465</v>
+        <v>445524</v>
       </c>
       <c r="R241" t="n">
-        <v>6811533</v>
+        <v>6811486</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250337</v>
+        <v>130250295</v>
       </c>
       <c r="B242" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,34 +24766,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445441</v>
+        <v>445263</v>
       </c>
       <c r="R242" t="n">
-        <v>6811531</v>
+        <v>6811480</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24852,10 +24860,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250384</v>
+        <v>130250337</v>
       </c>
       <c r="B243" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24863,21 +24871,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24887,10 +24895,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445209</v>
+        <v>445441</v>
       </c>
       <c r="R243" t="n">
-        <v>6811374</v>
+        <v>6811531</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24949,7 +24957,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250407</v>
+        <v>130250384</v>
       </c>
       <c r="B244" t="n">
         <v>79209</v>
@@ -24984,10 +24992,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445299</v>
+        <v>445209</v>
       </c>
       <c r="R244" t="n">
-        <v>6811253</v>
+        <v>6811374</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25143,7 +25151,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250403</v>
+        <v>130250378</v>
       </c>
       <c r="B246" t="n">
         <v>79209</v>
@@ -25178,10 +25186,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445337</v>
+        <v>445421</v>
       </c>
       <c r="R246" t="n">
-        <v>6811372</v>
+        <v>6811499</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25240,7 +25248,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250359</v>
+        <v>130250407</v>
       </c>
       <c r="B247" t="n">
         <v>79209</v>
@@ -25275,10 +25283,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445161</v>
+        <v>445299</v>
       </c>
       <c r="R247" t="n">
-        <v>6811404</v>
+        <v>6811253</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25337,7 +25345,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250378</v>
+        <v>130250403</v>
       </c>
       <c r="B248" t="n">
         <v>79209</v>
@@ -25372,10 +25380,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445421</v>
+        <v>445337</v>
       </c>
       <c r="R248" t="n">
-        <v>6811499</v>
+        <v>6811372</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25434,10 +25442,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250295</v>
+        <v>130250359</v>
       </c>
       <c r="B249" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25445,42 +25453,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445263</v>
+        <v>445161</v>
       </c>
       <c r="R249" t="n">
-        <v>6811480</v>
+        <v>6811404</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130237722</v>
+        <v>130237694</v>
       </c>
       <c r="B2" t="n">
         <v>57849</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445044</v>
+        <v>445036</v>
       </c>
       <c r="R2" t="n">
-        <v>6811281</v>
+        <v>6811601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130237694</v>
+        <v>130237722</v>
       </c>
       <c r="B3" t="n">
         <v>57849</v>
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445036</v>
+        <v>445044</v>
       </c>
       <c r="R3" t="n">
-        <v>6811601</v>
+        <v>6811281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130237706</v>
+        <v>130237743</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,42 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445093</v>
+        <v>445095</v>
       </c>
       <c r="R4" t="n">
-        <v>6811481</v>
+        <v>6811230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237743</v>
+        <v>130237712</v>
       </c>
       <c r="B5" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +993,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445095</v>
+        <v>445057</v>
       </c>
       <c r="R5" t="n">
-        <v>6811230</v>
+        <v>6811437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237745</v>
+        <v>130237706</v>
       </c>
       <c r="B6" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1098,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444954</v>
+        <v>445093</v>
       </c>
       <c r="R6" t="n">
-        <v>6811588</v>
+        <v>6811481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130237712</v>
+        <v>130237745</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,42 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445057</v>
+        <v>444954</v>
       </c>
       <c r="R8" t="n">
-        <v>6811437</v>
+        <v>6811588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237777</v>
+        <v>130237724</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1405,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445058</v>
+        <v>445064</v>
       </c>
       <c r="R9" t="n">
-        <v>6811322</v>
+        <v>6811249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237749</v>
+        <v>130237738</v>
       </c>
       <c r="B10" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1510,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,7 +1534,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445027</v>
+        <v>445081</v>
       </c>
       <c r="R10" t="n">
         <v>6811319</v>
@@ -1588,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237724</v>
+        <v>130237777</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,42 +1607,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445064</v>
+        <v>445058</v>
       </c>
       <c r="R11" t="n">
-        <v>6811249</v>
+        <v>6811322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237663</v>
+        <v>130237692</v>
       </c>
       <c r="B12" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1704,34 +1704,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444954</v>
+        <v>445036</v>
       </c>
       <c r="R12" t="n">
-        <v>6811588</v>
+        <v>6811602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,7 +1798,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237692</v>
+        <v>130237705</v>
       </c>
       <c r="B13" t="n">
         <v>57849</v>
@@ -1833,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445036</v>
+        <v>445092</v>
       </c>
       <c r="R13" t="n">
-        <v>6811602</v>
+        <v>6811513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130237705</v>
+        <v>130237749</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,42 +1914,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445092</v>
+        <v>445027</v>
       </c>
       <c r="R14" t="n">
-        <v>6811513</v>
+        <v>6811319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237738</v>
+        <v>130237663</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>79828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445081</v>
+        <v>444954</v>
       </c>
       <c r="R15" t="n">
-        <v>6811319</v>
+        <v>6811588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130237668</v>
+        <v>130237763</v>
       </c>
       <c r="B16" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445044</v>
+        <v>445019</v>
       </c>
       <c r="R16" t="n">
-        <v>6811305</v>
+        <v>6811423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130237763</v>
+        <v>130237668</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,21 +2205,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445019</v>
+        <v>445044</v>
       </c>
       <c r="R17" t="n">
-        <v>6811423</v>
+        <v>6811305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2986,45 +2986,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237744</v>
+        <v>130237677</v>
       </c>
       <c r="B25" t="n">
-        <v>78966</v>
+        <v>57042</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445002</v>
+        <v>445025</v>
       </c>
       <c r="R25" t="n">
-        <v>6811503</v>
+        <v>6811296</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,53 +3196,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237677</v>
+        <v>130237744</v>
       </c>
       <c r="B27" t="n">
-        <v>57042</v>
+        <v>78966</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445025</v>
+        <v>445002</v>
       </c>
       <c r="R27" t="n">
-        <v>6811296</v>
+        <v>6811503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4396,10 +4396,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130237670</v>
+        <v>130237764</v>
       </c>
       <c r="B39" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4407,21 +4407,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445045</v>
+        <v>445011</v>
       </c>
       <c r="R39" t="n">
-        <v>6811267</v>
+        <v>6811436</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130237669</v>
+        <v>130237779</v>
       </c>
       <c r="B40" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4504,21 +4504,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445036</v>
+        <v>445067</v>
       </c>
       <c r="R40" t="n">
-        <v>6811260</v>
+        <v>6811245</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130237764</v>
+        <v>130237669</v>
       </c>
       <c r="B42" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445011</v>
+        <v>445036</v>
       </c>
       <c r="R42" t="n">
-        <v>6811436</v>
+        <v>6811260</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237779</v>
+        <v>130237670</v>
       </c>
       <c r="B43" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4803,21 +4803,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445067</v>
+        <v>445045</v>
       </c>
       <c r="R43" t="n">
-        <v>6811245</v>
+        <v>6811267</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4986,49 +4986,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130237750</v>
+        <v>130237735</v>
       </c>
       <c r="B45" t="n">
-        <v>98950</v>
+        <v>78967</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445085</v>
+        <v>444985</v>
       </c>
       <c r="R45" t="n">
-        <v>6811515</v>
+        <v>6811589</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5063,18 +5059,12 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ett hundratal plantor.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5093,45 +5083,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130237735</v>
+        <v>130237750</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>98951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444985</v>
+        <v>445085</v>
       </c>
       <c r="R46" t="n">
-        <v>6811589</v>
+        <v>6811515</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5166,12 +5160,18 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett hundratal plantor.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237780</v>
+        <v>130237708</v>
       </c>
       <c r="B47" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,24 +5201,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
@@ -5228,7 +5236,7 @@
         <v>445066</v>
       </c>
       <c r="R47" t="n">
-        <v>6811223</v>
+        <v>6811502</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237708</v>
+        <v>130237660</v>
       </c>
       <c r="B48" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,42 +5306,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445066</v>
+        <v>444997</v>
       </c>
       <c r="R48" t="n">
-        <v>6811502</v>
+        <v>6811440</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237660</v>
+        <v>130237780</v>
       </c>
       <c r="B49" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R49" t="n">
-        <v>6811440</v>
+        <v>6811223</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130237704</v>
+        <v>130237710</v>
       </c>
       <c r="B52" t="n">
         <v>57849</v>
@@ -5728,7 +5728,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445097</v>
+        <v>445064</v>
       </c>
       <c r="R52" t="n">
-        <v>6811537</v>
+        <v>6811451</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130237710</v>
+        <v>130237704</v>
       </c>
       <c r="B53" t="n">
         <v>57849</v>
@@ -5833,7 +5833,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445064</v>
+        <v>445097</v>
       </c>
       <c r="R53" t="n">
-        <v>6811451</v>
+        <v>6811537</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130237776</v>
+        <v>130237661</v>
       </c>
       <c r="B54" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,21 +5916,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445092</v>
+        <v>444987</v>
       </c>
       <c r="R54" t="n">
-        <v>6811332</v>
+        <v>6811482</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130237762</v>
+        <v>130237776</v>
       </c>
       <c r="B55" t="n">
         <v>79209</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445021</v>
+        <v>445092</v>
       </c>
       <c r="R55" t="n">
-        <v>6811394</v>
+        <v>6811332</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130237661</v>
+        <v>130237762</v>
       </c>
       <c r="B56" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444987</v>
+        <v>445021</v>
       </c>
       <c r="R56" t="n">
-        <v>6811482</v>
+        <v>6811394</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,45 +6301,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237760</v>
+        <v>130237679</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445075</v>
+        <v>445036</v>
       </c>
       <c r="R58" t="n">
-        <v>6811319</v>
+        <v>6811277</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6398,10 +6406,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130237662</v>
+        <v>130237725</v>
       </c>
       <c r="B59" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6409,34 +6417,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445002</v>
+        <v>445073</v>
       </c>
       <c r="R59" t="n">
-        <v>6811503</v>
+        <v>6811522</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6495,53 +6511,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130237725</v>
+        <v>130237727</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>97822</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445073</v>
+        <v>445095</v>
       </c>
       <c r="R60" t="n">
-        <v>6811522</v>
+        <v>6811427</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6600,53 +6608,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237679</v>
+        <v>130237760</v>
       </c>
       <c r="B61" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445036</v>
+        <v>445075</v>
       </c>
       <c r="R61" t="n">
-        <v>6811277</v>
+        <v>6811319</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130237727</v>
+        <v>130237662</v>
       </c>
       <c r="B62" t="n">
-        <v>97821</v>
+        <v>79828</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445095</v>
+        <v>445002</v>
       </c>
       <c r="R62" t="n">
-        <v>6811427</v>
+        <v>6811503</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237709</v>
+        <v>130237711</v>
       </c>
       <c r="B63" t="n">
         <v>57849</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445058</v>
+        <v>445054</v>
       </c>
       <c r="R63" t="n">
-        <v>6811482</v>
+        <v>6811454</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,7 +6907,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237711</v>
+        <v>130237720</v>
       </c>
       <c r="B64" t="n">
         <v>57849</v>
@@ -6940,7 +6940,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445054</v>
+        <v>445048</v>
       </c>
       <c r="R64" t="n">
-        <v>6811454</v>
+        <v>6811299</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237713</v>
+        <v>130237709</v>
       </c>
       <c r="B65" t="n">
         <v>57849</v>
@@ -7045,7 +7045,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445073</v>
+        <v>445058</v>
       </c>
       <c r="R65" t="n">
-        <v>6811446</v>
+        <v>6811482</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7117,10 +7117,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237720</v>
+        <v>130237664</v>
       </c>
       <c r="B66" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7128,42 +7128,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445048</v>
+        <v>444968</v>
       </c>
       <c r="R66" t="n">
-        <v>6811299</v>
+        <v>6811605</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7222,10 +7214,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237664</v>
+        <v>130237713</v>
       </c>
       <c r="B67" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,34 +7225,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444968</v>
+        <v>445073</v>
       </c>
       <c r="R67" t="n">
-        <v>6811605</v>
+        <v>6811446</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130237769</v>
+        <v>130237690</v>
       </c>
       <c r="B71" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7637,34 +7637,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445114</v>
+        <v>445103</v>
       </c>
       <c r="R71" t="n">
-        <v>6811610</v>
+        <v>6811320</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7723,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130237716</v>
+        <v>130237769</v>
       </c>
       <c r="B72" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7734,42 +7742,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445149</v>
+        <v>445114</v>
       </c>
       <c r="R72" t="n">
-        <v>6811433</v>
+        <v>6811610</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130237690</v>
+        <v>130237716</v>
       </c>
       <c r="B73" t="n">
         <v>57849</v>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445103</v>
+        <v>445149</v>
       </c>
       <c r="R73" t="n">
-        <v>6811320</v>
+        <v>6811433</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8446,10 +8446,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130237747</v>
+        <v>130237700</v>
       </c>
       <c r="B79" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8457,34 +8457,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445113</v>
+        <v>445131</v>
       </c>
       <c r="R79" t="n">
-        <v>6811388</v>
+        <v>6811529</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8543,10 +8551,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130237700</v>
+        <v>130237747</v>
       </c>
       <c r="B80" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8554,42 +8562,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445131</v>
+        <v>445113</v>
       </c>
       <c r="R80" t="n">
-        <v>6811529</v>
+        <v>6811388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8648,10 +8648,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130237746</v>
+        <v>130237771</v>
       </c>
       <c r="B81" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8659,21 +8659,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445153</v>
+        <v>445159</v>
       </c>
       <c r="R81" t="n">
-        <v>6811549</v>
+        <v>6811562</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130237771</v>
+        <v>130237703</v>
       </c>
       <c r="B82" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8756,34 +8756,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445159</v>
+        <v>445132</v>
       </c>
       <c r="R82" t="n">
-        <v>6811562</v>
+        <v>6811535</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8842,10 +8850,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130237703</v>
+        <v>130237746</v>
       </c>
       <c r="B83" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8853,42 +8861,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445132</v>
+        <v>445153</v>
       </c>
       <c r="R83" t="n">
-        <v>6811535</v>
+        <v>6811549</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130237702</v>
+        <v>130237768</v>
       </c>
       <c r="B85" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9055,42 +9055,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445137</v>
+        <v>445145</v>
       </c>
       <c r="R85" t="n">
-        <v>6811505</v>
+        <v>6811638</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9149,10 +9141,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130237768</v>
+        <v>130237702</v>
       </c>
       <c r="B86" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9160,34 +9152,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445145</v>
+        <v>445137</v>
       </c>
       <c r="R86" t="n">
-        <v>6811638</v>
+        <v>6811505</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9744,7 +9744,7 @@
         <v>130237726</v>
       </c>
       <c r="B92" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237758</v>
+        <v>130237696</v>
       </c>
       <c r="B94" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9951,34 +9951,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445101</v>
+        <v>445118</v>
       </c>
       <c r="R94" t="n">
-        <v>6811246</v>
+        <v>6811654</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10037,7 +10045,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130237696</v>
+        <v>130237718</v>
       </c>
       <c r="B95" t="n">
         <v>57849</v>
@@ -10080,10 +10088,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445118</v>
+        <v>445116</v>
       </c>
       <c r="R95" t="n">
-        <v>6811654</v>
+        <v>6811382</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10142,10 +10150,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237718</v>
+        <v>130237758</v>
       </c>
       <c r="B96" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10153,42 +10161,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445116</v>
+        <v>445101</v>
       </c>
       <c r="R96" t="n">
-        <v>6811382</v>
+        <v>6811246</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10344,10 +10344,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130250364</v>
+        <v>130250309</v>
       </c>
       <c r="B98" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10355,34 +10355,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445309</v>
+        <v>445368</v>
       </c>
       <c r="R98" t="n">
-        <v>6811605</v>
+        <v>6811354</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10441,10 +10449,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130250379</v>
+        <v>130250294</v>
       </c>
       <c r="B99" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10452,34 +10460,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445369</v>
+        <v>445280</v>
       </c>
       <c r="R99" t="n">
-        <v>6811508</v>
+        <v>6811472</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10538,10 +10554,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130250366</v>
+        <v>130250304</v>
       </c>
       <c r="B100" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10549,34 +10565,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445328</v>
+        <v>445494</v>
       </c>
       <c r="R100" t="n">
-        <v>6811603</v>
+        <v>6811338</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10635,10 +10659,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130250294</v>
+        <v>130250364</v>
       </c>
       <c r="B101" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10646,42 +10670,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445280</v>
+        <v>445309</v>
       </c>
       <c r="R101" t="n">
-        <v>6811472</v>
+        <v>6811605</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10837,10 +10853,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130250304</v>
+        <v>130250379</v>
       </c>
       <c r="B103" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10848,42 +10864,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445494</v>
+        <v>445369</v>
       </c>
       <c r="R103" t="n">
-        <v>6811338</v>
+        <v>6811508</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10942,10 +10950,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130250309</v>
+        <v>130250366</v>
       </c>
       <c r="B104" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10953,42 +10961,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445368</v>
+        <v>445328</v>
       </c>
       <c r="R104" t="n">
-        <v>6811354</v>
+        <v>6811603</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11047,10 +11047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250343</v>
+        <v>130250267</v>
       </c>
       <c r="B105" t="n">
-        <v>78966</v>
+        <v>91759</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,34 +11058,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445471</v>
+        <v>445503</v>
       </c>
       <c r="R105" t="n">
-        <v>6811288</v>
+        <v>6811332</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11126,8 +11129,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11144,10 +11168,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130250261</v>
+        <v>130250343</v>
       </c>
       <c r="B106" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11155,21 +11179,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11179,10 +11203,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445339</v>
+        <v>445471</v>
       </c>
       <c r="R106" t="n">
-        <v>6811359</v>
+        <v>6811288</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11338,10 +11362,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130250302</v>
+        <v>130250401</v>
       </c>
       <c r="B108" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11349,42 +11373,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445239</v>
+        <v>445368</v>
       </c>
       <c r="R108" t="n">
-        <v>6811358</v>
+        <v>6811413</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11443,53 +11459,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130250270</v>
+        <v>130250409</v>
       </c>
       <c r="B109" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445426</v>
+        <v>445294</v>
       </c>
       <c r="R109" t="n">
-        <v>6811491</v>
+        <v>6811231</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11548,53 +11556,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130250272</v>
+        <v>130250261</v>
       </c>
       <c r="B110" t="n">
-        <v>57042</v>
+        <v>79828</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445468</v>
+        <v>445339</v>
       </c>
       <c r="R110" t="n">
-        <v>6811258</v>
+        <v>6811359</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11653,7 +11653,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130250401</v>
+        <v>130250402</v>
       </c>
       <c r="B111" t="n">
         <v>79209</v>
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445368</v>
+        <v>445364</v>
       </c>
       <c r="R111" t="n">
-        <v>6811413</v>
+        <v>6811345</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11750,45 +11750,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130250409</v>
+        <v>130250270</v>
       </c>
       <c r="B112" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445294</v>
+        <v>445426</v>
       </c>
       <c r="R112" t="n">
-        <v>6811231</v>
+        <v>6811491</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11847,45 +11855,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130250402</v>
+        <v>130250272</v>
       </c>
       <c r="B113" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445364</v>
+        <v>445468</v>
       </c>
       <c r="R113" t="n">
-        <v>6811345</v>
+        <v>6811258</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11944,10 +11960,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130250267</v>
+        <v>130250302</v>
       </c>
       <c r="B114" t="n">
-        <v>91758</v>
+        <v>57849</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11955,26 +11971,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -11982,10 +12003,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445503</v>
+        <v>445239</v>
       </c>
       <c r="R114" t="n">
-        <v>6811332</v>
+        <v>6811358</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12026,29 +12047,8 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12065,10 +12065,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130250296</v>
+        <v>130250385</v>
       </c>
       <c r="B115" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12076,42 +12076,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445240</v>
+        <v>445210</v>
       </c>
       <c r="R115" t="n">
-        <v>6811502</v>
+        <v>6811346</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12170,10 +12162,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130250313</v>
+        <v>130250345</v>
       </c>
       <c r="B116" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12181,42 +12173,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445334</v>
+        <v>445339</v>
       </c>
       <c r="R116" t="n">
-        <v>6811325</v>
+        <v>6811359</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12372,10 +12356,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130250345</v>
+        <v>130250313</v>
       </c>
       <c r="B118" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12383,34 +12367,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445339</v>
+        <v>445334</v>
       </c>
       <c r="R118" t="n">
-        <v>6811359</v>
+        <v>6811325</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12469,10 +12461,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130250385</v>
+        <v>130250296</v>
       </c>
       <c r="B119" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12480,34 +12472,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445210</v>
+        <v>445240</v>
       </c>
       <c r="R119" t="n">
-        <v>6811346</v>
+        <v>6811502</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,7 +12566,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250357</v>
+        <v>130250394</v>
       </c>
       <c r="B120" t="n">
         <v>79209</v>
@@ -12595,16 +12595,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445165</v>
+        <v>445495</v>
       </c>
       <c r="R120" t="n">
-        <v>6811302</v>
+        <v>6811385</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12645,6 +12648,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12663,10 +12667,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250289</v>
+        <v>130250259</v>
       </c>
       <c r="B121" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12674,42 +12678,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445468</v>
+        <v>445441</v>
       </c>
       <c r="R121" t="n">
-        <v>6811500</v>
+        <v>6811433</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12768,10 +12764,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250314</v>
+        <v>130250404</v>
       </c>
       <c r="B122" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12779,42 +12775,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445322</v>
+        <v>445330</v>
       </c>
       <c r="R122" t="n">
-        <v>6811309</v>
+        <v>6811333</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12873,10 +12861,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250315</v>
+        <v>130250360</v>
       </c>
       <c r="B123" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12884,42 +12872,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445317</v>
+        <v>445194</v>
       </c>
       <c r="R123" t="n">
-        <v>6811271</v>
+        <v>6811530</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12978,10 +12958,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250293</v>
+        <v>130250338</v>
       </c>
       <c r="B124" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12989,42 +12969,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445303</v>
+        <v>445492</v>
       </c>
       <c r="R124" t="n">
-        <v>6811490</v>
+        <v>6811520</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13083,10 +13055,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250338</v>
+        <v>130250399</v>
       </c>
       <c r="B125" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13094,21 +13066,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13118,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445492</v>
+        <v>445416</v>
       </c>
       <c r="R125" t="n">
-        <v>6811520</v>
+        <v>6811445</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13180,10 +13152,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250259</v>
+        <v>130250357</v>
       </c>
       <c r="B126" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13191,21 +13163,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13215,10 +13187,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445441</v>
+        <v>445165</v>
       </c>
       <c r="R126" t="n">
-        <v>6811433</v>
+        <v>6811302</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13277,10 +13249,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250394</v>
+        <v>130250289</v>
       </c>
       <c r="B127" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13288,26 +13260,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13315,10 +13292,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445495</v>
+        <v>445468</v>
       </c>
       <c r="R127" t="n">
-        <v>6811385</v>
+        <v>6811500</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13359,7 +13336,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13378,10 +13354,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250404</v>
+        <v>130250315</v>
       </c>
       <c r="B128" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13389,34 +13365,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445330</v>
+        <v>445317</v>
       </c>
       <c r="R128" t="n">
-        <v>6811333</v>
+        <v>6811271</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13475,10 +13459,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250360</v>
+        <v>130250314</v>
       </c>
       <c r="B129" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13486,34 +13470,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445194</v>
+        <v>445322</v>
       </c>
       <c r="R129" t="n">
-        <v>6811530</v>
+        <v>6811309</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13572,10 +13564,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250399</v>
+        <v>130250293</v>
       </c>
       <c r="B130" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13583,34 +13575,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445416</v>
+        <v>445303</v>
       </c>
       <c r="R130" t="n">
-        <v>6811445</v>
+        <v>6811490</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130250321</v>
+        <v>130250255</v>
       </c>
       <c r="B131" t="n">
-        <v>78967</v>
+        <v>79828</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13680,21 +13680,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13704,10 +13704,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>445326</v>
+        <v>445480</v>
       </c>
       <c r="R131" t="n">
-        <v>6811613</v>
+        <v>6811273</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130250255</v>
+        <v>130250321</v>
       </c>
       <c r="B132" t="n">
-        <v>79828</v>
+        <v>78967</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13777,21 +13777,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>445480</v>
+        <v>445326</v>
       </c>
       <c r="R132" t="n">
-        <v>6811273</v>
+        <v>6811613</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14861,10 +14861,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250303</v>
+        <v>130250362</v>
       </c>
       <c r="B143" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14872,42 +14872,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445389</v>
+        <v>445218</v>
       </c>
       <c r="R143" t="n">
-        <v>6811264</v>
+        <v>6811594</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14966,32 +14958,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250271</v>
+        <v>130250292</v>
       </c>
       <c r="B144" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14999,7 +14991,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -15009,10 +15001,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445375</v>
+        <v>445384</v>
       </c>
       <c r="R144" t="n">
-        <v>6811502</v>
+        <v>6811490</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15071,10 +15063,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250362</v>
+        <v>130250303</v>
       </c>
       <c r="B145" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15082,34 +15074,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445218</v>
+        <v>445389</v>
       </c>
       <c r="R145" t="n">
-        <v>6811594</v>
+        <v>6811264</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15273,32 +15273,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250292</v>
+        <v>130250274</v>
       </c>
       <c r="B147" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15306,7 +15306,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -15316,10 +15316,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445384</v>
+        <v>445376</v>
       </c>
       <c r="R147" t="n">
-        <v>6811490</v>
+        <v>6811389</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15378,45 +15378,53 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250323</v>
+        <v>130250271</v>
       </c>
       <c r="B148" t="n">
-        <v>78967</v>
+        <v>57042</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445371</v>
+        <v>445375</v>
       </c>
       <c r="R148" t="n">
-        <v>6811594</v>
+        <v>6811502</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15475,7 +15483,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250328</v>
+        <v>130250323</v>
       </c>
       <c r="B149" t="n">
         <v>78967</v>
@@ -15510,10 +15518,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445329</v>
+        <v>445371</v>
       </c>
       <c r="R149" t="n">
-        <v>6811272</v>
+        <v>6811594</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15669,53 +15677,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250274</v>
+        <v>130250328</v>
       </c>
       <c r="B151" t="n">
-        <v>57042</v>
+        <v>78967</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445376</v>
+        <v>445329</v>
       </c>
       <c r="R151" t="n">
-        <v>6811389</v>
+        <v>6811272</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15774,45 +15774,53 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130250335</v>
+        <v>130250276</v>
       </c>
       <c r="B152" t="n">
-        <v>78966</v>
+        <v>57042</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>445372</v>
+        <v>445328</v>
       </c>
       <c r="R152" t="n">
-        <v>6811595</v>
+        <v>6811392</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15871,45 +15879,49 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130250341</v>
+        <v>130250319</v>
       </c>
       <c r="B153" t="n">
-        <v>78966</v>
+        <v>97828</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>445383</v>
+        <v>445554</v>
       </c>
       <c r="R153" t="n">
-        <v>6811286</v>
+        <v>6811457</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15950,6 +15962,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -15968,10 +15981,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130250336</v>
+        <v>130250326</v>
       </c>
       <c r="B154" t="n">
-        <v>78966</v>
+        <v>78967</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15979,21 +15992,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16003,10 +16016,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>445413</v>
+        <v>445235</v>
       </c>
       <c r="R154" t="n">
-        <v>6811568</v>
+        <v>6811325</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16065,10 +16078,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130250381</v>
+        <v>130250329</v>
       </c>
       <c r="B155" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16076,21 +16089,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16100,10 +16113,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>445351</v>
+        <v>445323</v>
       </c>
       <c r="R155" t="n">
-        <v>6811495</v>
+        <v>6811270</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16162,10 +16175,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250326</v>
+        <v>130250381</v>
       </c>
       <c r="B156" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16173,21 +16186,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16197,10 +16210,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445235</v>
+        <v>445351</v>
       </c>
       <c r="R156" t="n">
-        <v>6811325</v>
+        <v>6811495</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16259,10 +16272,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130250329</v>
+        <v>130250335</v>
       </c>
       <c r="B157" t="n">
-        <v>78967</v>
+        <v>78966</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16270,21 +16283,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16294,10 +16307,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445323</v>
+        <v>445372</v>
       </c>
       <c r="R157" t="n">
-        <v>6811270</v>
+        <v>6811595</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16356,10 +16369,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130250317</v>
+        <v>130250341</v>
       </c>
       <c r="B158" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16367,42 +16380,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445487</v>
+        <v>445383</v>
       </c>
       <c r="R158" t="n">
-        <v>6811335</v>
+        <v>6811286</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16461,53 +16466,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130250276</v>
+        <v>130250336</v>
       </c>
       <c r="B159" t="n">
-        <v>57042</v>
+        <v>78966</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445328</v>
+        <v>445413</v>
       </c>
       <c r="R159" t="n">
-        <v>6811392</v>
+        <v>6811568</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16671,38 +16668,42 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250319</v>
+        <v>130250317</v>
       </c>
       <c r="B161" t="n">
-        <v>97827</v>
+        <v>57849</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -16710,10 +16711,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445554</v>
+        <v>445487</v>
       </c>
       <c r="R161" t="n">
-        <v>6811457</v>
+        <v>6811335</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16754,7 +16755,6 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130250391</v>
+        <v>130250340</v>
       </c>
       <c r="B162" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16784,21 +16784,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>445499</v>
+        <v>445366</v>
       </c>
       <c r="R162" t="n">
-        <v>6811328</v>
+        <v>6811298</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16870,10 +16870,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130250398</v>
+        <v>130250248</v>
       </c>
       <c r="B163" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16881,21 +16881,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16905,10 +16905,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>445426</v>
+        <v>445243</v>
       </c>
       <c r="R163" t="n">
-        <v>6811434</v>
+        <v>6811593</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16967,7 +16967,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130250371</v>
+        <v>130250391</v>
       </c>
       <c r="B164" t="n">
         <v>79209</v>
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>445588</v>
+        <v>445499</v>
       </c>
       <c r="R164" t="n">
-        <v>6811455</v>
+        <v>6811328</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17064,10 +17064,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130250279</v>
+        <v>130250398</v>
       </c>
       <c r="B165" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17075,42 +17075,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>445165</v>
+        <v>445426</v>
       </c>
       <c r="R165" t="n">
-        <v>6811426</v>
+        <v>6811434</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17169,10 +17161,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130250287</v>
+        <v>130250371</v>
       </c>
       <c r="B166" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17180,42 +17172,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>445575</v>
+        <v>445588</v>
       </c>
       <c r="R166" t="n">
-        <v>6811437</v>
+        <v>6811455</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17274,10 +17258,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130250282</v>
+        <v>130250342</v>
       </c>
       <c r="B167" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17285,42 +17269,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>445213</v>
+        <v>445390</v>
       </c>
       <c r="R167" t="n">
-        <v>6811666</v>
+        <v>6811275</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17379,10 +17355,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130250342</v>
+        <v>130250282</v>
       </c>
       <c r="B168" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17390,34 +17366,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>445390</v>
+        <v>445213</v>
       </c>
       <c r="R168" t="n">
-        <v>6811275</v>
+        <v>6811666</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17476,10 +17460,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130250248</v>
+        <v>130250279</v>
       </c>
       <c r="B169" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17487,34 +17471,42 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>445243</v>
+        <v>445165</v>
       </c>
       <c r="R169" t="n">
-        <v>6811593</v>
+        <v>6811426</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17573,10 +17565,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130250340</v>
+        <v>130250287</v>
       </c>
       <c r="B170" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17584,34 +17576,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>445366</v>
+        <v>445575</v>
       </c>
       <c r="R170" t="n">
-        <v>6811298</v>
+        <v>6811437</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17670,10 +17670,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130250347</v>
+        <v>130250290</v>
       </c>
       <c r="B171" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17681,34 +17681,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>445334</v>
+        <v>445457</v>
       </c>
       <c r="R171" t="n">
-        <v>6811304</v>
+        <v>6811507</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17767,10 +17775,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130250260</v>
+        <v>130250347</v>
       </c>
       <c r="B172" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17778,21 +17786,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17802,10 +17810,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>445425</v>
+        <v>445334</v>
       </c>
       <c r="R172" t="n">
-        <v>6811413</v>
+        <v>6811304</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17864,10 +17872,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130250346</v>
+        <v>130250260</v>
       </c>
       <c r="B173" t="n">
-        <v>78966</v>
+        <v>79828</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17875,21 +17883,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17899,10 +17907,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>445322</v>
+        <v>445425</v>
       </c>
       <c r="R173" t="n">
-        <v>6811363</v>
+        <v>6811413</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18252,10 +18260,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250290</v>
+        <v>130250346</v>
       </c>
       <c r="B177" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18263,42 +18271,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445457</v>
+        <v>445322</v>
       </c>
       <c r="R177" t="n">
-        <v>6811507</v>
+        <v>6811363</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18360,7 +18360,7 @@
         <v>130250318</v>
       </c>
       <c r="B178" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250325</v>
+        <v>130250406</v>
       </c>
       <c r="B180" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445457</v>
+        <v>445341</v>
       </c>
       <c r="R180" t="n">
-        <v>6811516</v>
+        <v>6811293</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250383</v>
+        <v>130250284</v>
       </c>
       <c r="B181" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,34 +18659,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445209</v>
+        <v>445310</v>
       </c>
       <c r="R181" t="n">
-        <v>6811451</v>
+        <v>6811604</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,10 +18753,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250406</v>
+        <v>130250311</v>
       </c>
       <c r="B182" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18756,34 +18764,42 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445341</v>
+        <v>445333</v>
       </c>
       <c r="R182" t="n">
-        <v>6811293</v>
+        <v>6811358</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,10 +18858,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250377</v>
+        <v>130250325</v>
       </c>
       <c r="B183" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18853,21 +18869,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18877,10 +18893,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445454</v>
+        <v>445457</v>
       </c>
       <c r="R183" t="n">
-        <v>6811502</v>
+        <v>6811516</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,10 +18955,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250284</v>
+        <v>130250333</v>
       </c>
       <c r="B184" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18950,42 +18966,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445310</v>
+        <v>445201</v>
       </c>
       <c r="R184" t="n">
-        <v>6811604</v>
+        <v>6811621</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19044,7 +19052,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250333</v>
+        <v>130250344</v>
       </c>
       <c r="B185" t="n">
         <v>78966</v>
@@ -19079,10 +19087,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445201</v>
+        <v>445358</v>
       </c>
       <c r="R185" t="n">
-        <v>6811621</v>
+        <v>6811433</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19141,10 +19149,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130250344</v>
+        <v>130250383</v>
       </c>
       <c r="B186" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19152,21 +19160,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19176,10 +19184,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>445358</v>
+        <v>445209</v>
       </c>
       <c r="R186" t="n">
-        <v>6811433</v>
+        <v>6811451</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19238,10 +19246,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>130250311</v>
+        <v>130250377</v>
       </c>
       <c r="B187" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19249,42 +19257,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>445333</v>
+        <v>445454</v>
       </c>
       <c r="R187" t="n">
-        <v>6811358</v>
+        <v>6811502</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130250256</v>
+        <v>130250298</v>
       </c>
       <c r="B194" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19970,34 +19970,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445484</v>
+        <v>445232</v>
       </c>
       <c r="R194" t="n">
-        <v>6811291</v>
+        <v>6811448</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20056,10 +20064,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250250</v>
+        <v>130250281</v>
       </c>
       <c r="B195" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20067,34 +20075,42 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445248</v>
+        <v>445205</v>
       </c>
       <c r="R195" t="n">
-        <v>6811642</v>
+        <v>6811619</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20153,10 +20169,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250370</v>
+        <v>130250300</v>
       </c>
       <c r="B196" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20164,34 +20180,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445542</v>
+        <v>445219</v>
       </c>
       <c r="R196" t="n">
-        <v>6811532</v>
+        <v>6811344</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20250,10 +20274,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250395</v>
+        <v>130250291</v>
       </c>
       <c r="B197" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20261,34 +20285,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445507</v>
+        <v>445385</v>
       </c>
       <c r="R197" t="n">
-        <v>6811412</v>
+        <v>6811504</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20347,10 +20379,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250386</v>
+        <v>130250327</v>
       </c>
       <c r="B198" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20358,21 +20390,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20382,10 +20414,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445226</v>
+        <v>445390</v>
       </c>
       <c r="R198" t="n">
-        <v>6811348</v>
+        <v>6811275</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20444,53 +20476,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250277</v>
+        <v>130250250</v>
       </c>
       <c r="B199" t="n">
-        <v>57042</v>
+        <v>79828</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445202</v>
+        <v>445248</v>
       </c>
       <c r="R199" t="n">
-        <v>6811655</v>
+        <v>6811642</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20549,53 +20573,45 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250355</v>
+        <v>130250370</v>
       </c>
       <c r="B200" t="n">
-        <v>57844</v>
+        <v>79209</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445443</v>
+        <v>445542</v>
       </c>
       <c r="R200" t="n">
-        <v>6811494</v>
+        <v>6811532</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20654,10 +20670,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250327</v>
+        <v>130250395</v>
       </c>
       <c r="B201" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20665,21 +20681,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20689,10 +20705,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445390</v>
+        <v>445507</v>
       </c>
       <c r="R201" t="n">
-        <v>6811275</v>
+        <v>6811412</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20751,10 +20767,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250300</v>
+        <v>130250256</v>
       </c>
       <c r="B202" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20762,42 +20778,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445219</v>
+        <v>445484</v>
       </c>
       <c r="R202" t="n">
-        <v>6811344</v>
+        <v>6811291</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20856,10 +20864,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250298</v>
+        <v>130250386</v>
       </c>
       <c r="B203" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20867,42 +20875,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445232</v>
+        <v>445226</v>
       </c>
       <c r="R203" t="n">
-        <v>6811448</v>
+        <v>6811348</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20961,32 +20961,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250291</v>
+        <v>130250355</v>
       </c>
       <c r="B204" t="n">
-        <v>57849</v>
+        <v>57844</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20994,7 +20994,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -21004,10 +21004,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445385</v>
+        <v>445443</v>
       </c>
       <c r="R204" t="n">
-        <v>6811504</v>
+        <v>6811494</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21066,32 +21066,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130250281</v>
+        <v>130250277</v>
       </c>
       <c r="B205" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21099,7 +21099,7 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
@@ -21109,10 +21109,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>445205</v>
+        <v>445202</v>
       </c>
       <c r="R205" t="n">
-        <v>6811619</v>
+        <v>6811655</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21268,7 +21268,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250249</v>
+        <v>130250254</v>
       </c>
       <c r="B207" t="n">
         <v>79828</v>
@@ -21303,10 +21303,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445200</v>
+        <v>445194</v>
       </c>
       <c r="R207" t="n">
-        <v>6811598</v>
+        <v>6811426</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21462,7 +21462,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250254</v>
+        <v>130250249</v>
       </c>
       <c r="B209" t="n">
         <v>79828</v>
@@ -21497,10 +21497,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445194</v>
+        <v>445200</v>
       </c>
       <c r="R209" t="n">
-        <v>6811426</v>
+        <v>6811598</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21559,10 +21559,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250280</v>
+        <v>130250392</v>
       </c>
       <c r="B210" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21570,42 +21570,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445179</v>
+        <v>445487</v>
       </c>
       <c r="R210" t="n">
-        <v>6811467</v>
+        <v>6811345</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21664,10 +21656,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250283</v>
+        <v>130250389</v>
       </c>
       <c r="B211" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21675,42 +21667,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445303</v>
+        <v>445483</v>
       </c>
       <c r="R211" t="n">
-        <v>6811621</v>
+        <v>6811288</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21769,7 +21753,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250392</v>
+        <v>130250367</v>
       </c>
       <c r="B212" t="n">
         <v>79209</v>
@@ -21804,10 +21788,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445487</v>
+        <v>445376</v>
       </c>
       <c r="R212" t="n">
-        <v>6811345</v>
+        <v>6811581</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21866,10 +21850,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250389</v>
+        <v>130250280</v>
       </c>
       <c r="B213" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21877,34 +21861,42 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445483</v>
+        <v>445179</v>
       </c>
       <c r="R213" t="n">
-        <v>6811288</v>
+        <v>6811467</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21963,10 +21955,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250367</v>
+        <v>130250305</v>
       </c>
       <c r="B214" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21974,34 +21966,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445376</v>
+        <v>445448</v>
       </c>
       <c r="R214" t="n">
-        <v>6811581</v>
+        <v>6811432</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22165,7 +22165,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250305</v>
+        <v>130250283</v>
       </c>
       <c r="B216" t="n">
         <v>57849</v>
@@ -22208,10 +22208,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445448</v>
+        <v>445303</v>
       </c>
       <c r="R216" t="n">
-        <v>6811432</v>
+        <v>6811621</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22270,10 +22270,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130250387</v>
+        <v>130250247</v>
       </c>
       <c r="B217" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22281,21 +22281,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22305,10 +22305,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>445238</v>
+        <v>445188</v>
       </c>
       <c r="R217" t="n">
-        <v>6811310</v>
+        <v>6811507</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22367,10 +22367,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130250252</v>
+        <v>130250348</v>
       </c>
       <c r="B218" t="n">
-        <v>79828</v>
+        <v>78966</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22378,21 +22378,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22402,10 +22402,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>445586</v>
+        <v>445329</v>
       </c>
       <c r="R218" t="n">
-        <v>6811454</v>
+        <v>6811272</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22464,7 +22464,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130250247</v>
+        <v>130250253</v>
       </c>
       <c r="B219" t="n">
         <v>79828</v>
@@ -22499,10 +22499,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>445188</v>
+        <v>445543</v>
       </c>
       <c r="R219" t="n">
-        <v>6811507</v>
+        <v>6811480</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22561,7 +22561,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130250253</v>
+        <v>130250252</v>
       </c>
       <c r="B220" t="n">
         <v>79828</v>
@@ -22596,10 +22596,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>445543</v>
+        <v>445586</v>
       </c>
       <c r="R220" t="n">
-        <v>6811480</v>
+        <v>6811454</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22658,10 +22658,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130250348</v>
+        <v>130250387</v>
       </c>
       <c r="B221" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22669,21 +22669,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22693,10 +22693,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>445329</v>
+        <v>445238</v>
       </c>
       <c r="R221" t="n">
-        <v>6811272</v>
+        <v>6811310</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22860,7 +22860,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130250307</v>
+        <v>130250299</v>
       </c>
       <c r="B223" t="n">
         <v>57849</v>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>445373</v>
+        <v>445206</v>
       </c>
       <c r="R223" t="n">
-        <v>6811417</v>
+        <v>6811400</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22965,7 +22965,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130250299</v>
+        <v>130250307</v>
       </c>
       <c r="B224" t="n">
         <v>57849</v>
@@ -23008,10 +23008,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>445206</v>
+        <v>445373</v>
       </c>
       <c r="R224" t="n">
-        <v>6811400</v>
+        <v>6811417</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23264,10 +23264,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130250382</v>
+        <v>130250263</v>
       </c>
       <c r="B227" t="n">
-        <v>79209</v>
+        <v>79828</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23275,21 +23275,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23299,10 +23299,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>445218</v>
+        <v>445321</v>
       </c>
       <c r="R227" t="n">
-        <v>6811435</v>
+        <v>6811263</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23462,10 +23462,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130250285</v>
+        <v>130250334</v>
       </c>
       <c r="B229" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23473,42 +23473,34 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>445439</v>
+        <v>445266</v>
       </c>
       <c r="R229" t="n">
-        <v>6811539</v>
+        <v>6811642</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23567,10 +23559,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130250263</v>
+        <v>130250382</v>
       </c>
       <c r="B230" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23578,21 +23570,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23602,10 +23594,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>445321</v>
+        <v>445218</v>
       </c>
       <c r="R230" t="n">
-        <v>6811263</v>
+        <v>6811435</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23664,10 +23656,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>130250334</v>
+        <v>130250285</v>
       </c>
       <c r="B231" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23675,34 +23667,42 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>445266</v>
+        <v>445439</v>
       </c>
       <c r="R231" t="n">
-        <v>6811642</v>
+        <v>6811539</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130250324</v>
+        <v>130250393</v>
       </c>
       <c r="B232" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23772,21 +23772,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -23796,10 +23796,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>445465</v>
+        <v>445477</v>
       </c>
       <c r="R232" t="n">
-        <v>6811533</v>
+        <v>6811356</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23858,7 +23858,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130250397</v>
+        <v>130250380</v>
       </c>
       <c r="B233" t="n">
         <v>79209</v>
@@ -23893,10 +23893,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>445441</v>
+        <v>445369</v>
       </c>
       <c r="R233" t="n">
-        <v>6811411</v>
+        <v>6811486</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23955,10 +23955,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130250288</v>
+        <v>130250408</v>
       </c>
       <c r="B234" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23966,42 +23966,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445564</v>
+        <v>445323</v>
       </c>
       <c r="R234" t="n">
-        <v>6811446</v>
+        <v>6811251</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24060,10 +24052,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130250301</v>
+        <v>130250246</v>
       </c>
       <c r="B235" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24071,42 +24063,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>445222</v>
+        <v>445182</v>
       </c>
       <c r="R235" t="n">
-        <v>6811352</v>
+        <v>6811329</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24165,10 +24149,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130250246</v>
+        <v>130250405</v>
       </c>
       <c r="B236" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24176,21 +24160,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24200,10 +24184,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>445182</v>
+        <v>445324</v>
       </c>
       <c r="R236" t="n">
-        <v>6811329</v>
+        <v>6811291</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24262,7 +24246,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130250393</v>
+        <v>130250397</v>
       </c>
       <c r="B237" t="n">
         <v>79209</v>
@@ -24297,10 +24281,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>445477</v>
+        <v>445441</v>
       </c>
       <c r="R237" t="n">
-        <v>6811356</v>
+        <v>6811411</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24359,10 +24343,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130250380</v>
+        <v>130250316</v>
       </c>
       <c r="B238" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24370,31 +24354,39 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>445369</v>
+        <v>445524</v>
       </c>
       <c r="R238" t="n">
         <v>6811486</v>
@@ -24456,10 +24448,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130250408</v>
+        <v>130250301</v>
       </c>
       <c r="B239" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24467,34 +24459,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>445323</v>
+        <v>445222</v>
       </c>
       <c r="R239" t="n">
-        <v>6811251</v>
+        <v>6811352</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24553,10 +24553,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130250405</v>
+        <v>130250288</v>
       </c>
       <c r="B240" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24564,34 +24564,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>445324</v>
+        <v>445564</v>
       </c>
       <c r="R240" t="n">
-        <v>6811291</v>
+        <v>6811446</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24650,10 +24658,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>130250316</v>
+        <v>130250324</v>
       </c>
       <c r="B241" t="n">
-        <v>57849</v>
+        <v>78967</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24661,42 +24669,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>445524</v>
+        <v>445465</v>
       </c>
       <c r="R241" t="n">
-        <v>6811486</v>
+        <v>6811533</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250295</v>
+        <v>130250337</v>
       </c>
       <c r="B242" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,42 +24766,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445263</v>
+        <v>445441</v>
       </c>
       <c r="R242" t="n">
-        <v>6811480</v>
+        <v>6811531</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24860,10 +24852,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250337</v>
+        <v>130250384</v>
       </c>
       <c r="B243" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24871,21 +24863,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24895,10 +24887,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445441</v>
+        <v>445209</v>
       </c>
       <c r="R243" t="n">
-        <v>6811531</v>
+        <v>6811374</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24957,7 +24949,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250384</v>
+        <v>130250375</v>
       </c>
       <c r="B244" t="n">
         <v>79209</v>
@@ -24992,10 +24984,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445209</v>
+        <v>445492</v>
       </c>
       <c r="R244" t="n">
-        <v>6811374</v>
+        <v>6811496</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25054,7 +25046,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250375</v>
+        <v>130250378</v>
       </c>
       <c r="B245" t="n">
         <v>79209</v>
@@ -25089,10 +25081,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445492</v>
+        <v>445421</v>
       </c>
       <c r="R245" t="n">
-        <v>6811496</v>
+        <v>6811499</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25151,7 +25143,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250378</v>
+        <v>130250407</v>
       </c>
       <c r="B246" t="n">
         <v>79209</v>
@@ -25186,10 +25178,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445421</v>
+        <v>445299</v>
       </c>
       <c r="R246" t="n">
-        <v>6811499</v>
+        <v>6811253</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25248,7 +25240,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250407</v>
+        <v>130250403</v>
       </c>
       <c r="B247" t="n">
         <v>79209</v>
@@ -25283,10 +25275,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445299</v>
+        <v>445337</v>
       </c>
       <c r="R247" t="n">
-        <v>6811253</v>
+        <v>6811372</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25345,7 +25337,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250403</v>
+        <v>130250359</v>
       </c>
       <c r="B248" t="n">
         <v>79209</v>
@@ -25380,10 +25372,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445337</v>
+        <v>445161</v>
       </c>
       <c r="R248" t="n">
-        <v>6811372</v>
+        <v>6811404</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25442,10 +25434,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250359</v>
+        <v>130250295</v>
       </c>
       <c r="B249" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25453,34 +25445,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445161</v>
+        <v>445263</v>
       </c>
       <c r="R249" t="n">
-        <v>6811404</v>
+        <v>6811480</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130237694</v>
+        <v>130237722</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445036</v>
+        <v>445044</v>
       </c>
       <c r="R2" t="n">
-        <v>6811601</v>
+        <v>6811281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130237722</v>
+        <v>130237694</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445044</v>
+        <v>445036</v>
       </c>
       <c r="R3" t="n">
-        <v>6811281</v>
+        <v>6811601</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
         <v>130237743</v>
       </c>
       <c r="B4" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237712</v>
+        <v>130237745</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,42 +993,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445057</v>
+        <v>444954</v>
       </c>
       <c r="R5" t="n">
-        <v>6811437</v>
+        <v>6811588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237706</v>
+        <v>130237712</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445093</v>
+        <v>445057</v>
       </c>
       <c r="R6" t="n">
-        <v>6811481</v>
+        <v>6811437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130237691</v>
+        <v>130237706</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444991</v>
+        <v>445093</v>
       </c>
       <c r="R7" t="n">
-        <v>6811568</v>
+        <v>6811481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130237745</v>
+        <v>130237691</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1300,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444954</v>
+        <v>444991</v>
       </c>
       <c r="R8" t="n">
-        <v>6811588</v>
+        <v>6811568</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237724</v>
+        <v>130237738</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>78969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,42 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445064</v>
+        <v>445081</v>
       </c>
       <c r="R9" t="n">
-        <v>6811249</v>
+        <v>6811319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237738</v>
+        <v>130237692</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,34 +1502,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445081</v>
+        <v>445036</v>
       </c>
       <c r="R10" t="n">
-        <v>6811319</v>
+        <v>6811602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237777</v>
+        <v>130237724</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,34 +1607,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445058</v>
+        <v>445064</v>
       </c>
       <c r="R11" t="n">
-        <v>6811322</v>
+        <v>6811249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237692</v>
+        <v>130237705</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445036</v>
+        <v>445092</v>
       </c>
       <c r="R12" t="n">
-        <v>6811602</v>
+        <v>6811513</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237705</v>
+        <v>130237777</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,42 +1817,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445092</v>
+        <v>445058</v>
       </c>
       <c r="R13" t="n">
-        <v>6811513</v>
+        <v>6811322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,7 +1906,7 @@
         <v>130237749</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>130237663</v>
       </c>
       <c r="B15" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130237763</v>
+        <v>130237668</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445019</v>
+        <v>445044</v>
       </c>
       <c r="R16" t="n">
-        <v>6811423</v>
+        <v>6811305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130237668</v>
+        <v>130237763</v>
       </c>
       <c r="B17" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,21 +2205,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445044</v>
+        <v>445019</v>
       </c>
       <c r="R17" t="n">
-        <v>6811305</v>
+        <v>6811423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>130237733</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130237778</v>
+        <v>130237736</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>78969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,21 +2399,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445058</v>
+        <v>445078</v>
       </c>
       <c r="R19" t="n">
-        <v>6811265</v>
+        <v>6811349</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130237761</v>
+        <v>130237778</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445019</v>
+        <v>445058</v>
       </c>
       <c r="R20" t="n">
-        <v>6811345</v>
+        <v>6811265</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237693</v>
+        <v>130237667</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,42 +2593,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445027</v>
+        <v>445051</v>
       </c>
       <c r="R21" t="n">
-        <v>6811603</v>
+        <v>6811326</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130237714</v>
+        <v>130237761</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2698,42 +2690,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445083</v>
+        <v>445019</v>
       </c>
       <c r="R22" t="n">
-        <v>6811458</v>
+        <v>6811345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2776,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237667</v>
+        <v>130237693</v>
       </c>
       <c r="B23" t="n">
-        <v>79828</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,34 +2787,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445051</v>
+        <v>445027</v>
       </c>
       <c r="R23" t="n">
-        <v>6811326</v>
+        <v>6811603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130237736</v>
+        <v>130237714</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,34 +2892,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445078</v>
+        <v>445083</v>
       </c>
       <c r="R24" t="n">
-        <v>6811349</v>
+        <v>6811458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,53 +2986,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237677</v>
+        <v>130237744</v>
       </c>
       <c r="B25" t="n">
-        <v>57042</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445025</v>
+        <v>445002</v>
       </c>
       <c r="R25" t="n">
-        <v>6811296</v>
+        <v>6811503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3094,7 +3086,7 @@
         <v>130237723</v>
       </c>
       <c r="B26" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3196,45 +3188,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237744</v>
+        <v>130237677</v>
       </c>
       <c r="B27" t="n">
-        <v>78966</v>
+        <v>57044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445002</v>
+        <v>445025</v>
       </c>
       <c r="R27" t="n">
-        <v>6811503</v>
+        <v>6811296</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,7 +3296,7 @@
         <v>130237757</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>130237715</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>130237739</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130237748</v>
+        <v>130237737</v>
       </c>
       <c r="B31" t="n">
-        <v>78966</v>
+        <v>78969</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445075</v>
+        <v>445091</v>
       </c>
       <c r="R31" t="n">
-        <v>6811351</v>
+        <v>6811332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237765</v>
+        <v>130237748</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445089</v>
+        <v>445075</v>
       </c>
       <c r="R32" t="n">
-        <v>6811602</v>
+        <v>6811351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237737</v>
+        <v>130237765</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445091</v>
+        <v>445089</v>
       </c>
       <c r="R33" t="n">
-        <v>6811332</v>
+        <v>6811602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
         <v>130237775</v>
       </c>
       <c r="B34" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>130237707</v>
       </c>
       <c r="B35" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>130237719</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4194,45 +4194,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130237658</v>
+        <v>130237676</v>
       </c>
       <c r="B37" t="n">
-        <v>79828</v>
+        <v>57044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445098</v>
+        <v>445054</v>
       </c>
       <c r="R37" t="n">
-        <v>6811287</v>
+        <v>6811606</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,53 +4299,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130237676</v>
+        <v>130237658</v>
       </c>
       <c r="B38" t="n">
-        <v>57042</v>
+        <v>79830</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445054</v>
+        <v>445098</v>
       </c>
       <c r="R38" t="n">
-        <v>6811606</v>
+        <v>6811287</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4399,7 +4399,7 @@
         <v>130237764</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>130237779</v>
       </c>
       <c r="B40" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,53 +4590,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130237675</v>
+        <v>130237670</v>
       </c>
       <c r="B41" t="n">
-        <v>57042</v>
+        <v>79830</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445000</v>
+        <v>445045</v>
       </c>
       <c r="R41" t="n">
-        <v>6811614</v>
+        <v>6811267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4698,7 +4690,7 @@
         <v>130237669</v>
       </c>
       <c r="B42" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,45 +4784,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237670</v>
+        <v>130237675</v>
       </c>
       <c r="B43" t="n">
-        <v>79828</v>
+        <v>57044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445045</v>
+        <v>445000</v>
       </c>
       <c r="R43" t="n">
-        <v>6811267</v>
+        <v>6811614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4889,45 +4889,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130237671</v>
+        <v>130237750</v>
       </c>
       <c r="B44" t="n">
-        <v>79828</v>
+        <v>98953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445066</v>
+        <v>445085</v>
       </c>
       <c r="R44" t="n">
-        <v>6811213</v>
+        <v>6811515</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,12 +4966,18 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett hundratal plantor.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4989,7 +4999,7 @@
         <v>130237735</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,49 +5093,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130237750</v>
+        <v>130237671</v>
       </c>
       <c r="B46" t="n">
-        <v>98951</v>
+        <v>79830</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445085</v>
+        <v>445066</v>
       </c>
       <c r="R46" t="n">
-        <v>6811515</v>
+        <v>6811213</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5160,18 +5166,12 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ett hundratal plantor.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237708</v>
+        <v>130237734</v>
       </c>
       <c r="B47" t="n">
-        <v>57849</v>
+        <v>78969</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,31 +5201,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445066</v>
+        <v>444954</v>
       </c>
       <c r="R47" t="n">
-        <v>6811502</v>
+        <v>6811588</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5277,6 +5272,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5295,10 +5291,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237660</v>
+        <v>130237780</v>
       </c>
       <c r="B48" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5306,21 +5302,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5330,10 +5326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R48" t="n">
-        <v>6811440</v>
+        <v>6811223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,10 +5388,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237780</v>
+        <v>130237708</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5403,24 +5399,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
@@ -5430,7 +5434,7 @@
         <v>445066</v>
       </c>
       <c r="R49" t="n">
-        <v>6811223</v>
+        <v>6811502</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5489,10 +5493,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130237734</v>
+        <v>130237660</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>79830</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5500,37 +5504,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444954</v>
+        <v>444997</v>
       </c>
       <c r="R50" t="n">
-        <v>6811588</v>
+        <v>6811440</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5571,7 +5572,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>130237721</v>
       </c>
       <c r="B51" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5695,10 +5695,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130237710</v>
+        <v>130237704</v>
       </c>
       <c r="B52" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445064</v>
+        <v>445097</v>
       </c>
       <c r="R52" t="n">
-        <v>6811451</v>
+        <v>6811537</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130237704</v>
+        <v>130237710</v>
       </c>
       <c r="B53" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445097</v>
+        <v>445064</v>
       </c>
       <c r="R53" t="n">
-        <v>6811537</v>
+        <v>6811451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130237661</v>
+        <v>130237776</v>
       </c>
       <c r="B54" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,21 +5916,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444987</v>
+        <v>445092</v>
       </c>
       <c r="R54" t="n">
-        <v>6811482</v>
+        <v>6811332</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,10 +6002,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130237776</v>
+        <v>130237762</v>
       </c>
       <c r="B55" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445092</v>
+        <v>445021</v>
       </c>
       <c r="R55" t="n">
-        <v>6811332</v>
+        <v>6811394</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130237762</v>
+        <v>130237695</v>
       </c>
       <c r="B56" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6110,34 +6110,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445021</v>
+        <v>445073</v>
       </c>
       <c r="R56" t="n">
-        <v>6811394</v>
+        <v>6811597</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6196,10 +6204,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130237695</v>
+        <v>130237661</v>
       </c>
       <c r="B57" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6207,42 +6215,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445073</v>
+        <v>444987</v>
       </c>
       <c r="R57" t="n">
-        <v>6811597</v>
+        <v>6811482</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,53 +6301,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237679</v>
+        <v>130237760</v>
       </c>
       <c r="B58" t="n">
-        <v>57042</v>
+        <v>79211</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445036</v>
+        <v>445075</v>
       </c>
       <c r="R58" t="n">
-        <v>6811277</v>
+        <v>6811319</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6409,7 +6401,7 @@
         <v>130237725</v>
       </c>
       <c r="B59" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,32 +6503,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130237727</v>
+        <v>130237662</v>
       </c>
       <c r="B60" t="n">
-        <v>97822</v>
+        <v>79830</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6546,10 +6538,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445095</v>
+        <v>445002</v>
       </c>
       <c r="R60" t="n">
-        <v>6811427</v>
+        <v>6811503</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,45 +6600,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237760</v>
+        <v>130237679</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>57044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445075</v>
+        <v>445036</v>
       </c>
       <c r="R61" t="n">
-        <v>6811319</v>
+        <v>6811277</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130237662</v>
+        <v>130237727</v>
       </c>
       <c r="B62" t="n">
-        <v>79828</v>
+        <v>97824</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445002</v>
+        <v>445095</v>
       </c>
       <c r="R62" t="n">
-        <v>6811503</v>
+        <v>6811427</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237711</v>
+        <v>130237713</v>
       </c>
       <c r="B63" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445054</v>
+        <v>445073</v>
       </c>
       <c r="R63" t="n">
-        <v>6811454</v>
+        <v>6811446</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237720</v>
+        <v>130237711</v>
       </c>
       <c r="B64" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445048</v>
+        <v>445054</v>
       </c>
       <c r="R64" t="n">
-        <v>6811299</v>
+        <v>6811454</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B65" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R65" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7117,10 +7117,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B66" t="n">
-        <v>79828</v>
+        <v>57851</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7128,34 +7128,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R66" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7214,10 +7222,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237713</v>
+        <v>130237664</v>
       </c>
       <c r="B67" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7225,42 +7233,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445073</v>
+        <v>444968</v>
       </c>
       <c r="R67" t="n">
-        <v>6811446</v>
+        <v>6811605</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
         <v>130237774</v>
       </c>
       <c r="B68" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>130237698</v>
       </c>
       <c r="B69" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>130237699</v>
       </c>
       <c r="B70" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130237690</v>
+        <v>130237769</v>
       </c>
       <c r="B71" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7637,42 +7637,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445103</v>
+        <v>445114</v>
       </c>
       <c r="R71" t="n">
-        <v>6811320</v>
+        <v>6811610</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7731,10 +7723,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130237769</v>
+        <v>130237716</v>
       </c>
       <c r="B72" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7742,34 +7734,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445114</v>
+        <v>445149</v>
       </c>
       <c r="R72" t="n">
-        <v>6811610</v>
+        <v>6811433</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,10 +7828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130237716</v>
+        <v>130237690</v>
       </c>
       <c r="B73" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445149</v>
+        <v>445103</v>
       </c>
       <c r="R73" t="n">
-        <v>6811433</v>
+        <v>6811320</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7936,7 +7936,7 @@
         <v>130237767</v>
       </c>
       <c r="B74" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>130237717</v>
       </c>
       <c r="B75" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>130237766</v>
       </c>
       <c r="B76" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>130237697</v>
       </c>
       <c r="B77" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>130237701</v>
       </c>
       <c r="B78" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8446,10 +8446,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130237700</v>
+        <v>130237747</v>
       </c>
       <c r="B79" t="n">
-        <v>57849</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8457,42 +8457,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445131</v>
+        <v>445113</v>
       </c>
       <c r="R79" t="n">
-        <v>6811529</v>
+        <v>6811388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8551,10 +8543,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130237747</v>
+        <v>130237700</v>
       </c>
       <c r="B80" t="n">
-        <v>78966</v>
+        <v>57851</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8562,34 +8554,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445113</v>
+        <v>445131</v>
       </c>
       <c r="R80" t="n">
-        <v>6811388</v>
+        <v>6811529</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8651,7 +8651,7 @@
         <v>130237771</v>
       </c>
       <c r="B81" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>130237703</v>
       </c>
       <c r="B82" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>130237746</v>
       </c>
       <c r="B83" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>130237772</v>
       </c>
       <c r="B84" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>130237768</v>
       </c>
       <c r="B85" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>130237702</v>
       </c>
       <c r="B86" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>130237770</v>
       </c>
       <c r="B88" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>130237759</v>
       </c>
       <c r="B89" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>130237665</v>
       </c>
       <c r="B90" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>130237666</v>
       </c>
       <c r="B91" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>130237726</v>
       </c>
       <c r="B92" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>130237773</v>
       </c>
       <c r="B93" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237696</v>
+        <v>130237758</v>
       </c>
       <c r="B94" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9951,42 +9951,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445118</v>
+        <v>445101</v>
       </c>
       <c r="R94" t="n">
-        <v>6811654</v>
+        <v>6811246</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,10 +10037,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130237718</v>
+        <v>130237696</v>
       </c>
       <c r="B95" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10088,10 +10080,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445116</v>
+        <v>445118</v>
       </c>
       <c r="R95" t="n">
-        <v>6811382</v>
+        <v>6811654</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10150,10 +10142,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237758</v>
+        <v>130237718</v>
       </c>
       <c r="B96" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10161,34 +10153,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445101</v>
+        <v>445116</v>
       </c>
       <c r="R96" t="n">
-        <v>6811246</v>
+        <v>6811382</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10250,7 +10250,7 @@
         <v>130237659</v>
       </c>
       <c r="B97" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10344,10 +10344,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130250309</v>
+        <v>130250364</v>
       </c>
       <c r="B98" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10355,42 +10355,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445368</v>
+        <v>445309</v>
       </c>
       <c r="R98" t="n">
-        <v>6811354</v>
+        <v>6811605</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10449,10 +10441,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130250294</v>
+        <v>130250262</v>
       </c>
       <c r="B99" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10460,42 +10452,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445280</v>
+        <v>445333</v>
       </c>
       <c r="R99" t="n">
-        <v>6811472</v>
+        <v>6811312</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10554,10 +10538,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130250304</v>
+        <v>130250379</v>
       </c>
       <c r="B100" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10565,42 +10549,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445494</v>
+        <v>445369</v>
       </c>
       <c r="R100" t="n">
-        <v>6811338</v>
+        <v>6811508</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10659,10 +10635,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130250364</v>
+        <v>130250366</v>
       </c>
       <c r="B101" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10694,10 +10670,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445309</v>
+        <v>445328</v>
       </c>
       <c r="R101" t="n">
-        <v>6811605</v>
+        <v>6811603</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10756,10 +10732,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130250262</v>
+        <v>130250304</v>
       </c>
       <c r="B102" t="n">
-        <v>79828</v>
+        <v>57851</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10767,34 +10743,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445333</v>
+        <v>445494</v>
       </c>
       <c r="R102" t="n">
-        <v>6811312</v>
+        <v>6811338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10853,10 +10837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130250379</v>
+        <v>130250309</v>
       </c>
       <c r="B103" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10864,34 +10848,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445369</v>
+        <v>445368</v>
       </c>
       <c r="R103" t="n">
-        <v>6811508</v>
+        <v>6811354</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10950,10 +10942,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130250366</v>
+        <v>130250294</v>
       </c>
       <c r="B104" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10961,34 +10953,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445328</v>
+        <v>445280</v>
       </c>
       <c r="R104" t="n">
-        <v>6811603</v>
+        <v>6811472</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11050,7 +11050,7 @@
         <v>130250267</v>
       </c>
       <c r="B105" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>130250343</v>
       </c>
       <c r="B106" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>130250373</v>
       </c>
       <c r="B107" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>130250401</v>
       </c>
       <c r="B108" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>130250409</v>
       </c>
       <c r="B109" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>130250261</v>
       </c>
       <c r="B110" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>130250402</v>
       </c>
       <c r="B111" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11750,32 +11750,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130250270</v>
+        <v>130250302</v>
       </c>
       <c r="B112" t="n">
-        <v>57042</v>
+        <v>57851</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11783,7 +11783,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11793,10 +11793,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445426</v>
+        <v>445239</v>
       </c>
       <c r="R112" t="n">
-        <v>6811491</v>
+        <v>6811358</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11855,10 +11855,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130250272</v>
+        <v>130250270</v>
       </c>
       <c r="B113" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445468</v>
+        <v>445426</v>
       </c>
       <c r="R113" t="n">
-        <v>6811258</v>
+        <v>6811491</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11960,32 +11960,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130250302</v>
+        <v>130250272</v>
       </c>
       <c r="B114" t="n">
-        <v>57849</v>
+        <v>57044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11993,7 +11993,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445239</v>
+        <v>445468</v>
       </c>
       <c r="R114" t="n">
-        <v>6811358</v>
+        <v>6811258</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12068,7 +12068,7 @@
         <v>130250385</v>
       </c>
       <c r="B115" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>130250345</v>
       </c>
       <c r="B116" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>130250339</v>
       </c>
       <c r="B117" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>130250313</v>
       </c>
       <c r="B118" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>130250296</v>
       </c>
       <c r="B119" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>130250394</v>
       </c>
       <c r="B120" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>130250259</v>
       </c>
       <c r="B121" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>130250404</v>
       </c>
       <c r="B122" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>130250360</v>
       </c>
       <c r="B123" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>130250338</v>
       </c>
       <c r="B124" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>130250399</v>
       </c>
       <c r="B125" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>130250357</v>
       </c>
       <c r="B126" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>130250289</v>
       </c>
       <c r="B127" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13354,10 +13354,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250315</v>
+        <v>130250314</v>
       </c>
       <c r="B128" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445317</v>
+        <v>445322</v>
       </c>
       <c r="R128" t="n">
-        <v>6811271</v>
+        <v>6811309</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13459,10 +13459,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250314</v>
+        <v>130250293</v>
       </c>
       <c r="B129" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -13502,10 +13502,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445322</v>
+        <v>445303</v>
       </c>
       <c r="R129" t="n">
-        <v>6811309</v>
+        <v>6811490</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13564,10 +13564,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250293</v>
+        <v>130250315</v>
       </c>
       <c r="B130" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445303</v>
+        <v>445317</v>
       </c>
       <c r="R130" t="n">
-        <v>6811490</v>
+        <v>6811271</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13672,7 +13672,7 @@
         <v>130250255</v>
       </c>
       <c r="B131" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>130250321</v>
       </c>
       <c r="B132" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>130250251</v>
       </c>
       <c r="B133" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>130250374</v>
       </c>
       <c r="B134" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>130250361</v>
       </c>
       <c r="B135" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>130250390</v>
       </c>
       <c r="B136" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>130250369</v>
       </c>
       <c r="B137" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>130250356</v>
       </c>
       <c r="B138" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>130250269</v>
       </c>
       <c r="B139" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>130250273</v>
       </c>
       <c r="B140" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>130250275</v>
       </c>
       <c r="B141" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14760,10 +14760,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130250376</v>
+        <v>130250297</v>
       </c>
       <c r="B142" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14771,26 +14771,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -14798,10 +14803,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>445462</v>
+        <v>445239</v>
       </c>
       <c r="R142" t="n">
-        <v>6811495</v>
+        <v>6811474</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14842,7 +14847,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14861,10 +14865,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250362</v>
+        <v>130250292</v>
       </c>
       <c r="B143" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14872,34 +14876,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445218</v>
+        <v>445384</v>
       </c>
       <c r="R143" t="n">
-        <v>6811594</v>
+        <v>6811490</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14958,10 +14970,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250292</v>
+        <v>130250376</v>
       </c>
       <c r="B144" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14969,31 +14981,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -15001,10 +15008,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445384</v>
+        <v>445462</v>
       </c>
       <c r="R144" t="n">
-        <v>6811490</v>
+        <v>6811495</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15045,6 +15052,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15063,10 +15071,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250303</v>
+        <v>130250362</v>
       </c>
       <c r="B145" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15074,42 +15082,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445389</v>
+        <v>445218</v>
       </c>
       <c r="R145" t="n">
-        <v>6811264</v>
+        <v>6811594</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15168,10 +15168,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250297</v>
+        <v>130250303</v>
       </c>
       <c r="B146" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15211,10 +15211,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445239</v>
+        <v>445389</v>
       </c>
       <c r="R146" t="n">
-        <v>6811474</v>
+        <v>6811264</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15276,7 +15276,7 @@
         <v>130250274</v>
       </c>
       <c r="B147" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>130250271</v>
       </c>
       <c r="B148" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15483,10 +15483,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250323</v>
+        <v>130250328</v>
       </c>
       <c r="B149" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15518,10 +15518,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445371</v>
+        <v>445329</v>
       </c>
       <c r="R149" t="n">
-        <v>6811594</v>
+        <v>6811272</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15583,7 +15583,7 @@
         <v>130250266</v>
       </c>
       <c r="B150" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15677,10 +15677,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250328</v>
+        <v>130250323</v>
       </c>
       <c r="B151" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445329</v>
+        <v>445371</v>
       </c>
       <c r="R151" t="n">
-        <v>6811272</v>
+        <v>6811594</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15774,53 +15774,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130250276</v>
+        <v>130250381</v>
       </c>
       <c r="B152" t="n">
-        <v>57042</v>
+        <v>79211</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>445328</v>
+        <v>445351</v>
       </c>
       <c r="R152" t="n">
-        <v>6811392</v>
+        <v>6811495</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15879,49 +15871,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130250319</v>
+        <v>130250335</v>
       </c>
       <c r="B153" t="n">
-        <v>97828</v>
+        <v>78968</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>445554</v>
+        <v>445372</v>
       </c>
       <c r="R153" t="n">
-        <v>6811457</v>
+        <v>6811595</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15962,7 +15950,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -15981,10 +15968,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130250326</v>
+        <v>130250341</v>
       </c>
       <c r="B154" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15992,21 +15979,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16016,10 +16003,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>445235</v>
+        <v>445383</v>
       </c>
       <c r="R154" t="n">
-        <v>6811325</v>
+        <v>6811286</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16078,10 +16065,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130250329</v>
+        <v>130250336</v>
       </c>
       <c r="B155" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16089,21 +16076,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16113,10 +16100,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>445323</v>
+        <v>445413</v>
       </c>
       <c r="R155" t="n">
-        <v>6811270</v>
+        <v>6811568</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16175,10 +16162,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250381</v>
+        <v>130250317</v>
       </c>
       <c r="B156" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16186,34 +16173,42 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445351</v>
+        <v>445487</v>
       </c>
       <c r="R156" t="n">
-        <v>6811495</v>
+        <v>6811335</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16272,10 +16267,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130250335</v>
+        <v>130250286</v>
       </c>
       <c r="B157" t="n">
-        <v>78966</v>
+        <v>57851</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16283,34 +16278,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445372</v>
+        <v>445540</v>
       </c>
       <c r="R157" t="n">
-        <v>6811595</v>
+        <v>6811525</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16369,45 +16372,49 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130250341</v>
+        <v>130250319</v>
       </c>
       <c r="B158" t="n">
-        <v>78966</v>
+        <v>97830</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445383</v>
+        <v>445554</v>
       </c>
       <c r="R158" t="n">
-        <v>6811286</v>
+        <v>6811457</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16448,6 +16455,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16466,45 +16474,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130250336</v>
+        <v>130250276</v>
       </c>
       <c r="B159" t="n">
-        <v>78966</v>
+        <v>57044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445413</v>
+        <v>445328</v>
       </c>
       <c r="R159" t="n">
-        <v>6811568</v>
+        <v>6811392</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16563,10 +16579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130250286</v>
+        <v>130250326</v>
       </c>
       <c r="B160" t="n">
-        <v>57849</v>
+        <v>78969</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16574,42 +16590,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>445540</v>
+        <v>445235</v>
       </c>
       <c r="R160" t="n">
-        <v>6811525</v>
+        <v>6811325</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16668,10 +16676,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250317</v>
+        <v>130250329</v>
       </c>
       <c r="B161" t="n">
-        <v>57849</v>
+        <v>78969</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16679,42 +16687,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445487</v>
+        <v>445323</v>
       </c>
       <c r="R161" t="n">
-        <v>6811335</v>
+        <v>6811270</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16776,7 +16776,7 @@
         <v>130250340</v>
       </c>
       <c r="B162" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>130250248</v>
       </c>
       <c r="B163" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>130250391</v>
       </c>
       <c r="B164" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>130250398</v>
       </c>
       <c r="B165" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>130250371</v>
       </c>
       <c r="B166" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>130250342</v>
       </c>
       <c r="B167" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17355,10 +17355,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130250282</v>
+        <v>130250279</v>
       </c>
       <c r="B168" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17398,10 +17398,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>445213</v>
+        <v>445165</v>
       </c>
       <c r="R168" t="n">
-        <v>6811666</v>
+        <v>6811426</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17460,10 +17460,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130250279</v>
+        <v>130250287</v>
       </c>
       <c r="B169" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17503,10 +17503,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>445165</v>
+        <v>445575</v>
       </c>
       <c r="R169" t="n">
-        <v>6811426</v>
+        <v>6811437</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17565,10 +17565,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130250287</v>
+        <v>130250282</v>
       </c>
       <c r="B170" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17608,10 +17608,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>445575</v>
+        <v>445213</v>
       </c>
       <c r="R170" t="n">
-        <v>6811437</v>
+        <v>6811666</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17670,10 +17670,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130250290</v>
+        <v>130250347</v>
       </c>
       <c r="B171" t="n">
-        <v>57849</v>
+        <v>78968</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17681,42 +17681,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>445457</v>
+        <v>445334</v>
       </c>
       <c r="R171" t="n">
-        <v>6811507</v>
+        <v>6811304</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17775,10 +17767,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130250347</v>
+        <v>130250260</v>
       </c>
       <c r="B172" t="n">
-        <v>78966</v>
+        <v>79830</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17786,21 +17778,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17810,10 +17802,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>445334</v>
+        <v>445425</v>
       </c>
       <c r="R172" t="n">
-        <v>6811304</v>
+        <v>6811413</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17872,10 +17864,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130250260</v>
+        <v>130250388</v>
       </c>
       <c r="B173" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17883,21 +17875,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17907,10 +17899,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>445425</v>
+        <v>445362</v>
       </c>
       <c r="R173" t="n">
-        <v>6811413</v>
+        <v>6811289</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17969,10 +17961,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130250388</v>
+        <v>130250368</v>
       </c>
       <c r="B174" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18004,10 +17996,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>445362</v>
+        <v>445385</v>
       </c>
       <c r="R174" t="n">
-        <v>6811289</v>
+        <v>6811579</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18066,10 +18058,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130250368</v>
+        <v>130250396</v>
       </c>
       <c r="B175" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18101,10 +18093,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>445385</v>
+        <v>445480</v>
       </c>
       <c r="R175" t="n">
-        <v>6811579</v>
+        <v>6811420</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18163,10 +18155,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130250396</v>
+        <v>130250346</v>
       </c>
       <c r="B176" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18174,21 +18166,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18198,10 +18190,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>445480</v>
+        <v>445322</v>
       </c>
       <c r="R176" t="n">
-        <v>6811420</v>
+        <v>6811363</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18260,32 +18252,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250346</v>
+        <v>130250318</v>
       </c>
       <c r="B177" t="n">
-        <v>78966</v>
+        <v>97824</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18295,10 +18287,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445322</v>
+        <v>445180</v>
       </c>
       <c r="R177" t="n">
-        <v>6811363</v>
+        <v>6811418</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18357,32 +18349,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130250318</v>
+        <v>130250265</v>
       </c>
       <c r="B178" t="n">
-        <v>97822</v>
+        <v>79801</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18392,10 +18384,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>445180</v>
+        <v>445586</v>
       </c>
       <c r="R178" t="n">
-        <v>6811418</v>
+        <v>6811454</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18454,10 +18446,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130250265</v>
+        <v>130250290</v>
       </c>
       <c r="B179" t="n">
-        <v>79799</v>
+        <v>57851</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18465,34 +18457,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>445586</v>
+        <v>445457</v>
       </c>
       <c r="R179" t="n">
-        <v>6811454</v>
+        <v>6811507</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250406</v>
+        <v>130250325</v>
       </c>
       <c r="B180" t="n">
-        <v>79209</v>
+        <v>78969</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445341</v>
+        <v>445457</v>
       </c>
       <c r="R180" t="n">
-        <v>6811293</v>
+        <v>6811516</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250284</v>
+        <v>130250333</v>
       </c>
       <c r="B181" t="n">
-        <v>57849</v>
+        <v>78968</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,42 +18659,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445310</v>
+        <v>445201</v>
       </c>
       <c r="R181" t="n">
-        <v>6811604</v>
+        <v>6811621</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18753,10 +18745,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250311</v>
+        <v>130250344</v>
       </c>
       <c r="B182" t="n">
-        <v>57849</v>
+        <v>78968</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18764,42 +18756,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445333</v>
+        <v>445358</v>
       </c>
       <c r="R182" t="n">
-        <v>6811358</v>
+        <v>6811433</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18858,10 +18842,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250325</v>
+        <v>130250383</v>
       </c>
       <c r="B183" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18869,21 +18853,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18893,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445457</v>
+        <v>445209</v>
       </c>
       <c r="R183" t="n">
-        <v>6811516</v>
+        <v>6811451</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18955,10 +18939,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250333</v>
+        <v>130250406</v>
       </c>
       <c r="B184" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18966,21 +18950,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18990,10 +18974,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445201</v>
+        <v>445341</v>
       </c>
       <c r="R184" t="n">
-        <v>6811621</v>
+        <v>6811293</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19052,10 +19036,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250344</v>
+        <v>130250377</v>
       </c>
       <c r="B185" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19063,21 +19047,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19087,10 +19071,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445358</v>
+        <v>445454</v>
       </c>
       <c r="R185" t="n">
-        <v>6811433</v>
+        <v>6811502</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19149,10 +19133,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130250383</v>
+        <v>130250311</v>
       </c>
       <c r="B186" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19160,34 +19144,42 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>445209</v>
+        <v>445333</v>
       </c>
       <c r="R186" t="n">
-        <v>6811451</v>
+        <v>6811358</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19246,10 +19238,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>130250377</v>
+        <v>130250284</v>
       </c>
       <c r="B187" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19257,34 +19249,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>445454</v>
+        <v>445310</v>
       </c>
       <c r="R187" t="n">
-        <v>6811502</v>
+        <v>6811604</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19346,7 +19346,7 @@
         <v>130250257</v>
       </c>
       <c r="B188" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>130250363</v>
       </c>
       <c r="B189" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>130250312</v>
       </c>
       <c r="B190" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>130250306</v>
       </c>
       <c r="B191" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>130250268</v>
       </c>
       <c r="B192" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130250298</v>
+        <v>130250250</v>
       </c>
       <c r="B194" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19970,42 +19970,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445232</v>
+        <v>445248</v>
       </c>
       <c r="R194" t="n">
-        <v>6811448</v>
+        <v>6811642</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20064,10 +20056,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250281</v>
+        <v>130250370</v>
       </c>
       <c r="B195" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20075,42 +20067,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445205</v>
+        <v>445542</v>
       </c>
       <c r="R195" t="n">
-        <v>6811619</v>
+        <v>6811532</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20169,10 +20153,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250300</v>
+        <v>130250395</v>
       </c>
       <c r="B196" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20180,42 +20164,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445219</v>
+        <v>445507</v>
       </c>
       <c r="R196" t="n">
-        <v>6811344</v>
+        <v>6811412</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20274,10 +20250,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250291</v>
+        <v>130250256</v>
       </c>
       <c r="B197" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20285,42 +20261,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445385</v>
+        <v>445484</v>
       </c>
       <c r="R197" t="n">
-        <v>6811504</v>
+        <v>6811291</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20379,10 +20347,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250327</v>
+        <v>130250386</v>
       </c>
       <c r="B198" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20390,21 +20358,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20414,10 +20382,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445390</v>
+        <v>445226</v>
       </c>
       <c r="R198" t="n">
-        <v>6811275</v>
+        <v>6811348</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20476,10 +20444,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250250</v>
+        <v>130250298</v>
       </c>
       <c r="B199" t="n">
-        <v>79828</v>
+        <v>57851</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20487,34 +20455,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445248</v>
+        <v>445232</v>
       </c>
       <c r="R199" t="n">
-        <v>6811642</v>
+        <v>6811448</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20573,10 +20549,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250370</v>
+        <v>130250300</v>
       </c>
       <c r="B200" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20584,34 +20560,42 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445542</v>
+        <v>445219</v>
       </c>
       <c r="R200" t="n">
-        <v>6811532</v>
+        <v>6811344</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20670,10 +20654,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250395</v>
+        <v>130250291</v>
       </c>
       <c r="B201" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20681,34 +20665,42 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445507</v>
+        <v>445385</v>
       </c>
       <c r="R201" t="n">
-        <v>6811412</v>
+        <v>6811504</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20767,10 +20759,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250256</v>
+        <v>130250281</v>
       </c>
       <c r="B202" t="n">
-        <v>79828</v>
+        <v>57851</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20778,34 +20770,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445484</v>
+        <v>445205</v>
       </c>
       <c r="R202" t="n">
-        <v>6811291</v>
+        <v>6811619</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20864,45 +20864,53 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250386</v>
+        <v>130250355</v>
       </c>
       <c r="B203" t="n">
-        <v>79209</v>
+        <v>57846</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445226</v>
+        <v>445443</v>
       </c>
       <c r="R203" t="n">
-        <v>6811348</v>
+        <v>6811494</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20961,53 +20969,45 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250355</v>
+        <v>130250327</v>
       </c>
       <c r="B204" t="n">
-        <v>57844</v>
+        <v>78969</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445443</v>
+        <v>445390</v>
       </c>
       <c r="R204" t="n">
-        <v>6811494</v>
+        <v>6811275</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21069,7 +21069,7 @@
         <v>130250277</v>
       </c>
       <c r="B205" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>130250264</v>
       </c>
       <c r="B206" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>130250254</v>
       </c>
       <c r="B207" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>130250258</v>
       </c>
       <c r="B208" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>130250249</v>
       </c>
       <c r="B209" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>130250392</v>
       </c>
       <c r="B210" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>130250389</v>
       </c>
       <c r="B211" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>130250367</v>
       </c>
       <c r="B212" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>130250280</v>
       </c>
       <c r="B213" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21955,10 +21955,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B214" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R214" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,10 +22060,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250310</v>
+        <v>130250305</v>
       </c>
       <c r="B215" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445339</v>
+        <v>445448</v>
       </c>
       <c r="R215" t="n">
-        <v>6811359</v>
+        <v>6811432</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22168,7 +22168,7 @@
         <v>130250283</v>
       </c>
       <c r="B216" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>130250247</v>
       </c>
       <c r="B217" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>130250348</v>
       </c>
       <c r="B218" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>130250253</v>
       </c>
       <c r="B219" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>130250252</v>
       </c>
       <c r="B220" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>130250387</v>
       </c>
       <c r="B221" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>130250308</v>
       </c>
       <c r="B222" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22860,10 +22860,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130250299</v>
+        <v>130250307</v>
       </c>
       <c r="B223" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>445206</v>
+        <v>445373</v>
       </c>
       <c r="R223" t="n">
-        <v>6811400</v>
+        <v>6811417</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22965,10 +22965,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130250307</v>
+        <v>130250299</v>
       </c>
       <c r="B224" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23008,10 +23008,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>445373</v>
+        <v>445206</v>
       </c>
       <c r="R224" t="n">
-        <v>6811417</v>
+        <v>6811400</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23070,10 +23070,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130250400</v>
+        <v>130250334</v>
       </c>
       <c r="B225" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23081,21 +23081,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23105,10 +23105,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>445401</v>
+        <v>445266</v>
       </c>
       <c r="R225" t="n">
-        <v>6811451</v>
+        <v>6811642</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23167,10 +23167,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130250358</v>
+        <v>130250400</v>
       </c>
       <c r="B226" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23202,10 +23202,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>445154</v>
+        <v>445401</v>
       </c>
       <c r="R226" t="n">
-        <v>6811359</v>
+        <v>6811451</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23264,10 +23264,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130250263</v>
+        <v>130250358</v>
       </c>
       <c r="B227" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23275,21 +23275,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23299,10 +23299,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>445321</v>
+        <v>445154</v>
       </c>
       <c r="R227" t="n">
-        <v>6811263</v>
+        <v>6811359</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23361,10 +23361,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130250372</v>
+        <v>130250263</v>
       </c>
       <c r="B228" t="n">
-        <v>79209</v>
+        <v>79830</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23372,37 +23372,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>445578</v>
+        <v>445321</v>
       </c>
       <c r="R228" t="n">
-        <v>6811455</v>
+        <v>6811263</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23443,7 +23440,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23462,10 +23458,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130250334</v>
+        <v>130250382</v>
       </c>
       <c r="B229" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23473,21 +23469,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23497,10 +23493,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>445266</v>
+        <v>445218</v>
       </c>
       <c r="R229" t="n">
-        <v>6811642</v>
+        <v>6811435</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23559,10 +23555,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130250382</v>
+        <v>130250372</v>
       </c>
       <c r="B230" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23588,16 +23584,19 @@
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>445218</v>
+        <v>445578</v>
       </c>
       <c r="R230" t="n">
-        <v>6811435</v>
+        <v>6811455</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23638,6 +23637,7 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
@@ -23659,7 +23659,7 @@
         <v>130250285</v>
       </c>
       <c r="B231" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130250393</v>
+        <v>130250301</v>
       </c>
       <c r="B232" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23772,34 +23772,42 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>445477</v>
+        <v>445222</v>
       </c>
       <c r="R232" t="n">
-        <v>6811356</v>
+        <v>6811352</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23858,10 +23866,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130250380</v>
+        <v>130250288</v>
       </c>
       <c r="B233" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23869,34 +23877,42 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>445369</v>
+        <v>445564</v>
       </c>
       <c r="R233" t="n">
-        <v>6811486</v>
+        <v>6811446</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23955,10 +23971,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130250408</v>
+        <v>130250316</v>
       </c>
       <c r="B234" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23966,34 +23982,42 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445323</v>
+        <v>445524</v>
       </c>
       <c r="R234" t="n">
-        <v>6811251</v>
+        <v>6811486</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24052,10 +24076,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130250246</v>
+        <v>130250393</v>
       </c>
       <c r="B235" t="n">
-        <v>79828</v>
+        <v>79211</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24063,21 +24087,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24087,10 +24111,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>445182</v>
+        <v>445477</v>
       </c>
       <c r="R235" t="n">
-        <v>6811329</v>
+        <v>6811356</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24149,10 +24173,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130250405</v>
+        <v>130250380</v>
       </c>
       <c r="B236" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24184,10 +24208,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>445324</v>
+        <v>445369</v>
       </c>
       <c r="R236" t="n">
-        <v>6811291</v>
+        <v>6811486</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24246,10 +24270,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130250397</v>
+        <v>130250408</v>
       </c>
       <c r="B237" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24281,10 +24305,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>445441</v>
+        <v>445323</v>
       </c>
       <c r="R237" t="n">
-        <v>6811411</v>
+        <v>6811251</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24343,10 +24367,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130250316</v>
+        <v>130250246</v>
       </c>
       <c r="B238" t="n">
-        <v>57849</v>
+        <v>79830</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24354,42 +24378,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>445524</v>
+        <v>445182</v>
       </c>
       <c r="R238" t="n">
-        <v>6811486</v>
+        <v>6811329</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24448,10 +24464,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130250301</v>
+        <v>130250405</v>
       </c>
       <c r="B239" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24459,42 +24475,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>445222</v>
+        <v>445324</v>
       </c>
       <c r="R239" t="n">
-        <v>6811352</v>
+        <v>6811291</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24553,10 +24561,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130250288</v>
+        <v>130250397</v>
       </c>
       <c r="B240" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24564,42 +24572,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>445564</v>
+        <v>445441</v>
       </c>
       <c r="R240" t="n">
-        <v>6811446</v>
+        <v>6811411</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24661,7 +24661,7 @@
         <v>130250324</v>
       </c>
       <c r="B241" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>130250337</v>
       </c>
       <c r="B242" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>130250384</v>
       </c>
       <c r="B243" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>130250375</v>
       </c>
       <c r="B244" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>130250378</v>
       </c>
       <c r="B245" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>130250407</v>
       </c>
       <c r="B246" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>130250403</v>
       </c>
       <c r="B247" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>130250359</v>
       </c>
       <c r="B248" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>130250295</v>
       </c>
       <c r="B249" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>130250353</v>
       </c>
       <c r="B250" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130237722</v>
+        <v>130237694</v>
       </c>
       <c r="B2" t="n">
         <v>57851</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445044</v>
+        <v>445036</v>
       </c>
       <c r="R2" t="n">
-        <v>6811281</v>
+        <v>6811601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130237694</v>
+        <v>130237722</v>
       </c>
       <c r="B3" t="n">
         <v>57851</v>
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445036</v>
+        <v>445044</v>
       </c>
       <c r="R3" t="n">
-        <v>6811601</v>
+        <v>6811281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130237743</v>
+        <v>130237691</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +896,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445095</v>
+        <v>444991</v>
       </c>
       <c r="R4" t="n">
-        <v>6811230</v>
+        <v>6811568</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237745</v>
+        <v>130237743</v>
       </c>
       <c r="B5" t="n">
         <v>78968</v>
@@ -1017,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444954</v>
+        <v>445095</v>
       </c>
       <c r="R5" t="n">
-        <v>6811588</v>
+        <v>6811230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237712</v>
+        <v>130237745</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,42 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445057</v>
+        <v>444954</v>
       </c>
       <c r="R6" t="n">
-        <v>6811437</v>
+        <v>6811588</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130237691</v>
+        <v>130237712</v>
       </c>
       <c r="B8" t="n">
         <v>57851</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444991</v>
+        <v>445057</v>
       </c>
       <c r="R8" t="n">
-        <v>6811568</v>
+        <v>6811437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237692</v>
+        <v>130237663</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,42 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445036</v>
+        <v>444954</v>
       </c>
       <c r="R10" t="n">
-        <v>6811602</v>
+        <v>6811588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1588,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237724</v>
+        <v>130237692</v>
       </c>
       <c r="B11" t="n">
         <v>57851</v>
@@ -1639,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445064</v>
+        <v>445036</v>
       </c>
       <c r="R11" t="n">
-        <v>6811249</v>
+        <v>6811602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237705</v>
+        <v>130237724</v>
       </c>
       <c r="B12" t="n">
         <v>57851</v>
@@ -1744,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445092</v>
+        <v>445064</v>
       </c>
       <c r="R12" t="n">
-        <v>6811513</v>
+        <v>6811249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237777</v>
+        <v>130237705</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,34 +1809,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445058</v>
+        <v>445092</v>
       </c>
       <c r="R13" t="n">
-        <v>6811322</v>
+        <v>6811513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130237749</v>
+        <v>130237777</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,21 +1914,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445027</v>
+        <v>445058</v>
       </c>
       <c r="R14" t="n">
-        <v>6811319</v>
+        <v>6811322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237663</v>
+        <v>130237749</v>
       </c>
       <c r="B15" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444954</v>
+        <v>445027</v>
       </c>
       <c r="R15" t="n">
-        <v>6811588</v>
+        <v>6811319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130237668</v>
+        <v>130237763</v>
       </c>
       <c r="B16" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445044</v>
+        <v>445019</v>
       </c>
       <c r="R16" t="n">
-        <v>6811305</v>
+        <v>6811423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130237763</v>
+        <v>130237668</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,21 +2205,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445019</v>
+        <v>445044</v>
       </c>
       <c r="R17" t="n">
-        <v>6811423</v>
+        <v>6811305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130237736</v>
+        <v>130237714</v>
       </c>
       <c r="B19" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,34 +2399,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445078</v>
+        <v>445083</v>
       </c>
       <c r="R19" t="n">
-        <v>6811349</v>
+        <v>6811458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237667</v>
+        <v>130237761</v>
       </c>
       <c r="B21" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2601,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445051</v>
+        <v>445019</v>
       </c>
       <c r="R21" t="n">
-        <v>6811326</v>
+        <v>6811345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,10 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130237761</v>
+        <v>130237693</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2690,34 +2698,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445019</v>
+        <v>445027</v>
       </c>
       <c r="R22" t="n">
-        <v>6811345</v>
+        <v>6811603</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237693</v>
+        <v>130237667</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2787,42 +2803,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445027</v>
+        <v>445051</v>
       </c>
       <c r="R23" t="n">
-        <v>6811603</v>
+        <v>6811326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2881,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130237714</v>
+        <v>130237736</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2892,42 +2900,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445083</v>
+        <v>445078</v>
       </c>
       <c r="R24" t="n">
-        <v>6811458</v>
+        <v>6811349</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237744</v>
+        <v>130237723</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,34 +2997,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445002</v>
+        <v>445063</v>
       </c>
       <c r="R25" t="n">
-        <v>6811503</v>
+        <v>6811256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3083,32 +3091,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237723</v>
+        <v>130237677</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,7 +3124,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3126,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445063</v>
+        <v>445025</v>
       </c>
       <c r="R26" t="n">
-        <v>6811256</v>
+        <v>6811296</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,53 +3196,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237677</v>
+        <v>130237744</v>
       </c>
       <c r="B27" t="n">
-        <v>57044</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445025</v>
+        <v>445002</v>
       </c>
       <c r="R27" t="n">
-        <v>6811296</v>
+        <v>6811503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130237737</v>
+        <v>130237748</v>
       </c>
       <c r="B31" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445091</v>
+        <v>445075</v>
       </c>
       <c r="R31" t="n">
-        <v>6811332</v>
+        <v>6811351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237748</v>
+        <v>130237765</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445075</v>
+        <v>445089</v>
       </c>
       <c r="R32" t="n">
-        <v>6811351</v>
+        <v>6811602</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237765</v>
+        <v>130237737</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445089</v>
+        <v>445091</v>
       </c>
       <c r="R33" t="n">
-        <v>6811602</v>
+        <v>6811332</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130237707</v>
+        <v>130237719</v>
       </c>
       <c r="B35" t="n">
         <v>57851</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445074</v>
+        <v>445094</v>
       </c>
       <c r="R35" t="n">
-        <v>6811505</v>
+        <v>6811360</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130237719</v>
+        <v>130237707</v>
       </c>
       <c r="B36" t="n">
         <v>57851</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445094</v>
+        <v>445074</v>
       </c>
       <c r="R36" t="n">
-        <v>6811360</v>
+        <v>6811505</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,53 +4194,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130237676</v>
+        <v>130237658</v>
       </c>
       <c r="B37" t="n">
-        <v>57044</v>
+        <v>79830</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445054</v>
+        <v>445098</v>
       </c>
       <c r="R37" t="n">
-        <v>6811606</v>
+        <v>6811287</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4299,45 +4291,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130237658</v>
+        <v>130237676</v>
       </c>
       <c r="B38" t="n">
-        <v>79830</v>
+        <v>57044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445098</v>
+        <v>445054</v>
       </c>
       <c r="R38" t="n">
-        <v>6811287</v>
+        <v>6811606</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,45 +4396,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130237764</v>
+        <v>130237675</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445011</v>
+        <v>445000</v>
       </c>
       <c r="R39" t="n">
-        <v>6811436</v>
+        <v>6811614</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,10 +4501,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130237779</v>
+        <v>130237670</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4504,21 +4512,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4528,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445067</v>
+        <v>445045</v>
       </c>
       <c r="R40" t="n">
-        <v>6811245</v>
+        <v>6811267</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,7 +4598,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130237670</v>
+        <v>130237669</v>
       </c>
       <c r="B41" t="n">
         <v>79830</v>
@@ -4625,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445045</v>
+        <v>445036</v>
       </c>
       <c r="R41" t="n">
-        <v>6811267</v>
+        <v>6811260</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4687,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130237669</v>
+        <v>130237764</v>
       </c>
       <c r="B42" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445036</v>
+        <v>445011</v>
       </c>
       <c r="R42" t="n">
-        <v>6811260</v>
+        <v>6811436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4784,53 +4792,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237675</v>
+        <v>130237779</v>
       </c>
       <c r="B43" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445000</v>
+        <v>445067</v>
       </c>
       <c r="R43" t="n">
-        <v>6811614</v>
+        <v>6811245</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4892,7 +4892,7 @@
         <v>130237750</v>
       </c>
       <c r="B44" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237734</v>
+        <v>130237660</v>
       </c>
       <c r="B47" t="n">
-        <v>78969</v>
+        <v>79830</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,37 +5201,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444954</v>
+        <v>444997</v>
       </c>
       <c r="R47" t="n">
-        <v>6811588</v>
+        <v>6811440</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5272,7 +5269,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5291,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237780</v>
+        <v>130237708</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5302,24 +5298,32 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
@@ -5329,7 +5333,7 @@
         <v>445066</v>
       </c>
       <c r="R48" t="n">
-        <v>6811223</v>
+        <v>6811502</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5388,10 +5392,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237708</v>
+        <v>130237780</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5399,32 +5403,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
@@ -5434,7 +5430,7 @@
         <v>445066</v>
       </c>
       <c r="R49" t="n">
-        <v>6811502</v>
+        <v>6811223</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5493,10 +5489,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130237660</v>
+        <v>130237734</v>
       </c>
       <c r="B50" t="n">
-        <v>79830</v>
+        <v>78969</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5504,34 +5500,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444997</v>
+        <v>444954</v>
       </c>
       <c r="R50" t="n">
-        <v>6811440</v>
+        <v>6811588</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5572,6 +5571,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130237704</v>
+        <v>130237710</v>
       </c>
       <c r="B52" t="n">
         <v>57851</v>
@@ -5728,7 +5728,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445097</v>
+        <v>445064</v>
       </c>
       <c r="R52" t="n">
-        <v>6811537</v>
+        <v>6811451</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130237710</v>
+        <v>130237704</v>
       </c>
       <c r="B53" t="n">
         <v>57851</v>
@@ -5833,7 +5833,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445064</v>
+        <v>445097</v>
       </c>
       <c r="R53" t="n">
-        <v>6811451</v>
+        <v>6811537</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237760</v>
+        <v>130237725</v>
       </c>
       <c r="B58" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6312,34 +6312,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445075</v>
+        <v>445073</v>
       </c>
       <c r="R58" t="n">
-        <v>6811319</v>
+        <v>6811522</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6398,32 +6406,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130237725</v>
+        <v>130237679</v>
       </c>
       <c r="B59" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6431,7 +6439,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6441,10 +6449,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445073</v>
+        <v>445036</v>
       </c>
       <c r="R59" t="n">
-        <v>6811522</v>
+        <v>6811277</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,53 +6608,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237679</v>
+        <v>130237760</v>
       </c>
       <c r="B61" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445036</v>
+        <v>445075</v>
       </c>
       <c r="R61" t="n">
-        <v>6811277</v>
+        <v>6811319</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
         <v>130237727</v>
       </c>
       <c r="B62" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237713</v>
+        <v>130237664</v>
       </c>
       <c r="B63" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,42 +6813,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445073</v>
+        <v>444968</v>
       </c>
       <c r="R63" t="n">
-        <v>6811446</v>
+        <v>6811605</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,7 +6899,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237711</v>
+        <v>130237713</v>
       </c>
       <c r="B64" t="n">
         <v>57851</v>
@@ -6940,7 +6932,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -6950,10 +6942,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445054</v>
+        <v>445073</v>
       </c>
       <c r="R64" t="n">
-        <v>6811454</v>
+        <v>6811446</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7012,7 +7004,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237720</v>
+        <v>130237711</v>
       </c>
       <c r="B65" t="n">
         <v>57851</v>
@@ -7045,7 +7037,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7055,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445048</v>
+        <v>445054</v>
       </c>
       <c r="R65" t="n">
-        <v>6811299</v>
+        <v>6811454</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7117,7 +7109,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B66" t="n">
         <v>57851</v>
@@ -7150,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7160,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R66" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7222,10 +7214,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B67" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,34 +7225,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R67" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130237769</v>
+        <v>130237716</v>
       </c>
       <c r="B71" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7637,34 +7637,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445114</v>
+        <v>445149</v>
       </c>
       <c r="R71" t="n">
-        <v>6811610</v>
+        <v>6811433</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7723,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130237716</v>
+        <v>130237769</v>
       </c>
       <c r="B72" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7734,42 +7742,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445149</v>
+        <v>445114</v>
       </c>
       <c r="R72" t="n">
-        <v>6811433</v>
+        <v>6811610</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8648,10 +8648,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130237771</v>
+        <v>130237746</v>
       </c>
       <c r="B81" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8659,21 +8659,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445159</v>
+        <v>445153</v>
       </c>
       <c r="R81" t="n">
-        <v>6811562</v>
+        <v>6811549</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130237703</v>
+        <v>130237771</v>
       </c>
       <c r="B82" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8756,42 +8756,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445132</v>
+        <v>445159</v>
       </c>
       <c r="R82" t="n">
-        <v>6811535</v>
+        <v>6811562</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8850,10 +8842,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130237746</v>
+        <v>130237703</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8861,34 +8853,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445153</v>
+        <v>445132</v>
       </c>
       <c r="R83" t="n">
-        <v>6811549</v>
+        <v>6811535</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130237768</v>
+        <v>130237702</v>
       </c>
       <c r="B85" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9055,34 +9055,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445145</v>
+        <v>445137</v>
       </c>
       <c r="R85" t="n">
-        <v>6811638</v>
+        <v>6811505</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9141,40 +9149,41 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130237702</v>
+        <v>130237782</v>
       </c>
       <c r="B86" t="n">
-        <v>57851</v>
+        <v>8440</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9184,10 +9193,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445137</v>
+        <v>445142</v>
       </c>
       <c r="R86" t="n">
-        <v>6811505</v>
+        <v>6811431</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9228,6 +9237,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9246,54 +9256,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130237782</v>
+        <v>130237768</v>
       </c>
       <c r="B87" t="n">
-        <v>8440</v>
+        <v>79211</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445142</v>
+        <v>445145</v>
       </c>
       <c r="R87" t="n">
-        <v>6811431</v>
+        <v>6811638</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,7 +9335,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>130237726</v>
       </c>
       <c r="B92" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237758</v>
+        <v>130237718</v>
       </c>
       <c r="B94" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9951,34 +9951,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445101</v>
+        <v>445116</v>
       </c>
       <c r="R94" t="n">
-        <v>6811246</v>
+        <v>6811382</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10142,10 +10150,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237718</v>
+        <v>130237758</v>
       </c>
       <c r="B96" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10153,42 +10161,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445116</v>
+        <v>445101</v>
       </c>
       <c r="R96" t="n">
-        <v>6811382</v>
+        <v>6811246</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11047,10 +11047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250267</v>
+        <v>130250302</v>
       </c>
       <c r="B105" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,26 +11058,31 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11085,10 +11090,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445503</v>
+        <v>445239</v>
       </c>
       <c r="R105" t="n">
-        <v>6811332</v>
+        <v>6811358</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11129,29 +11134,8 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11750,10 +11734,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130250302</v>
+        <v>130250267</v>
       </c>
       <c r="B112" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11761,31 +11745,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11793,10 +11772,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445239</v>
+        <v>445503</v>
       </c>
       <c r="R112" t="n">
-        <v>6811358</v>
+        <v>6811332</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11837,8 +11816,29 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12259,10 +12259,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130250339</v>
+        <v>130250296</v>
       </c>
       <c r="B117" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12270,34 +12270,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445457</v>
+        <v>445240</v>
       </c>
       <c r="R117" t="n">
-        <v>6811516</v>
+        <v>6811502</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12356,10 +12364,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130250313</v>
+        <v>130250339</v>
       </c>
       <c r="B118" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12367,42 +12375,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445334</v>
+        <v>445457</v>
       </c>
       <c r="R118" t="n">
-        <v>6811325</v>
+        <v>6811516</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12461,7 +12461,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130250296</v>
+        <v>130250313</v>
       </c>
       <c r="B119" t="n">
         <v>57851</v>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445240</v>
+        <v>445334</v>
       </c>
       <c r="R119" t="n">
-        <v>6811502</v>
+        <v>6811325</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250394</v>
+        <v>130250314</v>
       </c>
       <c r="B120" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12577,26 +12577,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -12604,10 +12609,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445495</v>
+        <v>445322</v>
       </c>
       <c r="R120" t="n">
-        <v>6811385</v>
+        <v>6811309</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12648,7 +12653,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12667,10 +12671,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250259</v>
+        <v>130250394</v>
       </c>
       <c r="B121" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12678,34 +12682,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445441</v>
+        <v>445495</v>
       </c>
       <c r="R121" t="n">
-        <v>6811433</v>
+        <v>6811385</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12746,6 +12753,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12764,10 +12772,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250404</v>
+        <v>130250259</v>
       </c>
       <c r="B122" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12775,21 +12783,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12799,10 +12807,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445330</v>
+        <v>445441</v>
       </c>
       <c r="R122" t="n">
-        <v>6811333</v>
+        <v>6811433</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12861,7 +12869,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250360</v>
+        <v>130250404</v>
       </c>
       <c r="B123" t="n">
         <v>79211</v>
@@ -12896,10 +12904,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445194</v>
+        <v>445330</v>
       </c>
       <c r="R123" t="n">
-        <v>6811530</v>
+        <v>6811333</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12958,10 +12966,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250338</v>
+        <v>130250360</v>
       </c>
       <c r="B124" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12969,21 +12977,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12993,10 +13001,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445492</v>
+        <v>445194</v>
       </c>
       <c r="R124" t="n">
-        <v>6811520</v>
+        <v>6811530</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13055,10 +13063,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250399</v>
+        <v>130250338</v>
       </c>
       <c r="B125" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13066,21 +13074,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13098,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445416</v>
+        <v>445492</v>
       </c>
       <c r="R125" t="n">
-        <v>6811445</v>
+        <v>6811520</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13152,7 +13160,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250357</v>
+        <v>130250399</v>
       </c>
       <c r="B126" t="n">
         <v>79211</v>
@@ -13187,10 +13195,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445165</v>
+        <v>445416</v>
       </c>
       <c r="R126" t="n">
-        <v>6811302</v>
+        <v>6811445</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13249,10 +13257,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250289</v>
+        <v>130250357</v>
       </c>
       <c r="B127" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13260,42 +13268,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445468</v>
+        <v>445165</v>
       </c>
       <c r="R127" t="n">
-        <v>6811500</v>
+        <v>6811302</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250314</v>
+        <v>130250289</v>
       </c>
       <c r="B128" t="n">
         <v>57851</v>
@@ -13387,7 +13387,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445322</v>
+        <v>445468</v>
       </c>
       <c r="R128" t="n">
-        <v>6811309</v>
+        <v>6811500</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130250255</v>
+        <v>130250321</v>
       </c>
       <c r="B131" t="n">
-        <v>79830</v>
+        <v>78969</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13680,21 +13680,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13704,10 +13704,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>445480</v>
+        <v>445326</v>
       </c>
       <c r="R131" t="n">
-        <v>6811273</v>
+        <v>6811613</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130250321</v>
+        <v>130250255</v>
       </c>
       <c r="B132" t="n">
-        <v>78969</v>
+        <v>79830</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13777,21 +13777,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>445326</v>
+        <v>445480</v>
       </c>
       <c r="R132" t="n">
-        <v>6811613</v>
+        <v>6811273</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130250390</v>
+        <v>130250369</v>
       </c>
       <c r="B136" t="n">
         <v>79211</v>
@@ -14189,10 +14189,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>445492</v>
+        <v>445518</v>
       </c>
       <c r="R136" t="n">
-        <v>6811299</v>
+        <v>6811539</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14251,7 +14251,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130250369</v>
+        <v>130250356</v>
       </c>
       <c r="B137" t="n">
         <v>79211</v>
@@ -14286,10 +14286,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>445518</v>
+        <v>445227</v>
       </c>
       <c r="R137" t="n">
-        <v>6811539</v>
+        <v>6811254</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14348,7 +14348,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130250356</v>
+        <v>130250390</v>
       </c>
       <c r="B138" t="n">
         <v>79211</v>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>445227</v>
+        <v>445492</v>
       </c>
       <c r="R138" t="n">
-        <v>6811254</v>
+        <v>6811299</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14760,10 +14760,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130250297</v>
+        <v>130250376</v>
       </c>
       <c r="B142" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14771,31 +14771,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -14803,10 +14798,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>445239</v>
+        <v>445462</v>
       </c>
       <c r="R142" t="n">
-        <v>6811474</v>
+        <v>6811495</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14847,6 +14842,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14865,10 +14861,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250292</v>
+        <v>130250362</v>
       </c>
       <c r="B143" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14876,42 +14872,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445384</v>
+        <v>445218</v>
       </c>
       <c r="R143" t="n">
-        <v>6811490</v>
+        <v>6811594</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14970,10 +14958,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250376</v>
+        <v>130250297</v>
       </c>
       <c r="B144" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14981,26 +14969,31 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -15008,10 +15001,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445462</v>
+        <v>445239</v>
       </c>
       <c r="R144" t="n">
-        <v>6811495</v>
+        <v>6811474</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15052,7 +15045,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15071,10 +15063,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250362</v>
+        <v>130250292</v>
       </c>
       <c r="B145" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15082,34 +15074,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445218</v>
+        <v>445384</v>
       </c>
       <c r="R145" t="n">
-        <v>6811594</v>
+        <v>6811490</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15483,7 +15483,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250328</v>
+        <v>130250323</v>
       </c>
       <c r="B149" t="n">
         <v>78969</v>
@@ -15518,10 +15518,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445329</v>
+        <v>445371</v>
       </c>
       <c r="R149" t="n">
-        <v>6811272</v>
+        <v>6811594</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15677,7 +15677,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250323</v>
+        <v>130250328</v>
       </c>
       <c r="B151" t="n">
         <v>78969</v>
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445371</v>
+        <v>445329</v>
       </c>
       <c r="R151" t="n">
-        <v>6811594</v>
+        <v>6811272</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16162,32 +16162,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250317</v>
+        <v>130250276</v>
       </c>
       <c r="B156" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16195,7 +16195,7 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -16205,10 +16205,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445487</v>
+        <v>445328</v>
       </c>
       <c r="R156" t="n">
-        <v>6811335</v>
+        <v>6811392</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16267,7 +16267,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130250286</v>
+        <v>130250317</v>
       </c>
       <c r="B157" t="n">
         <v>57851</v>
@@ -16300,7 +16300,7 @@
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -16310,10 +16310,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445540</v>
+        <v>445487</v>
       </c>
       <c r="R157" t="n">
-        <v>6811525</v>
+        <v>6811335</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16372,38 +16372,42 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130250319</v>
+        <v>130250286</v>
       </c>
       <c r="B158" t="n">
-        <v>97830</v>
+        <v>57851</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -16411,10 +16415,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445554</v>
+        <v>445540</v>
       </c>
       <c r="R158" t="n">
-        <v>6811457</v>
+        <v>6811525</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16455,7 +16459,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16474,53 +16477,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130250276</v>
+        <v>130250326</v>
       </c>
       <c r="B159" t="n">
-        <v>57044</v>
+        <v>78969</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445328</v>
+        <v>445235</v>
       </c>
       <c r="R159" t="n">
-        <v>6811392</v>
+        <v>6811325</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16579,7 +16574,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130250326</v>
+        <v>130250329</v>
       </c>
       <c r="B160" t="n">
         <v>78969</v>
@@ -16614,10 +16609,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>445235</v>
+        <v>445323</v>
       </c>
       <c r="R160" t="n">
-        <v>6811325</v>
+        <v>6811270</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16676,45 +16671,49 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250329</v>
+        <v>130250319</v>
       </c>
       <c r="B161" t="n">
-        <v>78969</v>
+        <v>97834</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445323</v>
+        <v>445554</v>
       </c>
       <c r="R161" t="n">
-        <v>6811270</v>
+        <v>6811457</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16755,6 +16754,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130250340</v>
+        <v>130250279</v>
       </c>
       <c r="B162" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16784,34 +16784,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>445366</v>
+        <v>445165</v>
       </c>
       <c r="R162" t="n">
-        <v>6811298</v>
+        <v>6811426</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16870,10 +16878,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130250248</v>
+        <v>130250340</v>
       </c>
       <c r="B163" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16881,21 +16889,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16905,10 +16913,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>445243</v>
+        <v>445366</v>
       </c>
       <c r="R163" t="n">
-        <v>6811593</v>
+        <v>6811298</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17064,10 +17072,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130250398</v>
+        <v>130250248</v>
       </c>
       <c r="B165" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17075,21 +17083,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17099,10 +17107,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>445426</v>
+        <v>445243</v>
       </c>
       <c r="R165" t="n">
-        <v>6811434</v>
+        <v>6811593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17161,7 +17169,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130250371</v>
+        <v>130250398</v>
       </c>
       <c r="B166" t="n">
         <v>79211</v>
@@ -17196,10 +17204,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>445588</v>
+        <v>445426</v>
       </c>
       <c r="R166" t="n">
-        <v>6811455</v>
+        <v>6811434</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17258,10 +17266,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130250342</v>
+        <v>130250371</v>
       </c>
       <c r="B167" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17269,21 +17277,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17293,10 +17301,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>445390</v>
+        <v>445588</v>
       </c>
       <c r="R167" t="n">
-        <v>6811275</v>
+        <v>6811455</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17355,10 +17363,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130250279</v>
+        <v>130250342</v>
       </c>
       <c r="B168" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17366,42 +17374,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>445165</v>
+        <v>445390</v>
       </c>
       <c r="R168" t="n">
-        <v>6811426</v>
+        <v>6811275</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18252,45 +18252,53 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250318</v>
+        <v>130250290</v>
       </c>
       <c r="B177" t="n">
-        <v>97824</v>
+        <v>57851</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445180</v>
+        <v>445457</v>
       </c>
       <c r="R177" t="n">
-        <v>6811418</v>
+        <v>6811507</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18349,32 +18357,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130250265</v>
+        <v>130250318</v>
       </c>
       <c r="B178" t="n">
-        <v>79801</v>
+        <v>97828</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18384,10 +18392,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>445586</v>
+        <v>445180</v>
       </c>
       <c r="R178" t="n">
-        <v>6811454</v>
+        <v>6811418</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18446,10 +18454,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130250290</v>
+        <v>130250265</v>
       </c>
       <c r="B179" t="n">
-        <v>57851</v>
+        <v>79801</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18457,42 +18465,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>445457</v>
+        <v>445586</v>
       </c>
       <c r="R179" t="n">
-        <v>6811507</v>
+        <v>6811454</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250325</v>
+        <v>130250406</v>
       </c>
       <c r="B180" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445457</v>
+        <v>445341</v>
       </c>
       <c r="R180" t="n">
-        <v>6811516</v>
+        <v>6811293</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250333</v>
+        <v>130250377</v>
       </c>
       <c r="B181" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,21 +18659,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445201</v>
+        <v>445454</v>
       </c>
       <c r="R181" t="n">
-        <v>6811621</v>
+        <v>6811502</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,10 +18745,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250344</v>
+        <v>130250325</v>
       </c>
       <c r="B182" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18756,21 +18756,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18780,10 +18780,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445358</v>
+        <v>445457</v>
       </c>
       <c r="R182" t="n">
-        <v>6811433</v>
+        <v>6811516</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,10 +18842,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250383</v>
+        <v>130250333</v>
       </c>
       <c r="B183" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18853,21 +18853,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445209</v>
+        <v>445201</v>
       </c>
       <c r="R183" t="n">
-        <v>6811451</v>
+        <v>6811621</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,10 +18939,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250406</v>
+        <v>130250344</v>
       </c>
       <c r="B184" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18950,21 +18950,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18974,10 +18974,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445341</v>
+        <v>445358</v>
       </c>
       <c r="R184" t="n">
-        <v>6811293</v>
+        <v>6811433</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19036,7 +19036,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250377</v>
+        <v>130250383</v>
       </c>
       <c r="B185" t="n">
         <v>79211</v>
@@ -19071,10 +19071,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445454</v>
+        <v>445209</v>
       </c>
       <c r="R185" t="n">
-        <v>6811502</v>
+        <v>6811451</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19343,10 +19343,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>130250257</v>
+        <v>130250312</v>
       </c>
       <c r="B188" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19354,34 +19354,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>445474</v>
+        <v>445324</v>
       </c>
       <c r="R188" t="n">
-        <v>6811433</v>
+        <v>6811362</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19440,45 +19448,54 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>130250363</v>
+        <v>130250330</v>
       </c>
       <c r="B189" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>445229</v>
+        <v>445218</v>
       </c>
       <c r="R189" t="n">
-        <v>6811687</v>
+        <v>6811247</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19519,6 +19536,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -19537,10 +19555,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130250312</v>
+        <v>130250257</v>
       </c>
       <c r="B190" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19548,42 +19566,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>445324</v>
+        <v>445474</v>
       </c>
       <c r="R190" t="n">
-        <v>6811362</v>
+        <v>6811433</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19642,10 +19652,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130250306</v>
+        <v>130250363</v>
       </c>
       <c r="B191" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19653,42 +19663,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>445401</v>
+        <v>445229</v>
       </c>
       <c r="R191" t="n">
-        <v>6811439</v>
+        <v>6811687</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19747,10 +19749,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130250268</v>
+        <v>130250306</v>
       </c>
       <c r="B192" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19758,16 +19760,16 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19790,10 +19792,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>445421</v>
+        <v>445401</v>
       </c>
       <c r="R192" t="n">
-        <v>6811460</v>
+        <v>6811439</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19852,41 +19854,40 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130250330</v>
+        <v>130250268</v>
       </c>
       <c r="B193" t="n">
-        <v>8451</v>
+        <v>57854</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -19896,10 +19897,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>445218</v>
+        <v>445421</v>
       </c>
       <c r="R193" t="n">
-        <v>6811247</v>
+        <v>6811460</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19940,7 +19941,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -20056,7 +20056,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250370</v>
+        <v>130250395</v>
       </c>
       <c r="B195" t="n">
         <v>79211</v>
@@ -20091,10 +20091,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445542</v>
+        <v>445507</v>
       </c>
       <c r="R195" t="n">
-        <v>6811532</v>
+        <v>6811412</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20153,10 +20153,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250395</v>
+        <v>130250256</v>
       </c>
       <c r="B196" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20164,21 +20164,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20188,10 +20188,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445507</v>
+        <v>445484</v>
       </c>
       <c r="R196" t="n">
-        <v>6811412</v>
+        <v>6811291</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20250,10 +20250,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250256</v>
+        <v>130250298</v>
       </c>
       <c r="B197" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20261,34 +20261,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445484</v>
+        <v>445232</v>
       </c>
       <c r="R197" t="n">
-        <v>6811291</v>
+        <v>6811448</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20347,10 +20355,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250386</v>
+        <v>130250300</v>
       </c>
       <c r="B198" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20358,34 +20366,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445226</v>
+        <v>445219</v>
       </c>
       <c r="R198" t="n">
-        <v>6811348</v>
+        <v>6811344</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20444,7 +20460,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250298</v>
+        <v>130250291</v>
       </c>
       <c r="B199" t="n">
         <v>57851</v>
@@ -20487,10 +20503,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445232</v>
+        <v>445385</v>
       </c>
       <c r="R199" t="n">
-        <v>6811448</v>
+        <v>6811504</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20549,7 +20565,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250300</v>
+        <v>130250281</v>
       </c>
       <c r="B200" t="n">
         <v>57851</v>
@@ -20592,10 +20608,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445219</v>
+        <v>445205</v>
       </c>
       <c r="R200" t="n">
-        <v>6811344</v>
+        <v>6811619</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20654,32 +20670,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250291</v>
+        <v>130250355</v>
       </c>
       <c r="B201" t="n">
-        <v>57851</v>
+        <v>57846</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20687,7 +20703,7 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -20697,10 +20713,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445385</v>
+        <v>445443</v>
       </c>
       <c r="R201" t="n">
-        <v>6811504</v>
+        <v>6811494</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20759,32 +20775,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250281</v>
+        <v>130250277</v>
       </c>
       <c r="B202" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20792,7 +20808,7 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -20802,10 +20818,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445205</v>
+        <v>445202</v>
       </c>
       <c r="R202" t="n">
-        <v>6811619</v>
+        <v>6811655</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20864,53 +20880,45 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250355</v>
+        <v>130250327</v>
       </c>
       <c r="B203" t="n">
-        <v>57846</v>
+        <v>78969</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445443</v>
+        <v>445390</v>
       </c>
       <c r="R203" t="n">
-        <v>6811494</v>
+        <v>6811275</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20969,10 +20977,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250327</v>
+        <v>130250370</v>
       </c>
       <c r="B204" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20980,21 +20988,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21004,10 +21012,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445390</v>
+        <v>445542</v>
       </c>
       <c r="R204" t="n">
-        <v>6811275</v>
+        <v>6811532</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21066,53 +21074,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130250277</v>
+        <v>130250386</v>
       </c>
       <c r="B205" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>445202</v>
+        <v>445226</v>
       </c>
       <c r="R205" t="n">
-        <v>6811655</v>
+        <v>6811348</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250264</v>
+        <v>130250280</v>
       </c>
       <c r="B206" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,34 +21182,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445315</v>
+        <v>445179</v>
       </c>
       <c r="R206" t="n">
-        <v>6811230</v>
+        <v>6811467</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21268,10 +21276,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250254</v>
+        <v>130250305</v>
       </c>
       <c r="B207" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21279,34 +21287,42 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445194</v>
+        <v>445448</v>
       </c>
       <c r="R207" t="n">
-        <v>6811426</v>
+        <v>6811432</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21365,7 +21381,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250258</v>
+        <v>130250264</v>
       </c>
       <c r="B208" t="n">
         <v>79830</v>
@@ -21400,10 +21416,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445470</v>
+        <v>445315</v>
       </c>
       <c r="R208" t="n">
-        <v>6811435</v>
+        <v>6811230</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21462,7 +21478,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250249</v>
+        <v>130250254</v>
       </c>
       <c r="B209" t="n">
         <v>79830</v>
@@ -21497,10 +21513,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445200</v>
+        <v>445194</v>
       </c>
       <c r="R209" t="n">
-        <v>6811598</v>
+        <v>6811426</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21559,10 +21575,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250392</v>
+        <v>130250258</v>
       </c>
       <c r="B210" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21570,21 +21586,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21594,10 +21610,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445487</v>
+        <v>445470</v>
       </c>
       <c r="R210" t="n">
-        <v>6811345</v>
+        <v>6811435</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21656,10 +21672,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250389</v>
+        <v>130250249</v>
       </c>
       <c r="B211" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21667,21 +21683,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21691,10 +21707,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445483</v>
+        <v>445200</v>
       </c>
       <c r="R211" t="n">
-        <v>6811288</v>
+        <v>6811598</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21753,7 +21769,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250367</v>
+        <v>130250392</v>
       </c>
       <c r="B212" t="n">
         <v>79211</v>
@@ -21788,10 +21804,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445376</v>
+        <v>445487</v>
       </c>
       <c r="R212" t="n">
-        <v>6811581</v>
+        <v>6811345</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21850,10 +21866,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250280</v>
+        <v>130250389</v>
       </c>
       <c r="B213" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21861,42 +21877,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445179</v>
+        <v>445483</v>
       </c>
       <c r="R213" t="n">
-        <v>6811467</v>
+        <v>6811288</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21955,10 +21963,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250310</v>
+        <v>130250367</v>
       </c>
       <c r="B214" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21966,42 +21974,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445339</v>
+        <v>445376</v>
       </c>
       <c r="R214" t="n">
-        <v>6811359</v>
+        <v>6811581</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B215" t="n">
         <v>57851</v>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R215" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22270,10 +22270,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130250247</v>
+        <v>130250307</v>
       </c>
       <c r="B217" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22281,34 +22281,42 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>445188</v>
+        <v>445373</v>
       </c>
       <c r="R217" t="n">
-        <v>6811507</v>
+        <v>6811417</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22367,10 +22375,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130250348</v>
+        <v>130250247</v>
       </c>
       <c r="B218" t="n">
-        <v>78968</v>
+        <v>79830</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22378,21 +22386,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22402,10 +22410,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>445329</v>
+        <v>445188</v>
       </c>
       <c r="R218" t="n">
-        <v>6811272</v>
+        <v>6811507</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22464,10 +22472,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130250253</v>
+        <v>130250348</v>
       </c>
       <c r="B219" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22475,21 +22483,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22499,10 +22507,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>445543</v>
+        <v>445329</v>
       </c>
       <c r="R219" t="n">
-        <v>6811480</v>
+        <v>6811272</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22561,7 +22569,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130250252</v>
+        <v>130250253</v>
       </c>
       <c r="B220" t="n">
         <v>79830</v>
@@ -22596,10 +22604,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>445586</v>
+        <v>445543</v>
       </c>
       <c r="R220" t="n">
-        <v>6811454</v>
+        <v>6811480</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22658,10 +22666,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130250387</v>
+        <v>130250252</v>
       </c>
       <c r="B221" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22669,21 +22677,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22693,10 +22701,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>445238</v>
+        <v>445586</v>
       </c>
       <c r="R221" t="n">
-        <v>6811310</v>
+        <v>6811454</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22755,10 +22763,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130250308</v>
+        <v>130250387</v>
       </c>
       <c r="B222" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22766,42 +22774,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>445379</v>
+        <v>445238</v>
       </c>
       <c r="R222" t="n">
-        <v>6811376</v>
+        <v>6811310</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22860,7 +22860,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130250307</v>
+        <v>130250308</v>
       </c>
       <c r="B223" t="n">
         <v>57851</v>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>445373</v>
+        <v>445379</v>
       </c>
       <c r="R223" t="n">
-        <v>6811417</v>
+        <v>6811376</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130250301</v>
+        <v>130250393</v>
       </c>
       <c r="B232" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23772,42 +23772,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>445222</v>
+        <v>445477</v>
       </c>
       <c r="R232" t="n">
-        <v>6811352</v>
+        <v>6811356</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23866,10 +23858,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130250288</v>
+        <v>130250380</v>
       </c>
       <c r="B233" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23877,42 +23869,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>445564</v>
+        <v>445369</v>
       </c>
       <c r="R233" t="n">
-        <v>6811446</v>
+        <v>6811486</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23971,10 +23955,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130250316</v>
+        <v>130250408</v>
       </c>
       <c r="B234" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23982,42 +23966,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445524</v>
+        <v>445323</v>
       </c>
       <c r="R234" t="n">
-        <v>6811486</v>
+        <v>6811251</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24076,10 +24052,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130250393</v>
+        <v>130250246</v>
       </c>
       <c r="B235" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24087,21 +24063,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24111,10 +24087,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>445477</v>
+        <v>445182</v>
       </c>
       <c r="R235" t="n">
-        <v>6811356</v>
+        <v>6811329</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24173,7 +24149,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130250380</v>
+        <v>130250405</v>
       </c>
       <c r="B236" t="n">
         <v>79211</v>
@@ -24208,10 +24184,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>445369</v>
+        <v>445324</v>
       </c>
       <c r="R236" t="n">
-        <v>6811486</v>
+        <v>6811291</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24270,7 +24246,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130250408</v>
+        <v>130250397</v>
       </c>
       <c r="B237" t="n">
         <v>79211</v>
@@ -24305,10 +24281,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>445323</v>
+        <v>445441</v>
       </c>
       <c r="R237" t="n">
-        <v>6811251</v>
+        <v>6811411</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24367,10 +24343,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130250246</v>
+        <v>130250301</v>
       </c>
       <c r="B238" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24378,34 +24354,42 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>445182</v>
+        <v>445222</v>
       </c>
       <c r="R238" t="n">
-        <v>6811329</v>
+        <v>6811352</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24464,10 +24448,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130250405</v>
+        <v>130250288</v>
       </c>
       <c r="B239" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24475,34 +24459,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>445324</v>
+        <v>445564</v>
       </c>
       <c r="R239" t="n">
-        <v>6811291</v>
+        <v>6811446</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24561,10 +24553,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130250397</v>
+        <v>130250316</v>
       </c>
       <c r="B240" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24572,34 +24564,42 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>445441</v>
+        <v>445524</v>
       </c>
       <c r="R240" t="n">
-        <v>6811411</v>
+        <v>6811486</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250337</v>
+        <v>130250295</v>
       </c>
       <c r="B242" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,34 +24766,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445441</v>
+        <v>445263</v>
       </c>
       <c r="R242" t="n">
-        <v>6811531</v>
+        <v>6811480</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24852,10 +24860,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250384</v>
+        <v>130250337</v>
       </c>
       <c r="B243" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24863,21 +24871,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24887,10 +24895,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445209</v>
+        <v>445441</v>
       </c>
       <c r="R243" t="n">
-        <v>6811374</v>
+        <v>6811531</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24949,7 +24957,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250375</v>
+        <v>130250384</v>
       </c>
       <c r="B244" t="n">
         <v>79211</v>
@@ -24984,10 +24992,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445492</v>
+        <v>445209</v>
       </c>
       <c r="R244" t="n">
-        <v>6811496</v>
+        <v>6811374</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25046,7 +25054,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250378</v>
+        <v>130250375</v>
       </c>
       <c r="B245" t="n">
         <v>79211</v>
@@ -25081,10 +25089,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445421</v>
+        <v>445492</v>
       </c>
       <c r="R245" t="n">
-        <v>6811499</v>
+        <v>6811496</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25143,7 +25151,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250407</v>
+        <v>130250378</v>
       </c>
       <c r="B246" t="n">
         <v>79211</v>
@@ -25178,10 +25186,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445299</v>
+        <v>445421</v>
       </c>
       <c r="R246" t="n">
-        <v>6811253</v>
+        <v>6811499</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25240,7 +25248,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250403</v>
+        <v>130250407</v>
       </c>
       <c r="B247" t="n">
         <v>79211</v>
@@ -25275,10 +25283,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445337</v>
+        <v>445299</v>
       </c>
       <c r="R247" t="n">
-        <v>6811372</v>
+        <v>6811253</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25337,7 +25345,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250359</v>
+        <v>130250403</v>
       </c>
       <c r="B248" t="n">
         <v>79211</v>
@@ -25372,10 +25380,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445161</v>
+        <v>445337</v>
       </c>
       <c r="R248" t="n">
-        <v>6811404</v>
+        <v>6811372</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25434,10 +25442,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250295</v>
+        <v>130250359</v>
       </c>
       <c r="B249" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25445,42 +25453,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445263</v>
+        <v>445161</v>
       </c>
       <c r="R249" t="n">
-        <v>6811480</v>
+        <v>6811404</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130237691</v>
+        <v>130237743</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,42 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444991</v>
+        <v>445095</v>
       </c>
       <c r="R4" t="n">
-        <v>6811568</v>
+        <v>6811230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +982,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130237743</v>
+        <v>130237745</v>
       </c>
       <c r="B5" t="n">
         <v>78968</v>
@@ -1025,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445095</v>
+        <v>444954</v>
       </c>
       <c r="R5" t="n">
-        <v>6811230</v>
+        <v>6811588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130237745</v>
+        <v>130237691</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,34 +1090,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444954</v>
+        <v>444991</v>
       </c>
       <c r="R6" t="n">
-        <v>6811588</v>
+        <v>6811568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237663</v>
+        <v>130237724</v>
       </c>
       <c r="B10" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444954</v>
+        <v>445064</v>
       </c>
       <c r="R10" t="n">
-        <v>6811588</v>
+        <v>6811249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1701,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237724</v>
+        <v>130237705</v>
       </c>
       <c r="B12" t="n">
         <v>57851</v>
@@ -1736,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445064</v>
+        <v>445092</v>
       </c>
       <c r="R12" t="n">
-        <v>6811249</v>
+        <v>6811513</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237705</v>
+        <v>130237777</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,42 +1817,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445092</v>
+        <v>445058</v>
       </c>
       <c r="R13" t="n">
-        <v>6811513</v>
+        <v>6811322</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130237777</v>
+        <v>130237749</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,21 +1914,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445058</v>
+        <v>445027</v>
       </c>
       <c r="R14" t="n">
-        <v>6811322</v>
+        <v>6811319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237749</v>
+        <v>130237663</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>79830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445027</v>
+        <v>444954</v>
       </c>
       <c r="R15" t="n">
-        <v>6811319</v>
+        <v>6811588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130237714</v>
+        <v>130237778</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2399,42 +2399,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445083</v>
+        <v>445058</v>
       </c>
       <c r="R19" t="n">
-        <v>6811458</v>
+        <v>6811265</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2493,7 +2485,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130237778</v>
+        <v>130237761</v>
       </c>
       <c r="B20" t="n">
         <v>79211</v>
@@ -2528,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445058</v>
+        <v>445019</v>
       </c>
       <c r="R20" t="n">
-        <v>6811265</v>
+        <v>6811345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130237761</v>
+        <v>130237667</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2601,21 +2593,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2625,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445019</v>
+        <v>445051</v>
       </c>
       <c r="R21" t="n">
-        <v>6811345</v>
+        <v>6811326</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,7 +2679,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130237693</v>
+        <v>130237714</v>
       </c>
       <c r="B22" t="n">
         <v>57851</v>
@@ -2730,10 +2722,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445027</v>
+        <v>445083</v>
       </c>
       <c r="R22" t="n">
-        <v>6811603</v>
+        <v>6811458</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,10 +2784,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130237667</v>
+        <v>130237693</v>
       </c>
       <c r="B23" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,34 +2795,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445051</v>
+        <v>445027</v>
       </c>
       <c r="R23" t="n">
-        <v>6811326</v>
+        <v>6811603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,32 +2986,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237723</v>
+        <v>130237677</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445063</v>
+        <v>445025</v>
       </c>
       <c r="R25" t="n">
-        <v>6811256</v>
+        <v>6811296</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,53 +3091,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237677</v>
+        <v>130237744</v>
       </c>
       <c r="B26" t="n">
-        <v>57044</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445025</v>
+        <v>445002</v>
       </c>
       <c r="R26" t="n">
-        <v>6811296</v>
+        <v>6811503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,10 +3188,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130237744</v>
+        <v>130237723</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3207,34 +3199,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445002</v>
+        <v>445063</v>
       </c>
       <c r="R27" t="n">
-        <v>6811503</v>
+        <v>6811256</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130237715</v>
+        <v>130237739</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,31 +3401,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3433,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445094</v>
+        <v>445044</v>
       </c>
       <c r="R29" t="n">
-        <v>6811438</v>
+        <v>6811298</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,6 +3472,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3495,10 +3491,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130237739</v>
+        <v>130237715</v>
       </c>
       <c r="B30" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,26 +3502,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3533,10 +3534,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445044</v>
+        <v>445094</v>
       </c>
       <c r="R30" t="n">
-        <v>6811298</v>
+        <v>6811438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3577,7 +3578,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130237719</v>
+        <v>130237707</v>
       </c>
       <c r="B35" t="n">
         <v>57851</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445094</v>
+        <v>445074</v>
       </c>
       <c r="R35" t="n">
-        <v>6811360</v>
+        <v>6811505</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130237707</v>
+        <v>130237719</v>
       </c>
       <c r="B36" t="n">
         <v>57851</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445074</v>
+        <v>445094</v>
       </c>
       <c r="R36" t="n">
-        <v>6811505</v>
+        <v>6811360</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4396,53 +4396,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130237675</v>
+        <v>130237670</v>
       </c>
       <c r="B39" t="n">
-        <v>57044</v>
+        <v>79830</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445000</v>
+        <v>445045</v>
       </c>
       <c r="R39" t="n">
-        <v>6811614</v>
+        <v>6811267</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4501,10 +4493,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130237670</v>
+        <v>130237764</v>
       </c>
       <c r="B40" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4504,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4528,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445045</v>
+        <v>445011</v>
       </c>
       <c r="R40" t="n">
-        <v>6811267</v>
+        <v>6811436</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,10 +4590,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130237669</v>
+        <v>130237779</v>
       </c>
       <c r="B41" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,21 +4601,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445036</v>
+        <v>445067</v>
       </c>
       <c r="R41" t="n">
-        <v>6811260</v>
+        <v>6811245</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4687,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130237764</v>
+        <v>130237669</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,21 +4698,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445011</v>
+        <v>445036</v>
       </c>
       <c r="R42" t="n">
-        <v>6811436</v>
+        <v>6811260</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,45 +4784,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237779</v>
+        <v>130237675</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445067</v>
+        <v>445000</v>
       </c>
       <c r="R43" t="n">
-        <v>6811245</v>
+        <v>6811614</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4889,49 +4889,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130237750</v>
+        <v>130237671</v>
       </c>
       <c r="B44" t="n">
-        <v>98957</v>
+        <v>79830</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445085</v>
+        <v>445066</v>
       </c>
       <c r="R44" t="n">
-        <v>6811515</v>
+        <v>6811213</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4966,18 +4962,12 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett hundratal plantor.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4996,45 +4986,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130237735</v>
+        <v>130237750</v>
       </c>
       <c r="B45" t="n">
-        <v>78969</v>
+        <v>98957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444985</v>
+        <v>445085</v>
       </c>
       <c r="R45" t="n">
-        <v>6811589</v>
+        <v>6811515</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5069,12 +5063,18 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ett hundratal plantor.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5093,10 +5093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130237671</v>
+        <v>130237735</v>
       </c>
       <c r="B46" t="n">
-        <v>79830</v>
+        <v>78969</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445066</v>
+        <v>444985</v>
       </c>
       <c r="R46" t="n">
-        <v>6811213</v>
+        <v>6811589</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237660</v>
+        <v>130237708</v>
       </c>
       <c r="B47" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,34 +5201,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R47" t="n">
-        <v>6811440</v>
+        <v>6811502</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237708</v>
+        <v>130237780</v>
       </c>
       <c r="B48" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,32 +5306,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
@@ -5333,7 +5333,7 @@
         <v>445066</v>
       </c>
       <c r="R48" t="n">
-        <v>6811502</v>
+        <v>6811223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237780</v>
+        <v>130237660</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445066</v>
+        <v>444997</v>
       </c>
       <c r="R49" t="n">
-        <v>6811223</v>
+        <v>6811440</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130237710</v>
+        <v>130237704</v>
       </c>
       <c r="B52" t="n">
         <v>57851</v>
@@ -5728,7 +5728,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445064</v>
+        <v>445097</v>
       </c>
       <c r="R52" t="n">
-        <v>6811451</v>
+        <v>6811537</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130237704</v>
+        <v>130237710</v>
       </c>
       <c r="B53" t="n">
         <v>57851</v>
@@ -5833,7 +5833,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445097</v>
+        <v>445064</v>
       </c>
       <c r="R53" t="n">
-        <v>6811537</v>
+        <v>6811451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130237776</v>
+        <v>130237695</v>
       </c>
       <c r="B54" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,34 +5916,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445092</v>
+        <v>445073</v>
       </c>
       <c r="R54" t="n">
-        <v>6811332</v>
+        <v>6811597</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,7 +6010,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130237762</v>
+        <v>130237776</v>
       </c>
       <c r="B55" t="n">
         <v>79211</v>
@@ -6037,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445021</v>
+        <v>445092</v>
       </c>
       <c r="R55" t="n">
-        <v>6811394</v>
+        <v>6811332</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6099,10 +6107,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130237695</v>
+        <v>130237661</v>
       </c>
       <c r="B56" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6110,42 +6118,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445073</v>
+        <v>444987</v>
       </c>
       <c r="R56" t="n">
-        <v>6811597</v>
+        <v>6811482</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130237661</v>
+        <v>130237762</v>
       </c>
       <c r="B57" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444987</v>
+        <v>445021</v>
       </c>
       <c r="R57" t="n">
-        <v>6811482</v>
+        <v>6811394</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,32 +6301,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237725</v>
+        <v>130237679</v>
       </c>
       <c r="B58" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445073</v>
+        <v>445036</v>
       </c>
       <c r="R58" t="n">
-        <v>6811522</v>
+        <v>6811277</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,53 +6406,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130237679</v>
+        <v>130237760</v>
       </c>
       <c r="B59" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445036</v>
+        <v>445075</v>
       </c>
       <c r="R59" t="n">
-        <v>6811277</v>
+        <v>6811319</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6608,10 +6600,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237760</v>
+        <v>130237725</v>
       </c>
       <c r="B61" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6619,34 +6611,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445075</v>
+        <v>445073</v>
       </c>
       <c r="R61" t="n">
-        <v>6811319</v>
+        <v>6811522</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237711</v>
+        <v>130237720</v>
       </c>
       <c r="B65" t="n">
         <v>57851</v>
@@ -7037,7 +7037,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445054</v>
+        <v>445048</v>
       </c>
       <c r="R65" t="n">
-        <v>6811454</v>
+        <v>6811299</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237720</v>
+        <v>130237709</v>
       </c>
       <c r="B66" t="n">
         <v>57851</v>
@@ -7142,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445048</v>
+        <v>445058</v>
       </c>
       <c r="R66" t="n">
-        <v>6811299</v>
+        <v>6811482</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130237709</v>
+        <v>130237711</v>
       </c>
       <c r="B67" t="n">
         <v>57851</v>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445058</v>
+        <v>445054</v>
       </c>
       <c r="R67" t="n">
-        <v>6811482</v>
+        <v>6811454</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130237716</v>
+        <v>130237769</v>
       </c>
       <c r="B71" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7637,42 +7637,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445149</v>
+        <v>445114</v>
       </c>
       <c r="R71" t="n">
-        <v>6811433</v>
+        <v>6811610</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7731,10 +7723,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130237769</v>
+        <v>130237690</v>
       </c>
       <c r="B72" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7742,34 +7734,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445114</v>
+        <v>445103</v>
       </c>
       <c r="R72" t="n">
-        <v>6811610</v>
+        <v>6811320</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130237690</v>
+        <v>130237716</v>
       </c>
       <c r="B73" t="n">
         <v>57851</v>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445103</v>
+        <v>445149</v>
       </c>
       <c r="R73" t="n">
-        <v>6811320</v>
+        <v>6811433</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130237702</v>
+        <v>130237768</v>
       </c>
       <c r="B85" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9055,42 +9055,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445137</v>
+        <v>445145</v>
       </c>
       <c r="R85" t="n">
-        <v>6811505</v>
+        <v>6811638</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9149,41 +9141,40 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130237782</v>
+        <v>130237702</v>
       </c>
       <c r="B86" t="n">
-        <v>8440</v>
+        <v>57851</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9193,10 +9184,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445142</v>
+        <v>445137</v>
       </c>
       <c r="R86" t="n">
-        <v>6811431</v>
+        <v>6811505</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,7 +9228,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9256,45 +9246,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130237768</v>
+        <v>130237782</v>
       </c>
       <c r="B87" t="n">
-        <v>79211</v>
+        <v>8440</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445145</v>
+        <v>445142</v>
       </c>
       <c r="R87" t="n">
-        <v>6811638</v>
+        <v>6811431</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9335,6 +9334,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237718</v>
+        <v>130237758</v>
       </c>
       <c r="B94" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9951,42 +9951,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445116</v>
+        <v>445101</v>
       </c>
       <c r="R94" t="n">
-        <v>6811382</v>
+        <v>6811246</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,7 +10037,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130237696</v>
+        <v>130237718</v>
       </c>
       <c r="B95" t="n">
         <v>57851</v>
@@ -10088,10 +10080,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445118</v>
+        <v>445116</v>
       </c>
       <c r="R95" t="n">
-        <v>6811654</v>
+        <v>6811382</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10150,10 +10142,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237758</v>
+        <v>130237696</v>
       </c>
       <c r="B96" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10161,34 +10153,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445101</v>
+        <v>445118</v>
       </c>
       <c r="R96" t="n">
-        <v>6811246</v>
+        <v>6811654</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130250296</v>
+        <v>130250339</v>
       </c>
       <c r="B117" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12270,42 +12270,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445240</v>
+        <v>445457</v>
       </c>
       <c r="R117" t="n">
-        <v>6811502</v>
+        <v>6811516</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12364,10 +12356,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130250339</v>
+        <v>130250313</v>
       </c>
       <c r="B118" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12375,34 +12367,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445457</v>
+        <v>445334</v>
       </c>
       <c r="R118" t="n">
-        <v>6811516</v>
+        <v>6811325</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12461,7 +12461,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130250313</v>
+        <v>130250296</v>
       </c>
       <c r="B119" t="n">
         <v>57851</v>
@@ -12504,10 +12504,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445334</v>
+        <v>445240</v>
       </c>
       <c r="R119" t="n">
-        <v>6811325</v>
+        <v>6811502</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250314</v>
+        <v>130250357</v>
       </c>
       <c r="B120" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12577,42 +12577,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445322</v>
+        <v>445165</v>
       </c>
       <c r="R120" t="n">
-        <v>6811309</v>
+        <v>6811302</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13257,10 +13249,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250357</v>
+        <v>130250289</v>
       </c>
       <c r="B127" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13268,34 +13260,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445165</v>
+        <v>445468</v>
       </c>
       <c r="R127" t="n">
-        <v>6811302</v>
+        <v>6811500</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250289</v>
+        <v>130250314</v>
       </c>
       <c r="B128" t="n">
         <v>57851</v>
@@ -13387,7 +13387,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445468</v>
+        <v>445322</v>
       </c>
       <c r="R128" t="n">
-        <v>6811500</v>
+        <v>6811309</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130250321</v>
+        <v>130250255</v>
       </c>
       <c r="B131" t="n">
-        <v>78969</v>
+        <v>79830</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13680,21 +13680,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13704,10 +13704,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>445326</v>
+        <v>445480</v>
       </c>
       <c r="R131" t="n">
-        <v>6811613</v>
+        <v>6811273</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130250255</v>
+        <v>130250321</v>
       </c>
       <c r="B132" t="n">
-        <v>79830</v>
+        <v>78969</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13777,21 +13777,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>445480</v>
+        <v>445326</v>
       </c>
       <c r="R132" t="n">
-        <v>6811273</v>
+        <v>6811613</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130250369</v>
+        <v>130250390</v>
       </c>
       <c r="B136" t="n">
         <v>79211</v>
@@ -14189,10 +14189,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>445518</v>
+        <v>445492</v>
       </c>
       <c r="R136" t="n">
-        <v>6811539</v>
+        <v>6811299</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14251,7 +14251,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130250356</v>
+        <v>130250369</v>
       </c>
       <c r="B137" t="n">
         <v>79211</v>
@@ -14286,10 +14286,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>445227</v>
+        <v>445518</v>
       </c>
       <c r="R137" t="n">
-        <v>6811254</v>
+        <v>6811539</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14348,7 +14348,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130250390</v>
+        <v>130250356</v>
       </c>
       <c r="B138" t="n">
         <v>79211</v>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>445492</v>
+        <v>445227</v>
       </c>
       <c r="R138" t="n">
-        <v>6811299</v>
+        <v>6811254</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14958,32 +14958,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250297</v>
+        <v>130250274</v>
       </c>
       <c r="B144" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14991,7 +14991,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
@@ -15001,10 +15001,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445239</v>
+        <v>445376</v>
       </c>
       <c r="R144" t="n">
-        <v>6811474</v>
+        <v>6811389</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15063,32 +15063,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250292</v>
+        <v>130250271</v>
       </c>
       <c r="B145" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15096,7 +15096,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
@@ -15106,10 +15106,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445384</v>
+        <v>445375</v>
       </c>
       <c r="R145" t="n">
-        <v>6811490</v>
+        <v>6811502</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15168,10 +15168,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250303</v>
+        <v>130250323</v>
       </c>
       <c r="B146" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15179,42 +15179,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445389</v>
+        <v>445371</v>
       </c>
       <c r="R146" t="n">
-        <v>6811264</v>
+        <v>6811594</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15273,53 +15265,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250274</v>
+        <v>130250266</v>
       </c>
       <c r="B147" t="n">
-        <v>57044</v>
+        <v>79801</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445376</v>
+        <v>445580</v>
       </c>
       <c r="R147" t="n">
-        <v>6811389</v>
+        <v>6811443</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15378,53 +15362,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250271</v>
+        <v>130250328</v>
       </c>
       <c r="B148" t="n">
-        <v>57044</v>
+        <v>78969</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445375</v>
+        <v>445329</v>
       </c>
       <c r="R148" t="n">
-        <v>6811502</v>
+        <v>6811272</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15483,10 +15459,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250323</v>
+        <v>130250297</v>
       </c>
       <c r="B149" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15494,34 +15470,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445371</v>
+        <v>445239</v>
       </c>
       <c r="R149" t="n">
-        <v>6811594</v>
+        <v>6811474</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15580,10 +15564,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130250266</v>
+        <v>130250292</v>
       </c>
       <c r="B150" t="n">
-        <v>79801</v>
+        <v>57851</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15591,34 +15575,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>445580</v>
+        <v>445384</v>
       </c>
       <c r="R150" t="n">
-        <v>6811443</v>
+        <v>6811490</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15677,10 +15669,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250328</v>
+        <v>130250303</v>
       </c>
       <c r="B151" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15688,34 +15680,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445329</v>
+        <v>445389</v>
       </c>
       <c r="R151" t="n">
-        <v>6811272</v>
+        <v>6811264</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15774,45 +15774,49 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130250381</v>
+        <v>130250319</v>
       </c>
       <c r="B152" t="n">
-        <v>79211</v>
+        <v>97834</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>445351</v>
+        <v>445554</v>
       </c>
       <c r="R152" t="n">
-        <v>6811495</v>
+        <v>6811457</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15853,6 +15857,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15871,10 +15876,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130250335</v>
+        <v>130250326</v>
       </c>
       <c r="B153" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15882,21 +15887,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15906,10 +15911,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>445372</v>
+        <v>445235</v>
       </c>
       <c r="R153" t="n">
-        <v>6811595</v>
+        <v>6811325</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15968,10 +15973,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130250341</v>
+        <v>130250329</v>
       </c>
       <c r="B154" t="n">
-        <v>78968</v>
+        <v>78969</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15979,21 +15984,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16003,10 +16008,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>445383</v>
+        <v>445323</v>
       </c>
       <c r="R154" t="n">
-        <v>6811286</v>
+        <v>6811270</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16065,10 +16070,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130250336</v>
+        <v>130250381</v>
       </c>
       <c r="B155" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16076,21 +16081,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16100,10 +16105,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>445413</v>
+        <v>445351</v>
       </c>
       <c r="R155" t="n">
-        <v>6811568</v>
+        <v>6811495</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16162,53 +16167,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250276</v>
+        <v>130250335</v>
       </c>
       <c r="B156" t="n">
-        <v>57044</v>
+        <v>78968</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445328</v>
+        <v>445372</v>
       </c>
       <c r="R156" t="n">
-        <v>6811392</v>
+        <v>6811595</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16267,10 +16264,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130250317</v>
+        <v>130250341</v>
       </c>
       <c r="B157" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16278,42 +16275,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445487</v>
+        <v>445383</v>
       </c>
       <c r="R157" t="n">
-        <v>6811335</v>
+        <v>6811286</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16372,10 +16361,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130250286</v>
+        <v>130250336</v>
       </c>
       <c r="B158" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16383,42 +16372,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445540</v>
+        <v>445413</v>
       </c>
       <c r="R158" t="n">
-        <v>6811525</v>
+        <v>6811568</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16477,10 +16458,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130250326</v>
+        <v>130250317</v>
       </c>
       <c r="B159" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16488,34 +16469,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445235</v>
+        <v>445487</v>
       </c>
       <c r="R159" t="n">
-        <v>6811325</v>
+        <v>6811335</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16574,10 +16563,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130250329</v>
+        <v>130250286</v>
       </c>
       <c r="B160" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16585,34 +16574,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>445323</v>
+        <v>445540</v>
       </c>
       <c r="R160" t="n">
-        <v>6811270</v>
+        <v>6811525</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16671,10 +16668,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250319</v>
+        <v>130250276</v>
       </c>
       <c r="B161" t="n">
-        <v>97834</v>
+        <v>57044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16682,27 +16679,31 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -16710,10 +16711,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445554</v>
+        <v>445328</v>
       </c>
       <c r="R161" t="n">
-        <v>6811457</v>
+        <v>6811392</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16754,7 +16755,6 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130250279</v>
+        <v>130250340</v>
       </c>
       <c r="B162" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16784,42 +16784,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>445165</v>
+        <v>445366</v>
       </c>
       <c r="R162" t="n">
-        <v>6811426</v>
+        <v>6811298</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16878,10 +16870,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130250340</v>
+        <v>130250248</v>
       </c>
       <c r="B163" t="n">
-        <v>78968</v>
+        <v>79830</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16889,21 +16881,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16913,10 +16905,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>445366</v>
+        <v>445243</v>
       </c>
       <c r="R163" t="n">
-        <v>6811298</v>
+        <v>6811593</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17072,10 +17064,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130250248</v>
+        <v>130250398</v>
       </c>
       <c r="B165" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17083,21 +17075,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17107,10 +17099,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>445243</v>
+        <v>445426</v>
       </c>
       <c r="R165" t="n">
-        <v>6811593</v>
+        <v>6811434</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17169,7 +17161,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130250398</v>
+        <v>130250371</v>
       </c>
       <c r="B166" t="n">
         <v>79211</v>
@@ -17204,10 +17196,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>445426</v>
+        <v>445588</v>
       </c>
       <c r="R166" t="n">
-        <v>6811434</v>
+        <v>6811455</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17266,10 +17258,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130250371</v>
+        <v>130250342</v>
       </c>
       <c r="B167" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17277,21 +17269,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17301,10 +17293,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>445588</v>
+        <v>445390</v>
       </c>
       <c r="R167" t="n">
-        <v>6811455</v>
+        <v>6811275</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17363,10 +17355,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130250342</v>
+        <v>130250279</v>
       </c>
       <c r="B168" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17374,34 +17366,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>445390</v>
+        <v>445165</v>
       </c>
       <c r="R168" t="n">
-        <v>6811275</v>
+        <v>6811426</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18357,32 +18357,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130250318</v>
+        <v>130250265</v>
       </c>
       <c r="B178" t="n">
-        <v>97828</v>
+        <v>79801</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18392,10 +18392,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>445180</v>
+        <v>445586</v>
       </c>
       <c r="R178" t="n">
-        <v>6811418</v>
+        <v>6811454</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18454,32 +18454,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130250265</v>
+        <v>130250318</v>
       </c>
       <c r="B179" t="n">
-        <v>79801</v>
+        <v>97828</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18489,10 +18489,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>445586</v>
+        <v>445180</v>
       </c>
       <c r="R179" t="n">
-        <v>6811454</v>
+        <v>6811418</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250406</v>
+        <v>130250325</v>
       </c>
       <c r="B180" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445341</v>
+        <v>445457</v>
       </c>
       <c r="R180" t="n">
-        <v>6811293</v>
+        <v>6811516</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18648,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250377</v>
+        <v>130250333</v>
       </c>
       <c r="B181" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,21 +18659,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445454</v>
+        <v>445201</v>
       </c>
       <c r="R181" t="n">
-        <v>6811502</v>
+        <v>6811621</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,10 +18745,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250325</v>
+        <v>130250344</v>
       </c>
       <c r="B182" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18756,21 +18756,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18780,10 +18780,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445457</v>
+        <v>445358</v>
       </c>
       <c r="R182" t="n">
-        <v>6811516</v>
+        <v>6811433</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,10 +18842,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250333</v>
+        <v>130250383</v>
       </c>
       <c r="B183" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18853,21 +18853,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445201</v>
+        <v>445209</v>
       </c>
       <c r="R183" t="n">
-        <v>6811621</v>
+        <v>6811451</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,10 +18939,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250344</v>
+        <v>130250406</v>
       </c>
       <c r="B184" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18950,21 +18950,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18974,10 +18974,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445358</v>
+        <v>445341</v>
       </c>
       <c r="R184" t="n">
-        <v>6811433</v>
+        <v>6811293</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19036,7 +19036,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250383</v>
+        <v>130250377</v>
       </c>
       <c r="B185" t="n">
         <v>79211</v>
@@ -19071,10 +19071,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445209</v>
+        <v>445454</v>
       </c>
       <c r="R185" t="n">
-        <v>6811451</v>
+        <v>6811502</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19343,40 +19343,41 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>130250312</v>
+        <v>130250330</v>
       </c>
       <c r="B188" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
@@ -19386,10 +19387,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>445324</v>
+        <v>445218</v>
       </c>
       <c r="R188" t="n">
-        <v>6811362</v>
+        <v>6811247</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19430,6 +19431,7 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -19448,54 +19450,45 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>130250330</v>
+        <v>130250257</v>
       </c>
       <c r="B189" t="n">
-        <v>8451</v>
+        <v>79830</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>445218</v>
+        <v>445474</v>
       </c>
       <c r="R189" t="n">
-        <v>6811247</v>
+        <v>6811433</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19536,7 +19529,6 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -19555,10 +19547,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130250257</v>
+        <v>130250363</v>
       </c>
       <c r="B190" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19566,21 +19558,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19590,10 +19582,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>445474</v>
+        <v>445229</v>
       </c>
       <c r="R190" t="n">
-        <v>6811433</v>
+        <v>6811687</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19652,10 +19644,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130250363</v>
+        <v>130250312</v>
       </c>
       <c r="B191" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19663,34 +19655,42 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>445229</v>
+        <v>445324</v>
       </c>
       <c r="R191" t="n">
-        <v>6811687</v>
+        <v>6811362</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20056,7 +20056,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250395</v>
+        <v>130250370</v>
       </c>
       <c r="B195" t="n">
         <v>79211</v>
@@ -20091,10 +20091,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445507</v>
+        <v>445542</v>
       </c>
       <c r="R195" t="n">
-        <v>6811412</v>
+        <v>6811532</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20153,10 +20153,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250256</v>
+        <v>130250395</v>
       </c>
       <c r="B196" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20164,21 +20164,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20188,10 +20188,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445484</v>
+        <v>445507</v>
       </c>
       <c r="R196" t="n">
-        <v>6811291</v>
+        <v>6811412</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20250,10 +20250,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250298</v>
+        <v>130250256</v>
       </c>
       <c r="B197" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20261,42 +20261,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445232</v>
+        <v>445484</v>
       </c>
       <c r="R197" t="n">
-        <v>6811448</v>
+        <v>6811291</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20355,10 +20347,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250300</v>
+        <v>130250386</v>
       </c>
       <c r="B198" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20366,42 +20358,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445219</v>
+        <v>445226</v>
       </c>
       <c r="R198" t="n">
-        <v>6811344</v>
+        <v>6811348</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20460,32 +20444,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250291</v>
+        <v>130250355</v>
       </c>
       <c r="B199" t="n">
-        <v>57851</v>
+        <v>57846</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20493,7 +20477,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -20503,10 +20487,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445385</v>
+        <v>445443</v>
       </c>
       <c r="R199" t="n">
-        <v>6811504</v>
+        <v>6811494</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20565,7 +20549,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250281</v>
+        <v>130250298</v>
       </c>
       <c r="B200" t="n">
         <v>57851</v>
@@ -20608,10 +20592,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445205</v>
+        <v>445232</v>
       </c>
       <c r="R200" t="n">
-        <v>6811619</v>
+        <v>6811448</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20670,32 +20654,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250355</v>
+        <v>130250300</v>
       </c>
       <c r="B201" t="n">
-        <v>57846</v>
+        <v>57851</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20703,7 +20687,7 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
@@ -20713,10 +20697,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445443</v>
+        <v>445219</v>
       </c>
       <c r="R201" t="n">
-        <v>6811494</v>
+        <v>6811344</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20775,32 +20759,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250277</v>
+        <v>130250291</v>
       </c>
       <c r="B202" t="n">
-        <v>57044</v>
+        <v>57851</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20808,7 +20792,7 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -20818,10 +20802,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445202</v>
+        <v>445385</v>
       </c>
       <c r="R202" t="n">
-        <v>6811655</v>
+        <v>6811504</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20880,10 +20864,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250327</v>
+        <v>130250281</v>
       </c>
       <c r="B203" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20891,34 +20875,42 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445390</v>
+        <v>445205</v>
       </c>
       <c r="R203" t="n">
-        <v>6811275</v>
+        <v>6811619</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20977,45 +20969,53 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250370</v>
+        <v>130250277</v>
       </c>
       <c r="B204" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445542</v>
+        <v>445202</v>
       </c>
       <c r="R204" t="n">
-        <v>6811532</v>
+        <v>6811655</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21074,10 +21074,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130250386</v>
+        <v>130250327</v>
       </c>
       <c r="B205" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21085,21 +21085,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21109,10 +21109,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>445226</v>
+        <v>445390</v>
       </c>
       <c r="R205" t="n">
-        <v>6811348</v>
+        <v>6811275</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21276,7 +21276,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B207" t="n">
         <v>57851</v>
@@ -21319,10 +21319,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R207" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21381,10 +21381,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250264</v>
+        <v>130250305</v>
       </c>
       <c r="B208" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21392,34 +21392,42 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445315</v>
+        <v>445448</v>
       </c>
       <c r="R208" t="n">
-        <v>6811230</v>
+        <v>6811432</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21478,10 +21486,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250254</v>
+        <v>130250283</v>
       </c>
       <c r="B209" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21489,34 +21497,42 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445194</v>
+        <v>445303</v>
       </c>
       <c r="R209" t="n">
-        <v>6811426</v>
+        <v>6811621</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21575,7 +21591,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250258</v>
+        <v>130250264</v>
       </c>
       <c r="B210" t="n">
         <v>79830</v>
@@ -21610,10 +21626,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445470</v>
+        <v>445315</v>
       </c>
       <c r="R210" t="n">
-        <v>6811435</v>
+        <v>6811230</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21672,7 +21688,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250249</v>
+        <v>130250254</v>
       </c>
       <c r="B211" t="n">
         <v>79830</v>
@@ -21707,10 +21723,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445200</v>
+        <v>445194</v>
       </c>
       <c r="R211" t="n">
-        <v>6811598</v>
+        <v>6811426</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21769,10 +21785,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250392</v>
+        <v>130250258</v>
       </c>
       <c r="B212" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21780,21 +21796,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21804,10 +21820,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445487</v>
+        <v>445470</v>
       </c>
       <c r="R212" t="n">
-        <v>6811345</v>
+        <v>6811435</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21866,10 +21882,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250389</v>
+        <v>130250249</v>
       </c>
       <c r="B213" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21877,21 +21893,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21901,10 +21917,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445483</v>
+        <v>445200</v>
       </c>
       <c r="R213" t="n">
-        <v>6811288</v>
+        <v>6811598</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21963,7 +21979,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250367</v>
+        <v>130250392</v>
       </c>
       <c r="B214" t="n">
         <v>79211</v>
@@ -21998,10 +22014,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445376</v>
+        <v>445487</v>
       </c>
       <c r="R214" t="n">
-        <v>6811581</v>
+        <v>6811345</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,10 +22076,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250310</v>
+        <v>130250389</v>
       </c>
       <c r="B215" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22071,42 +22087,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445339</v>
+        <v>445483</v>
       </c>
       <c r="R215" t="n">
-        <v>6811359</v>
+        <v>6811288</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22165,10 +22173,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250283</v>
+        <v>130250367</v>
       </c>
       <c r="B216" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22176,42 +22184,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445303</v>
+        <v>445376</v>
       </c>
       <c r="R216" t="n">
-        <v>6811621</v>
+        <v>6811581</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22270,10 +22270,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130250307</v>
+        <v>130250247</v>
       </c>
       <c r="B217" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22281,42 +22281,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>445373</v>
+        <v>445188</v>
       </c>
       <c r="R217" t="n">
-        <v>6811417</v>
+        <v>6811507</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22375,10 +22367,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130250247</v>
+        <v>130250348</v>
       </c>
       <c r="B218" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22386,21 +22378,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22410,10 +22402,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>445188</v>
+        <v>445329</v>
       </c>
       <c r="R218" t="n">
-        <v>6811507</v>
+        <v>6811272</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22472,10 +22464,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130250348</v>
+        <v>130250253</v>
       </c>
       <c r="B219" t="n">
-        <v>78968</v>
+        <v>79830</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22483,21 +22475,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22507,10 +22499,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>445329</v>
+        <v>445543</v>
       </c>
       <c r="R219" t="n">
-        <v>6811272</v>
+        <v>6811480</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22569,7 +22561,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130250253</v>
+        <v>130250252</v>
       </c>
       <c r="B220" t="n">
         <v>79830</v>
@@ -22604,10 +22596,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>445543</v>
+        <v>445586</v>
       </c>
       <c r="R220" t="n">
-        <v>6811480</v>
+        <v>6811454</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22666,10 +22658,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130250252</v>
+        <v>130250387</v>
       </c>
       <c r="B221" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22677,21 +22669,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22701,10 +22693,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>445586</v>
+        <v>445238</v>
       </c>
       <c r="R221" t="n">
-        <v>6811454</v>
+        <v>6811310</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22763,10 +22755,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130250387</v>
+        <v>130250308</v>
       </c>
       <c r="B222" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22774,34 +22766,42 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>445238</v>
+        <v>445379</v>
       </c>
       <c r="R222" t="n">
-        <v>6811310</v>
+        <v>6811376</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22860,7 +22860,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130250308</v>
+        <v>130250307</v>
       </c>
       <c r="B223" t="n">
         <v>57851</v>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>445379</v>
+        <v>445373</v>
       </c>
       <c r="R223" t="n">
-        <v>6811376</v>
+        <v>6811417</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130237738</v>
+        <v>130237749</v>
       </c>
       <c r="B9" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445081</v>
+        <v>445027</v>
       </c>
       <c r="R9" t="n">
         <v>6811319</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130237724</v>
+        <v>130237663</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,42 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445064</v>
+        <v>444954</v>
       </c>
       <c r="R10" t="n">
-        <v>6811249</v>
+        <v>6811588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130237692</v>
+        <v>130237777</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,42 +1599,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445036</v>
+        <v>445058</v>
       </c>
       <c r="R11" t="n">
-        <v>6811602</v>
+        <v>6811322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130237705</v>
+        <v>130237724</v>
       </c>
       <c r="B12" t="n">
         <v>57851</v>
@@ -1744,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445092</v>
+        <v>445064</v>
       </c>
       <c r="R12" t="n">
-        <v>6811513</v>
+        <v>6811249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1790,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130237777</v>
+        <v>130237692</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,34 +1801,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445058</v>
+        <v>445036</v>
       </c>
       <c r="R13" t="n">
-        <v>6811322</v>
+        <v>6811602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130237749</v>
+        <v>130237705</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,34 +1906,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445027</v>
+        <v>445092</v>
       </c>
       <c r="R14" t="n">
-        <v>6811319</v>
+        <v>6811513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130237663</v>
+        <v>130237738</v>
       </c>
       <c r="B15" t="n">
-        <v>79830</v>
+        <v>78969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444954</v>
+        <v>445081</v>
       </c>
       <c r="R15" t="n">
-        <v>6811588</v>
+        <v>6811319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2986,53 +2986,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130237677</v>
+        <v>130237744</v>
       </c>
       <c r="B25" t="n">
-        <v>57044</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445025</v>
+        <v>445002</v>
       </c>
       <c r="R25" t="n">
-        <v>6811296</v>
+        <v>6811503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,45 +3083,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130237744</v>
+        <v>130237677</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>57044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445002</v>
+        <v>445025</v>
       </c>
       <c r="R26" t="n">
-        <v>6811503</v>
+        <v>6811296</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130237739</v>
+        <v>130237715</v>
       </c>
       <c r="B29" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,26 +3401,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3428,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445044</v>
+        <v>445094</v>
       </c>
       <c r="R29" t="n">
-        <v>6811298</v>
+        <v>6811438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3472,7 +3477,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3491,10 +3495,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130237715</v>
+        <v>130237739</v>
       </c>
       <c r="B30" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,31 +3506,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3534,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445094</v>
+        <v>445044</v>
       </c>
       <c r="R30" t="n">
-        <v>6811438</v>
+        <v>6811298</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3578,6 +3577,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130237765</v>
+        <v>130237737</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445089</v>
+        <v>445091</v>
       </c>
       <c r="R32" t="n">
-        <v>6811602</v>
+        <v>6811332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130237737</v>
+        <v>130237765</v>
       </c>
       <c r="B33" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445091</v>
+        <v>445089</v>
       </c>
       <c r="R33" t="n">
-        <v>6811332</v>
+        <v>6811602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130237670</v>
+        <v>130237669</v>
       </c>
       <c r="B39" t="n">
         <v>79830</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445045</v>
+        <v>445036</v>
       </c>
       <c r="R39" t="n">
-        <v>6811267</v>
+        <v>6811260</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,45 +4493,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130237764</v>
+        <v>130237675</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445011</v>
+        <v>445000</v>
       </c>
       <c r="R40" t="n">
-        <v>6811436</v>
+        <v>6811614</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,7 +4598,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130237779</v>
+        <v>130237764</v>
       </c>
       <c r="B41" t="n">
         <v>79211</v>
@@ -4625,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445067</v>
+        <v>445011</v>
       </c>
       <c r="R41" t="n">
-        <v>6811245</v>
+        <v>6811436</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4687,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130237669</v>
+        <v>130237779</v>
       </c>
       <c r="B42" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445036</v>
+        <v>445067</v>
       </c>
       <c r="R42" t="n">
-        <v>6811260</v>
+        <v>6811245</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4784,53 +4792,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130237675</v>
+        <v>130237670</v>
       </c>
       <c r="B43" t="n">
-        <v>57044</v>
+        <v>79830</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445000</v>
+        <v>445045</v>
       </c>
       <c r="R43" t="n">
-        <v>6811614</v>
+        <v>6811267</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130237708</v>
+        <v>130237780</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5201,32 +5201,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
@@ -5236,7 +5228,7 @@
         <v>445066</v>
       </c>
       <c r="R47" t="n">
-        <v>6811502</v>
+        <v>6811223</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130237780</v>
+        <v>130237660</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5306,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5330,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445066</v>
+        <v>444997</v>
       </c>
       <c r="R48" t="n">
-        <v>6811223</v>
+        <v>6811440</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5392,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130237660</v>
+        <v>130237708</v>
       </c>
       <c r="B49" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5403,34 +5395,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444997</v>
+        <v>445066</v>
       </c>
       <c r="R49" t="n">
-        <v>6811440</v>
+        <v>6811502</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5905,10 +5905,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130237695</v>
+        <v>130237776</v>
       </c>
       <c r="B54" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5916,42 +5916,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445073</v>
+        <v>445092</v>
       </c>
       <c r="R54" t="n">
-        <v>6811597</v>
+        <v>6811332</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,10 +6002,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130237776</v>
+        <v>130237695</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6021,34 +6013,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445092</v>
+        <v>445073</v>
       </c>
       <c r="R55" t="n">
-        <v>6811332</v>
+        <v>6811597</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130237661</v>
+        <v>130237762</v>
       </c>
       <c r="B56" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6118,21 +6118,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444987</v>
+        <v>445021</v>
       </c>
       <c r="R56" t="n">
-        <v>6811482</v>
+        <v>6811394</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130237762</v>
+        <v>130237661</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445021</v>
+        <v>444987</v>
       </c>
       <c r="R57" t="n">
-        <v>6811394</v>
+        <v>6811482</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,53 +6301,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130237679</v>
+        <v>130237662</v>
       </c>
       <c r="B58" t="n">
-        <v>57044</v>
+        <v>79830</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445036</v>
+        <v>445002</v>
       </c>
       <c r="R58" t="n">
-        <v>6811277</v>
+        <v>6811503</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,10 +6398,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130237760</v>
+        <v>130237725</v>
       </c>
       <c r="B59" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6417,34 +6409,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445075</v>
+        <v>445073</v>
       </c>
       <c r="R59" t="n">
-        <v>6811319</v>
+        <v>6811522</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6503,45 +6503,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130237662</v>
+        <v>130237679</v>
       </c>
       <c r="B60" t="n">
-        <v>79830</v>
+        <v>57044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445002</v>
+        <v>445036</v>
       </c>
       <c r="R60" t="n">
-        <v>6811503</v>
+        <v>6811277</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6600,10 +6608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130237725</v>
+        <v>130237760</v>
       </c>
       <c r="B61" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6611,42 +6619,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445073</v>
+        <v>445075</v>
       </c>
       <c r="R61" t="n">
-        <v>6811522</v>
+        <v>6811319</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130237664</v>
+        <v>130237709</v>
       </c>
       <c r="B63" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6813,34 +6813,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444968</v>
+        <v>445058</v>
       </c>
       <c r="R63" t="n">
-        <v>6811605</v>
+        <v>6811482</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130237713</v>
+        <v>130237664</v>
       </c>
       <c r="B64" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,42 +6918,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445073</v>
+        <v>444968</v>
       </c>
       <c r="R64" t="n">
-        <v>6811446</v>
+        <v>6811605</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130237720</v>
+        <v>130237713</v>
       </c>
       <c r="B65" t="n">
         <v>57851</v>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445048</v>
+        <v>445073</v>
       </c>
       <c r="R65" t="n">
-        <v>6811299</v>
+        <v>6811446</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130237709</v>
+        <v>130237720</v>
       </c>
       <c r="B66" t="n">
         <v>57851</v>
@@ -7142,7 +7142,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445058</v>
+        <v>445048</v>
       </c>
       <c r="R66" t="n">
-        <v>6811482</v>
+        <v>6811299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8446,10 +8446,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130237747</v>
+        <v>130237700</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8457,34 +8457,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445113</v>
+        <v>445131</v>
       </c>
       <c r="R79" t="n">
-        <v>6811388</v>
+        <v>6811529</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8543,10 +8551,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130237700</v>
+        <v>130237747</v>
       </c>
       <c r="B80" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8554,42 +8562,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445131</v>
+        <v>445113</v>
       </c>
       <c r="R80" t="n">
-        <v>6811529</v>
+        <v>6811388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130237771</v>
+        <v>130237703</v>
       </c>
       <c r="B82" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8756,34 +8756,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445159</v>
+        <v>445132</v>
       </c>
       <c r="R82" t="n">
-        <v>6811562</v>
+        <v>6811535</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8842,10 +8850,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130237703</v>
+        <v>130237771</v>
       </c>
       <c r="B83" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8853,42 +8861,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445132</v>
+        <v>445159</v>
       </c>
       <c r="R83" t="n">
-        <v>6811535</v>
+        <v>6811562</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130237758</v>
+        <v>130237696</v>
       </c>
       <c r="B94" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9951,34 +9951,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445101</v>
+        <v>445118</v>
       </c>
       <c r="R94" t="n">
-        <v>6811246</v>
+        <v>6811654</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10142,10 +10150,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130237696</v>
+        <v>130237758</v>
       </c>
       <c r="B96" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10153,42 +10161,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445118</v>
+        <v>445101</v>
       </c>
       <c r="R96" t="n">
-        <v>6811654</v>
+        <v>6811246</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11047,10 +11047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250302</v>
+        <v>130250267</v>
       </c>
       <c r="B105" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,31 +11058,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11090,10 +11085,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445239</v>
+        <v>445503</v>
       </c>
       <c r="R105" t="n">
-        <v>6811358</v>
+        <v>6811332</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11134,8 +11129,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11734,10 +11750,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130250267</v>
+        <v>130250302</v>
       </c>
       <c r="B112" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11745,26 +11761,31 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11772,10 +11793,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445503</v>
+        <v>445239</v>
       </c>
       <c r="R112" t="n">
-        <v>6811332</v>
+        <v>6811358</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11816,29 +11837,8 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12566,7 +12566,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250357</v>
+        <v>130250394</v>
       </c>
       <c r="B120" t="n">
         <v>79211</v>
@@ -12595,16 +12595,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445165</v>
+        <v>445495</v>
       </c>
       <c r="R120" t="n">
-        <v>6811302</v>
+        <v>6811385</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12645,6 +12648,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12663,10 +12667,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250394</v>
+        <v>130250259</v>
       </c>
       <c r="B121" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12674,37 +12678,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445495</v>
+        <v>445441</v>
       </c>
       <c r="R121" t="n">
-        <v>6811385</v>
+        <v>6811433</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12745,7 +12746,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12764,10 +12764,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250259</v>
+        <v>130250404</v>
       </c>
       <c r="B122" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12775,21 +12775,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12799,10 +12799,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445441</v>
+        <v>445330</v>
       </c>
       <c r="R122" t="n">
-        <v>6811433</v>
+        <v>6811333</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12861,7 +12861,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250404</v>
+        <v>130250360</v>
       </c>
       <c r="B123" t="n">
         <v>79211</v>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445330</v>
+        <v>445194</v>
       </c>
       <c r="R123" t="n">
-        <v>6811333</v>
+        <v>6811530</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12958,10 +12958,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250360</v>
+        <v>130250338</v>
       </c>
       <c r="B124" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12969,21 +12969,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445194</v>
+        <v>445492</v>
       </c>
       <c r="R124" t="n">
-        <v>6811530</v>
+        <v>6811520</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13055,10 +13055,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250338</v>
+        <v>130250399</v>
       </c>
       <c r="B125" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13066,21 +13066,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445492</v>
+        <v>445416</v>
       </c>
       <c r="R125" t="n">
-        <v>6811520</v>
+        <v>6811445</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130250399</v>
+        <v>130250357</v>
       </c>
       <c r="B126" t="n">
         <v>79211</v>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>445416</v>
+        <v>445165</v>
       </c>
       <c r="R126" t="n">
-        <v>6811445</v>
+        <v>6811302</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13249,7 +13249,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250289</v>
+        <v>130250293</v>
       </c>
       <c r="B127" t="n">
         <v>57851</v>
@@ -13292,10 +13292,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445468</v>
+        <v>445303</v>
       </c>
       <c r="R127" t="n">
-        <v>6811500</v>
+        <v>6811490</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130250314</v>
+        <v>130250289</v>
       </c>
       <c r="B128" t="n">
         <v>57851</v>
@@ -13387,7 +13387,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>445322</v>
+        <v>445468</v>
       </c>
       <c r="R128" t="n">
-        <v>6811309</v>
+        <v>6811500</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13459,7 +13459,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130250293</v>
+        <v>130250314</v>
       </c>
       <c r="B129" t="n">
         <v>57851</v>
@@ -13492,7 +13492,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -13502,10 +13502,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>445303</v>
+        <v>445322</v>
       </c>
       <c r="R129" t="n">
-        <v>6811490</v>
+        <v>6811309</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15168,7 +15168,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250323</v>
+        <v>130250328</v>
       </c>
       <c r="B146" t="n">
         <v>78969</v>
@@ -15203,10 +15203,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445371</v>
+        <v>445329</v>
       </c>
       <c r="R146" t="n">
-        <v>6811594</v>
+        <v>6811272</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15265,10 +15265,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250266</v>
+        <v>130250323</v>
       </c>
       <c r="B147" t="n">
-        <v>79801</v>
+        <v>78969</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15276,21 +15276,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15300,10 +15300,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445580</v>
+        <v>445371</v>
       </c>
       <c r="R147" t="n">
-        <v>6811443</v>
+        <v>6811594</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15362,10 +15362,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250328</v>
+        <v>130250266</v>
       </c>
       <c r="B148" t="n">
-        <v>78969</v>
+        <v>79801</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15373,21 +15373,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15397,10 +15397,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445329</v>
+        <v>445580</v>
       </c>
       <c r="R148" t="n">
-        <v>6811272</v>
+        <v>6811443</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15774,38 +15774,42 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130250319</v>
+        <v>130250317</v>
       </c>
       <c r="B152" t="n">
-        <v>97834</v>
+        <v>57851</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -15813,10 +15817,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>445554</v>
+        <v>445487</v>
       </c>
       <c r="R152" t="n">
-        <v>6811457</v>
+        <v>6811335</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15857,7 +15861,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15876,10 +15879,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130250326</v>
+        <v>130250286</v>
       </c>
       <c r="B153" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15887,34 +15890,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>445235</v>
+        <v>445540</v>
       </c>
       <c r="R153" t="n">
-        <v>6811325</v>
+        <v>6811525</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15973,45 +15984,53 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130250329</v>
+        <v>130250276</v>
       </c>
       <c r="B154" t="n">
-        <v>78969</v>
+        <v>57044</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>445323</v>
+        <v>445328</v>
       </c>
       <c r="R154" t="n">
-        <v>6811270</v>
+        <v>6811392</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16070,45 +16089,49 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130250381</v>
+        <v>130250319</v>
       </c>
       <c r="B155" t="n">
-        <v>79211</v>
+        <v>97834</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>445351</v>
+        <v>445554</v>
       </c>
       <c r="R155" t="n">
-        <v>6811495</v>
+        <v>6811457</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16149,6 +16172,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -16167,10 +16191,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250335</v>
+        <v>130250381</v>
       </c>
       <c r="B156" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16178,21 +16202,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16202,10 +16226,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445372</v>
+        <v>445351</v>
       </c>
       <c r="R156" t="n">
-        <v>6811595</v>
+        <v>6811495</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16264,7 +16288,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130250341</v>
+        <v>130250335</v>
       </c>
       <c r="B157" t="n">
         <v>78968</v>
@@ -16299,10 +16323,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>445383</v>
+        <v>445372</v>
       </c>
       <c r="R157" t="n">
-        <v>6811286</v>
+        <v>6811595</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16361,7 +16385,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130250336</v>
+        <v>130250341</v>
       </c>
       <c r="B158" t="n">
         <v>78968</v>
@@ -16396,10 +16420,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>445413</v>
+        <v>445383</v>
       </c>
       <c r="R158" t="n">
-        <v>6811568</v>
+        <v>6811286</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16458,10 +16482,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130250317</v>
+        <v>130250336</v>
       </c>
       <c r="B159" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16469,42 +16493,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>445487</v>
+        <v>445413</v>
       </c>
       <c r="R159" t="n">
-        <v>6811335</v>
+        <v>6811568</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16563,10 +16579,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130250286</v>
+        <v>130250326</v>
       </c>
       <c r="B160" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16574,42 +16590,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>445540</v>
+        <v>445235</v>
       </c>
       <c r="R160" t="n">
-        <v>6811525</v>
+        <v>6811325</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16668,53 +16676,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250276</v>
+        <v>130250329</v>
       </c>
       <c r="B161" t="n">
-        <v>57044</v>
+        <v>78969</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445328</v>
+        <v>445323</v>
       </c>
       <c r="R161" t="n">
-        <v>6811392</v>
+        <v>6811270</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17670,10 +17670,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130250347</v>
+        <v>130250290</v>
       </c>
       <c r="B171" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17681,34 +17681,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>445334</v>
+        <v>445457</v>
       </c>
       <c r="R171" t="n">
-        <v>6811304</v>
+        <v>6811507</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17767,10 +17775,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130250260</v>
+        <v>130250347</v>
       </c>
       <c r="B172" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17778,21 +17786,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17802,10 +17810,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>445425</v>
+        <v>445334</v>
       </c>
       <c r="R172" t="n">
-        <v>6811413</v>
+        <v>6811304</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17864,10 +17872,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130250388</v>
+        <v>130250260</v>
       </c>
       <c r="B173" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17875,21 +17883,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17899,10 +17907,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>445362</v>
+        <v>445425</v>
       </c>
       <c r="R173" t="n">
-        <v>6811289</v>
+        <v>6811413</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17961,7 +17969,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130250368</v>
+        <v>130250388</v>
       </c>
       <c r="B174" t="n">
         <v>79211</v>
@@ -17996,10 +18004,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>445385</v>
+        <v>445362</v>
       </c>
       <c r="R174" t="n">
-        <v>6811579</v>
+        <v>6811289</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18058,7 +18066,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130250396</v>
+        <v>130250368</v>
       </c>
       <c r="B175" t="n">
         <v>79211</v>
@@ -18093,10 +18101,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>445480</v>
+        <v>445385</v>
       </c>
       <c r="R175" t="n">
-        <v>6811420</v>
+        <v>6811579</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18155,10 +18163,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130250346</v>
+        <v>130250396</v>
       </c>
       <c r="B176" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18166,21 +18174,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18190,10 +18198,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>445322</v>
+        <v>445480</v>
       </c>
       <c r="R176" t="n">
-        <v>6811363</v>
+        <v>6811420</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18252,10 +18260,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250290</v>
+        <v>130250346</v>
       </c>
       <c r="B177" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18263,42 +18271,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445457</v>
+        <v>445322</v>
       </c>
       <c r="R177" t="n">
-        <v>6811507</v>
+        <v>6811363</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250325</v>
+        <v>130250333</v>
       </c>
       <c r="B180" t="n">
-        <v>78969</v>
+        <v>78968</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,21 +18562,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18586,10 +18586,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445457</v>
+        <v>445201</v>
       </c>
       <c r="R180" t="n">
-        <v>6811516</v>
+        <v>6811621</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,7 +18648,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250333</v>
+        <v>130250344</v>
       </c>
       <c r="B181" t="n">
         <v>78968</v>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445201</v>
+        <v>445358</v>
       </c>
       <c r="R181" t="n">
-        <v>6811621</v>
+        <v>6811433</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,10 +18745,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250344</v>
+        <v>130250383</v>
       </c>
       <c r="B182" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18756,21 +18756,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18780,10 +18780,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445358</v>
+        <v>445209</v>
       </c>
       <c r="R182" t="n">
-        <v>6811433</v>
+        <v>6811451</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,7 +18842,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250383</v>
+        <v>130250406</v>
       </c>
       <c r="B183" t="n">
         <v>79211</v>
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445209</v>
+        <v>445341</v>
       </c>
       <c r="R183" t="n">
-        <v>6811451</v>
+        <v>6811293</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,7 +18939,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250406</v>
+        <v>130250377</v>
       </c>
       <c r="B184" t="n">
         <v>79211</v>
@@ -18974,10 +18974,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445341</v>
+        <v>445454</v>
       </c>
       <c r="R184" t="n">
-        <v>6811293</v>
+        <v>6811502</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19036,10 +19036,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250377</v>
+        <v>130250311</v>
       </c>
       <c r="B185" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19047,34 +19047,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445454</v>
+        <v>445333</v>
       </c>
       <c r="R185" t="n">
-        <v>6811502</v>
+        <v>6811358</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19133,7 +19141,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130250311</v>
+        <v>130250284</v>
       </c>
       <c r="B186" t="n">
         <v>57851</v>
@@ -19176,10 +19184,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>445333</v>
+        <v>445310</v>
       </c>
       <c r="R186" t="n">
-        <v>6811358</v>
+        <v>6811604</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19238,10 +19246,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>130250284</v>
+        <v>130250325</v>
       </c>
       <c r="B187" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19249,42 +19257,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>445310</v>
+        <v>445457</v>
       </c>
       <c r="R187" t="n">
-        <v>6811604</v>
+        <v>6811516</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19343,54 +19343,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>130250330</v>
+        <v>130250257</v>
       </c>
       <c r="B188" t="n">
-        <v>8451</v>
+        <v>79830</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>445218</v>
+        <v>445474</v>
       </c>
       <c r="R188" t="n">
-        <v>6811247</v>
+        <v>6811433</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19431,7 +19422,6 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -19450,10 +19440,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>130250257</v>
+        <v>130250363</v>
       </c>
       <c r="B189" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19461,21 +19451,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19485,10 +19475,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>445474</v>
+        <v>445229</v>
       </c>
       <c r="R189" t="n">
-        <v>6811433</v>
+        <v>6811687</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19547,10 +19537,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130250363</v>
+        <v>130250312</v>
       </c>
       <c r="B190" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19558,34 +19548,42 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>445229</v>
+        <v>445324</v>
       </c>
       <c r="R190" t="n">
-        <v>6811687</v>
+        <v>6811362</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19644,7 +19642,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130250312</v>
+        <v>130250306</v>
       </c>
       <c r="B191" t="n">
         <v>57851</v>
@@ -19677,7 +19675,7 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
@@ -19687,10 +19685,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>445324</v>
+        <v>445401</v>
       </c>
       <c r="R191" t="n">
-        <v>6811362</v>
+        <v>6811439</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19749,10 +19747,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130250306</v>
+        <v>130250268</v>
       </c>
       <c r="B192" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19760,16 +19758,16 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19792,10 +19790,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>445401</v>
+        <v>445421</v>
       </c>
       <c r="R192" t="n">
-        <v>6811439</v>
+        <v>6811460</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19854,40 +19852,41 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130250268</v>
+        <v>130250330</v>
       </c>
       <c r="B193" t="n">
-        <v>57854</v>
+        <v>8451</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -19897,10 +19896,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>445421</v>
+        <v>445218</v>
       </c>
       <c r="R193" t="n">
-        <v>6811460</v>
+        <v>6811247</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19941,6 +19940,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130250250</v>
+        <v>130250298</v>
       </c>
       <c r="B194" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19970,34 +19970,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445248</v>
+        <v>445232</v>
       </c>
       <c r="R194" t="n">
-        <v>6811642</v>
+        <v>6811448</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20056,10 +20064,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250370</v>
+        <v>130250300</v>
       </c>
       <c r="B195" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20067,34 +20075,42 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445542</v>
+        <v>445219</v>
       </c>
       <c r="R195" t="n">
-        <v>6811532</v>
+        <v>6811344</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20153,10 +20169,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250395</v>
+        <v>130250291</v>
       </c>
       <c r="B196" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20164,34 +20180,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445507</v>
+        <v>445385</v>
       </c>
       <c r="R196" t="n">
-        <v>6811412</v>
+        <v>6811504</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20250,10 +20274,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250256</v>
+        <v>130250281</v>
       </c>
       <c r="B197" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20261,34 +20285,42 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445484</v>
+        <v>445205</v>
       </c>
       <c r="R197" t="n">
-        <v>6811291</v>
+        <v>6811619</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20347,45 +20379,53 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250386</v>
+        <v>130250277</v>
       </c>
       <c r="B198" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445226</v>
+        <v>445202</v>
       </c>
       <c r="R198" t="n">
-        <v>6811348</v>
+        <v>6811655</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20444,53 +20484,45 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250355</v>
+        <v>130250250</v>
       </c>
       <c r="B199" t="n">
-        <v>57846</v>
+        <v>79830</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100110</v>
+        <v>6453</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445443</v>
+        <v>445248</v>
       </c>
       <c r="R199" t="n">
-        <v>6811494</v>
+        <v>6811642</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20549,10 +20581,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250298</v>
+        <v>130250370</v>
       </c>
       <c r="B200" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20560,42 +20592,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445232</v>
+        <v>445542</v>
       </c>
       <c r="R200" t="n">
-        <v>6811448</v>
+        <v>6811532</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20654,10 +20678,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250300</v>
+        <v>130250395</v>
       </c>
       <c r="B201" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20665,42 +20689,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445219</v>
+        <v>445507</v>
       </c>
       <c r="R201" t="n">
-        <v>6811344</v>
+        <v>6811412</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20759,10 +20775,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250291</v>
+        <v>130250256</v>
       </c>
       <c r="B202" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20770,42 +20786,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445385</v>
+        <v>445484</v>
       </c>
       <c r="R202" t="n">
-        <v>6811504</v>
+        <v>6811291</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20864,10 +20872,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250281</v>
+        <v>130250386</v>
       </c>
       <c r="B203" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20875,42 +20883,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445205</v>
+        <v>445226</v>
       </c>
       <c r="R203" t="n">
-        <v>6811619</v>
+        <v>6811348</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20969,10 +20969,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250277</v>
+        <v>130250355</v>
       </c>
       <c r="B204" t="n">
-        <v>57044</v>
+        <v>57846</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20980,21 +20980,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21002,7 +21002,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445202</v>
+        <v>445443</v>
       </c>
       <c r="R204" t="n">
-        <v>6811655</v>
+        <v>6811494</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250280</v>
+        <v>130250264</v>
       </c>
       <c r="B206" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,42 +21182,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445179</v>
+        <v>445315</v>
       </c>
       <c r="R206" t="n">
-        <v>6811467</v>
+        <v>6811230</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21276,10 +21268,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250310</v>
+        <v>130250254</v>
       </c>
       <c r="B207" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21287,42 +21279,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445339</v>
+        <v>445194</v>
       </c>
       <c r="R207" t="n">
-        <v>6811359</v>
+        <v>6811426</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21381,10 +21365,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250305</v>
+        <v>130250258</v>
       </c>
       <c r="B208" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21392,42 +21376,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445448</v>
+        <v>445470</v>
       </c>
       <c r="R208" t="n">
-        <v>6811432</v>
+        <v>6811435</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21486,10 +21462,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250283</v>
+        <v>130250249</v>
       </c>
       <c r="B209" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21497,42 +21473,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445303</v>
+        <v>445200</v>
       </c>
       <c r="R209" t="n">
-        <v>6811621</v>
+        <v>6811598</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21591,10 +21559,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250264</v>
+        <v>130250392</v>
       </c>
       <c r="B210" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21602,21 +21570,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21626,10 +21594,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445315</v>
+        <v>445487</v>
       </c>
       <c r="R210" t="n">
-        <v>6811230</v>
+        <v>6811345</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21688,10 +21656,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250254</v>
+        <v>130250389</v>
       </c>
       <c r="B211" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21699,21 +21667,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21723,10 +21691,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445194</v>
+        <v>445483</v>
       </c>
       <c r="R211" t="n">
-        <v>6811426</v>
+        <v>6811288</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21785,10 +21753,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250258</v>
+        <v>130250367</v>
       </c>
       <c r="B212" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21796,21 +21764,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21820,10 +21788,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445470</v>
+        <v>445376</v>
       </c>
       <c r="R212" t="n">
-        <v>6811435</v>
+        <v>6811581</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21882,10 +21850,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250249</v>
+        <v>130250280</v>
       </c>
       <c r="B213" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21893,34 +21861,42 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445200</v>
+        <v>445179</v>
       </c>
       <c r="R213" t="n">
-        <v>6811598</v>
+        <v>6811467</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21979,10 +21955,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250392</v>
+        <v>130250310</v>
       </c>
       <c r="B214" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21990,34 +21966,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445487</v>
+        <v>445339</v>
       </c>
       <c r="R214" t="n">
-        <v>6811345</v>
+        <v>6811359</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22076,10 +22060,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250389</v>
+        <v>130250305</v>
       </c>
       <c r="B215" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22087,34 +22071,42 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445483</v>
+        <v>445448</v>
       </c>
       <c r="R215" t="n">
-        <v>6811288</v>
+        <v>6811432</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22173,10 +22165,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250367</v>
+        <v>130250283</v>
       </c>
       <c r="B216" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22184,34 +22176,42 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445376</v>
+        <v>445303</v>
       </c>
       <c r="R216" t="n">
-        <v>6811581</v>
+        <v>6811621</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130250393</v>
+        <v>130250301</v>
       </c>
       <c r="B232" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23772,34 +23772,42 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>445477</v>
+        <v>445222</v>
       </c>
       <c r="R232" t="n">
-        <v>6811356</v>
+        <v>6811352</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23858,10 +23866,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130250380</v>
+        <v>130250288</v>
       </c>
       <c r="B233" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23869,34 +23877,42 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>445369</v>
+        <v>445564</v>
       </c>
       <c r="R233" t="n">
-        <v>6811486</v>
+        <v>6811446</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23955,10 +23971,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130250408</v>
+        <v>130250316</v>
       </c>
       <c r="B234" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23966,34 +23982,42 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445323</v>
+        <v>445524</v>
       </c>
       <c r="R234" t="n">
-        <v>6811251</v>
+        <v>6811486</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24052,10 +24076,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130250246</v>
+        <v>130250393</v>
       </c>
       <c r="B235" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24063,21 +24087,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24087,10 +24111,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>445182</v>
+        <v>445477</v>
       </c>
       <c r="R235" t="n">
-        <v>6811329</v>
+        <v>6811356</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24149,7 +24173,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130250405</v>
+        <v>130250380</v>
       </c>
       <c r="B236" t="n">
         <v>79211</v>
@@ -24184,10 +24208,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>445324</v>
+        <v>445369</v>
       </c>
       <c r="R236" t="n">
-        <v>6811291</v>
+        <v>6811486</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24246,7 +24270,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130250397</v>
+        <v>130250408</v>
       </c>
       <c r="B237" t="n">
         <v>79211</v>
@@ -24281,10 +24305,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>445441</v>
+        <v>445323</v>
       </c>
       <c r="R237" t="n">
-        <v>6811411</v>
+        <v>6811251</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24343,10 +24367,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130250301</v>
+        <v>130250246</v>
       </c>
       <c r="B238" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24354,42 +24378,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>445222</v>
+        <v>445182</v>
       </c>
       <c r="R238" t="n">
-        <v>6811352</v>
+        <v>6811329</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24448,10 +24464,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130250288</v>
+        <v>130250405</v>
       </c>
       <c r="B239" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24459,42 +24475,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>445564</v>
+        <v>445324</v>
       </c>
       <c r="R239" t="n">
-        <v>6811446</v>
+        <v>6811291</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24553,10 +24561,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130250316</v>
+        <v>130250397</v>
       </c>
       <c r="B240" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24564,42 +24572,34 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>445524</v>
+        <v>445441</v>
       </c>
       <c r="R240" t="n">
-        <v>6811486</v>
+        <v>6811411</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250295</v>
+        <v>130250337</v>
       </c>
       <c r="B242" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,42 +24766,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445263</v>
+        <v>445441</v>
       </c>
       <c r="R242" t="n">
-        <v>6811480</v>
+        <v>6811531</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -24860,10 +24852,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130250337</v>
+        <v>130250384</v>
       </c>
       <c r="B243" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -24871,21 +24863,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -24895,10 +24887,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>445441</v>
+        <v>445209</v>
       </c>
       <c r="R243" t="n">
-        <v>6811531</v>
+        <v>6811374</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -24957,7 +24949,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130250384</v>
+        <v>130250375</v>
       </c>
       <c r="B244" t="n">
         <v>79211</v>
@@ -24992,10 +24984,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>445209</v>
+        <v>445492</v>
       </c>
       <c r="R244" t="n">
-        <v>6811374</v>
+        <v>6811496</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25054,7 +25046,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130250375</v>
+        <v>130250378</v>
       </c>
       <c r="B245" t="n">
         <v>79211</v>
@@ -25089,10 +25081,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>445492</v>
+        <v>445421</v>
       </c>
       <c r="R245" t="n">
-        <v>6811496</v>
+        <v>6811499</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25151,7 +25143,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130250378</v>
+        <v>130250407</v>
       </c>
       <c r="B246" t="n">
         <v>79211</v>
@@ -25186,10 +25178,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>445421</v>
+        <v>445299</v>
       </c>
       <c r="R246" t="n">
-        <v>6811499</v>
+        <v>6811253</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25248,7 +25240,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250407</v>
+        <v>130250403</v>
       </c>
       <c r="B247" t="n">
         <v>79211</v>
@@ -25283,10 +25275,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445299</v>
+        <v>445337</v>
       </c>
       <c r="R247" t="n">
-        <v>6811253</v>
+        <v>6811372</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25345,7 +25337,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250403</v>
+        <v>130250359</v>
       </c>
       <c r="B248" t="n">
         <v>79211</v>
@@ -25380,10 +25372,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445337</v>
+        <v>445161</v>
       </c>
       <c r="R248" t="n">
-        <v>6811372</v>
+        <v>6811404</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25442,10 +25434,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250359</v>
+        <v>130250295</v>
       </c>
       <c r="B249" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25453,34 +25445,42 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445161</v>
+        <v>445263</v>
       </c>
       <c r="R249" t="n">
-        <v>6811404</v>
+        <v>6811480</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -11047,10 +11047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130250267</v>
+        <v>130250402</v>
       </c>
       <c r="B105" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,37 +11058,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445503</v>
+        <v>445364</v>
       </c>
       <c r="R105" t="n">
-        <v>6811332</v>
+        <v>6811345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11129,29 +11126,8 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11653,45 +11629,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130250402</v>
+        <v>130250270</v>
       </c>
       <c r="B111" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445364</v>
+        <v>445426</v>
       </c>
       <c r="R111" t="n">
-        <v>6811345</v>
+        <v>6811491</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11750,32 +11734,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130250302</v>
+        <v>130250272</v>
       </c>
       <c r="B112" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11783,7 +11767,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11793,10 +11777,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445239</v>
+        <v>445468</v>
       </c>
       <c r="R112" t="n">
-        <v>6811358</v>
+        <v>6811258</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11855,32 +11839,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130250270</v>
+        <v>130250302</v>
       </c>
       <c r="B113" t="n">
-        <v>57044</v>
+        <v>57851</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11888,7 +11872,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -11898,10 +11882,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445426</v>
+        <v>445239</v>
       </c>
       <c r="R113" t="n">
-        <v>6811491</v>
+        <v>6811358</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11960,42 +11944,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130250272</v>
+        <v>130250267</v>
       </c>
       <c r="B114" t="n">
-        <v>57044</v>
+        <v>91761</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12003,10 +11982,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445468</v>
+        <v>445503</v>
       </c>
       <c r="R114" t="n">
-        <v>6811258</v>
+        <v>6811332</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12047,8 +12026,29 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12566,10 +12566,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130250394</v>
+        <v>130250259</v>
       </c>
       <c r="B120" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12577,37 +12577,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445495</v>
+        <v>445441</v>
       </c>
       <c r="R120" t="n">
-        <v>6811385</v>
+        <v>6811433</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12648,7 +12645,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12667,10 +12663,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130250259</v>
+        <v>130250404</v>
       </c>
       <c r="B121" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12678,21 +12674,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12702,10 +12698,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445441</v>
+        <v>445330</v>
       </c>
       <c r="R121" t="n">
-        <v>6811433</v>
+        <v>6811333</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12764,7 +12760,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130250404</v>
+        <v>130250360</v>
       </c>
       <c r="B122" t="n">
         <v>79211</v>
@@ -12799,10 +12795,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445330</v>
+        <v>445194</v>
       </c>
       <c r="R122" t="n">
-        <v>6811333</v>
+        <v>6811530</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12861,10 +12857,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130250360</v>
+        <v>130250338</v>
       </c>
       <c r="B123" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12872,21 +12868,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12896,10 +12892,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445194</v>
+        <v>445492</v>
       </c>
       <c r="R123" t="n">
-        <v>6811530</v>
+        <v>6811520</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12958,10 +12954,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130250338</v>
+        <v>130250399</v>
       </c>
       <c r="B124" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12969,21 +12965,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12993,10 +12989,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445492</v>
+        <v>445416</v>
       </c>
       <c r="R124" t="n">
-        <v>6811520</v>
+        <v>6811445</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13055,7 +13051,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130250399</v>
+        <v>130250394</v>
       </c>
       <c r="B125" t="n">
         <v>79211</v>
@@ -13084,16 +13080,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>445416</v>
+        <v>445495</v>
       </c>
       <c r="R125" t="n">
-        <v>6811445</v>
+        <v>6811385</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13134,6 +13133,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13249,7 +13249,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130250293</v>
+        <v>130250315</v>
       </c>
       <c r="B127" t="n">
         <v>57851</v>
@@ -13282,7 +13282,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -13292,10 +13292,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>445303</v>
+        <v>445317</v>
       </c>
       <c r="R127" t="n">
-        <v>6811490</v>
+        <v>6811271</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13564,7 +13564,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130250315</v>
+        <v>130250293</v>
       </c>
       <c r="B130" t="n">
         <v>57851</v>
@@ -13597,7 +13597,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>445317</v>
+        <v>445303</v>
       </c>
       <c r="R130" t="n">
-        <v>6811271</v>
+        <v>6811490</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130250255</v>
+        <v>130250321</v>
       </c>
       <c r="B131" t="n">
-        <v>79830</v>
+        <v>78969</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13680,21 +13680,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13704,10 +13704,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>445480</v>
+        <v>445326</v>
       </c>
       <c r="R131" t="n">
-        <v>6811273</v>
+        <v>6811613</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13766,10 +13766,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130250321</v>
+        <v>130250255</v>
       </c>
       <c r="B132" t="n">
-        <v>78969</v>
+        <v>79830</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13777,21 +13777,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>445326</v>
+        <v>445480</v>
       </c>
       <c r="R132" t="n">
-        <v>6811613</v>
+        <v>6811273</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130250390</v>
+        <v>130250369</v>
       </c>
       <c r="B136" t="n">
         <v>79211</v>
@@ -14189,10 +14189,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>445492</v>
+        <v>445518</v>
       </c>
       <c r="R136" t="n">
-        <v>6811299</v>
+        <v>6811539</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14251,7 +14251,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130250369</v>
+        <v>130250356</v>
       </c>
       <c r="B137" t="n">
         <v>79211</v>
@@ -14286,10 +14286,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>445518</v>
+        <v>445227</v>
       </c>
       <c r="R137" t="n">
-        <v>6811539</v>
+        <v>6811254</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14348,7 +14348,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130250356</v>
+        <v>130250390</v>
       </c>
       <c r="B138" t="n">
         <v>79211</v>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>445227</v>
+        <v>445492</v>
       </c>
       <c r="R138" t="n">
-        <v>6811254</v>
+        <v>6811299</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14861,45 +14861,53 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130250362</v>
+        <v>130250274</v>
       </c>
       <c r="B143" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>445218</v>
+        <v>445376</v>
       </c>
       <c r="R143" t="n">
-        <v>6811594</v>
+        <v>6811389</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14958,7 +14966,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130250274</v>
+        <v>130250271</v>
       </c>
       <c r="B144" t="n">
         <v>57044</v>
@@ -15001,10 +15009,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>445376</v>
+        <v>445375</v>
       </c>
       <c r="R144" t="n">
-        <v>6811389</v>
+        <v>6811502</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15063,53 +15071,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130250271</v>
+        <v>130250362</v>
       </c>
       <c r="B145" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>445375</v>
+        <v>445218</v>
       </c>
       <c r="R145" t="n">
-        <v>6811502</v>
+        <v>6811594</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15168,10 +15168,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130250328</v>
+        <v>130250297</v>
       </c>
       <c r="B146" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15179,34 +15179,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>445329</v>
+        <v>445239</v>
       </c>
       <c r="R146" t="n">
-        <v>6811272</v>
+        <v>6811474</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15265,10 +15273,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130250323</v>
+        <v>130250292</v>
       </c>
       <c r="B147" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15276,34 +15284,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>445371</v>
+        <v>445384</v>
       </c>
       <c r="R147" t="n">
-        <v>6811594</v>
+        <v>6811490</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15362,10 +15378,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130250266</v>
+        <v>130250303</v>
       </c>
       <c r="B148" t="n">
-        <v>79801</v>
+        <v>57851</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15373,34 +15389,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>445580</v>
+        <v>445389</v>
       </c>
       <c r="R148" t="n">
-        <v>6811443</v>
+        <v>6811264</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15459,10 +15483,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130250297</v>
+        <v>130250323</v>
       </c>
       <c r="B149" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15470,42 +15494,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>445239</v>
+        <v>445371</v>
       </c>
       <c r="R149" t="n">
-        <v>6811474</v>
+        <v>6811594</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15564,10 +15580,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130250292</v>
+        <v>130250266</v>
       </c>
       <c r="B150" t="n">
-        <v>57851</v>
+        <v>79801</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15575,42 +15591,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>445384</v>
+        <v>445580</v>
       </c>
       <c r="R150" t="n">
-        <v>6811490</v>
+        <v>6811443</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15669,10 +15677,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130250303</v>
+        <v>130250328</v>
       </c>
       <c r="B151" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15680,42 +15688,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>445389</v>
+        <v>445329</v>
       </c>
       <c r="R151" t="n">
-        <v>6811264</v>
+        <v>6811272</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15774,10 +15774,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130250317</v>
+        <v>130250381</v>
       </c>
       <c r="B152" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15785,42 +15785,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>445487</v>
+        <v>445351</v>
       </c>
       <c r="R152" t="n">
-        <v>6811335</v>
+        <v>6811495</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15879,32 +15871,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130250286</v>
+        <v>130250276</v>
       </c>
       <c r="B153" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15912,7 +15904,7 @@
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
@@ -15922,10 +15914,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>445540</v>
+        <v>445328</v>
       </c>
       <c r="R153" t="n">
-        <v>6811525</v>
+        <v>6811392</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15984,32 +15976,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130250276</v>
+        <v>130250317</v>
       </c>
       <c r="B154" t="n">
-        <v>57044</v>
+        <v>57851</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16017,7 +16009,7 @@
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
@@ -16027,10 +16019,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>445328</v>
+        <v>445487</v>
       </c>
       <c r="R154" t="n">
-        <v>6811392</v>
+        <v>6811335</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16089,49 +16081,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130250319</v>
+        <v>130250326</v>
       </c>
       <c r="B155" t="n">
-        <v>97834</v>
+        <v>78969</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>445554</v>
+        <v>445235</v>
       </c>
       <c r="R155" t="n">
-        <v>6811457</v>
+        <v>6811325</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16172,7 +16160,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -16191,10 +16178,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130250381</v>
+        <v>130250329</v>
       </c>
       <c r="B156" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16202,21 +16189,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16226,10 +16213,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>445351</v>
+        <v>445323</v>
       </c>
       <c r="R156" t="n">
-        <v>6811495</v>
+        <v>6811270</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16579,10 +16566,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130250326</v>
+        <v>130250286</v>
       </c>
       <c r="B160" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16590,34 +16577,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>445235</v>
+        <v>445540</v>
       </c>
       <c r="R160" t="n">
-        <v>6811325</v>
+        <v>6811525</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16676,45 +16671,49 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130250329</v>
+        <v>130250319</v>
       </c>
       <c r="B161" t="n">
-        <v>78969</v>
+        <v>97834</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>445323</v>
+        <v>445554</v>
       </c>
       <c r="R161" t="n">
-        <v>6811270</v>
+        <v>6811457</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16755,6 +16754,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130250340</v>
+        <v>130250391</v>
       </c>
       <c r="B162" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16784,21 +16784,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>445366</v>
+        <v>445499</v>
       </c>
       <c r="R162" t="n">
-        <v>6811298</v>
+        <v>6811328</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16870,10 +16870,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130250248</v>
+        <v>130250398</v>
       </c>
       <c r="B163" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16881,21 +16881,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16905,10 +16905,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>445243</v>
+        <v>445426</v>
       </c>
       <c r="R163" t="n">
-        <v>6811593</v>
+        <v>6811434</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16967,10 +16967,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130250391</v>
+        <v>130250340</v>
       </c>
       <c r="B164" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16978,21 +16978,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17002,10 +17002,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>445499</v>
+        <v>445366</v>
       </c>
       <c r="R164" t="n">
-        <v>6811328</v>
+        <v>6811298</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17064,10 +17064,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130250398</v>
+        <v>130250248</v>
       </c>
       <c r="B165" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17075,21 +17075,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17099,10 +17099,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>445426</v>
+        <v>445243</v>
       </c>
       <c r="R165" t="n">
-        <v>6811434</v>
+        <v>6811593</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17355,7 +17355,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130250279</v>
+        <v>130250287</v>
       </c>
       <c r="B168" t="n">
         <v>57851</v>
@@ -17398,10 +17398,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>445165</v>
+        <v>445575</v>
       </c>
       <c r="R168" t="n">
-        <v>6811426</v>
+        <v>6811437</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17460,7 +17460,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130250287</v>
+        <v>130250279</v>
       </c>
       <c r="B169" t="n">
         <v>57851</v>
@@ -17503,10 +17503,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>445575</v>
+        <v>445165</v>
       </c>
       <c r="R169" t="n">
-        <v>6811437</v>
+        <v>6811426</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17670,10 +17670,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130250290</v>
+        <v>130250388</v>
       </c>
       <c r="B171" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17681,42 +17681,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>445457</v>
+        <v>445362</v>
       </c>
       <c r="R171" t="n">
-        <v>6811507</v>
+        <v>6811289</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17775,10 +17767,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130250347</v>
+        <v>130250368</v>
       </c>
       <c r="B172" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17786,21 +17778,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17810,10 +17802,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>445334</v>
+        <v>445385</v>
       </c>
       <c r="R172" t="n">
-        <v>6811304</v>
+        <v>6811579</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17872,10 +17864,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130250260</v>
+        <v>130250396</v>
       </c>
       <c r="B173" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17883,21 +17875,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17907,10 +17899,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>445425</v>
+        <v>445480</v>
       </c>
       <c r="R173" t="n">
-        <v>6811413</v>
+        <v>6811420</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17969,10 +17961,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130250388</v>
+        <v>130250347</v>
       </c>
       <c r="B174" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17980,21 +17972,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18004,10 +17996,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>445362</v>
+        <v>445334</v>
       </c>
       <c r="R174" t="n">
-        <v>6811289</v>
+        <v>6811304</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18066,10 +18058,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130250368</v>
+        <v>130250260</v>
       </c>
       <c r="B175" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18077,21 +18069,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18101,10 +18093,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>445385</v>
+        <v>445425</v>
       </c>
       <c r="R175" t="n">
-        <v>6811579</v>
+        <v>6811413</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18163,10 +18155,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130250396</v>
+        <v>130250346</v>
       </c>
       <c r="B176" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18174,21 +18166,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18198,10 +18190,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>445480</v>
+        <v>445322</v>
       </c>
       <c r="R176" t="n">
-        <v>6811420</v>
+        <v>6811363</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18260,10 +18252,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130250346</v>
+        <v>130250290</v>
       </c>
       <c r="B177" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18271,34 +18263,42 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>445322</v>
+        <v>445457</v>
       </c>
       <c r="R177" t="n">
-        <v>6811363</v>
+        <v>6811507</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18551,10 +18551,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130250333</v>
+        <v>130250311</v>
       </c>
       <c r="B180" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18562,34 +18562,42 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>445201</v>
+        <v>445333</v>
       </c>
       <c r="R180" t="n">
-        <v>6811621</v>
+        <v>6811358</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18648,10 +18656,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130250344</v>
+        <v>130250284</v>
       </c>
       <c r="B181" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18659,34 +18667,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>445358</v>
+        <v>445310</v>
       </c>
       <c r="R181" t="n">
-        <v>6811433</v>
+        <v>6811604</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18745,7 +18761,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130250383</v>
+        <v>130250377</v>
       </c>
       <c r="B182" t="n">
         <v>79211</v>
@@ -18780,10 +18796,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>445209</v>
+        <v>445454</v>
       </c>
       <c r="R182" t="n">
-        <v>6811451</v>
+        <v>6811502</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18842,10 +18858,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130250406</v>
+        <v>130250333</v>
       </c>
       <c r="B183" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18853,21 +18869,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18877,10 +18893,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>445341</v>
+        <v>445201</v>
       </c>
       <c r="R183" t="n">
-        <v>6811293</v>
+        <v>6811621</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18939,10 +18955,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130250377</v>
+        <v>130250344</v>
       </c>
       <c r="B184" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18950,21 +18966,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18974,10 +18990,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>445454</v>
+        <v>445358</v>
       </c>
       <c r="R184" t="n">
-        <v>6811502</v>
+        <v>6811433</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19036,10 +19052,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130250311</v>
+        <v>130250383</v>
       </c>
       <c r="B185" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19047,42 +19063,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>445333</v>
+        <v>445209</v>
       </c>
       <c r="R185" t="n">
-        <v>6811358</v>
+        <v>6811451</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19141,10 +19149,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130250284</v>
+        <v>130250406</v>
       </c>
       <c r="B186" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19152,42 +19160,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>445310</v>
+        <v>445341</v>
       </c>
       <c r="R186" t="n">
-        <v>6811604</v>
+        <v>6811293</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19343,10 +19343,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>130250257</v>
+        <v>130250363</v>
       </c>
       <c r="B188" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19354,21 +19354,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19378,10 +19378,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>445474</v>
+        <v>445229</v>
       </c>
       <c r="R188" t="n">
-        <v>6811433</v>
+        <v>6811687</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19440,10 +19440,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>130250363</v>
+        <v>130250257</v>
       </c>
       <c r="B189" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19451,21 +19451,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>445229</v>
+        <v>445474</v>
       </c>
       <c r="R189" t="n">
-        <v>6811687</v>
+        <v>6811433</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19959,10 +19959,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130250298</v>
+        <v>130250250</v>
       </c>
       <c r="B194" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19970,42 +19970,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>445232</v>
+        <v>445248</v>
       </c>
       <c r="R194" t="n">
-        <v>6811448</v>
+        <v>6811642</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20064,10 +20056,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130250300</v>
+        <v>130250370</v>
       </c>
       <c r="B195" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20075,42 +20067,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>445219</v>
+        <v>445542</v>
       </c>
       <c r="R195" t="n">
-        <v>6811344</v>
+        <v>6811532</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20169,10 +20153,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130250291</v>
+        <v>130250395</v>
       </c>
       <c r="B196" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20180,42 +20164,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>445385</v>
+        <v>445507</v>
       </c>
       <c r="R196" t="n">
-        <v>6811504</v>
+        <v>6811412</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20274,10 +20250,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130250281</v>
+        <v>130250256</v>
       </c>
       <c r="B197" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20285,42 +20261,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>445205</v>
+        <v>445484</v>
       </c>
       <c r="R197" t="n">
-        <v>6811619</v>
+        <v>6811291</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20379,53 +20347,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130250277</v>
+        <v>130250386</v>
       </c>
       <c r="B198" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>445202</v>
+        <v>445226</v>
       </c>
       <c r="R198" t="n">
-        <v>6811655</v>
+        <v>6811348</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20484,45 +20444,53 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130250250</v>
+        <v>130250355</v>
       </c>
       <c r="B199" t="n">
-        <v>79830</v>
+        <v>57846</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6453</v>
+        <v>100110</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>445248</v>
+        <v>445443</v>
       </c>
       <c r="R199" t="n">
-        <v>6811642</v>
+        <v>6811494</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20581,45 +20549,53 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130250370</v>
+        <v>130250277</v>
       </c>
       <c r="B200" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>445542</v>
+        <v>445202</v>
       </c>
       <c r="R200" t="n">
-        <v>6811532</v>
+        <v>6811655</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20678,10 +20654,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130250395</v>
+        <v>130250298</v>
       </c>
       <c r="B201" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20689,34 +20665,42 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>445507</v>
+        <v>445232</v>
       </c>
       <c r="R201" t="n">
-        <v>6811412</v>
+        <v>6811448</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20775,10 +20759,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>130250256</v>
+        <v>130250281</v>
       </c>
       <c r="B202" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20786,34 +20770,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>445484</v>
+        <v>445205</v>
       </c>
       <c r="R202" t="n">
-        <v>6811291</v>
+        <v>6811619</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20872,10 +20864,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>130250386</v>
+        <v>130250300</v>
       </c>
       <c r="B203" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20883,34 +20875,42 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>445226</v>
+        <v>445219</v>
       </c>
       <c r="R203" t="n">
-        <v>6811348</v>
+        <v>6811344</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20969,32 +20969,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>130250355</v>
+        <v>130250291</v>
       </c>
       <c r="B204" t="n">
-        <v>57846</v>
+        <v>57851</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21002,7 +21002,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -21012,10 +21012,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>445443</v>
+        <v>445385</v>
       </c>
       <c r="R204" t="n">
-        <v>6811494</v>
+        <v>6811504</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21171,10 +21171,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130250264</v>
+        <v>130250392</v>
       </c>
       <c r="B206" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21182,21 +21182,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21206,10 +21206,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>445315</v>
+        <v>445487</v>
       </c>
       <c r="R206" t="n">
-        <v>6811230</v>
+        <v>6811345</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21268,10 +21268,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130250254</v>
+        <v>130250389</v>
       </c>
       <c r="B207" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21279,21 +21279,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21303,10 +21303,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>445194</v>
+        <v>445483</v>
       </c>
       <c r="R207" t="n">
-        <v>6811426</v>
+        <v>6811288</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21365,10 +21365,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130250258</v>
+        <v>130250367</v>
       </c>
       <c r="B208" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21376,21 +21376,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21400,10 +21400,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>445470</v>
+        <v>445376</v>
       </c>
       <c r="R208" t="n">
-        <v>6811435</v>
+        <v>6811581</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21462,10 +21462,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130250249</v>
+        <v>130250280</v>
       </c>
       <c r="B209" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21473,34 +21473,42 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>445200</v>
+        <v>445179</v>
       </c>
       <c r="R209" t="n">
-        <v>6811598</v>
+        <v>6811467</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21559,10 +21567,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130250392</v>
+        <v>130250283</v>
       </c>
       <c r="B210" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21570,34 +21578,42 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>445487</v>
+        <v>445303</v>
       </c>
       <c r="R210" t="n">
-        <v>6811345</v>
+        <v>6811621</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21656,10 +21672,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130250389</v>
+        <v>130250264</v>
       </c>
       <c r="B211" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21667,21 +21683,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21691,10 +21707,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>445483</v>
+        <v>445315</v>
       </c>
       <c r="R211" t="n">
-        <v>6811288</v>
+        <v>6811230</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21753,10 +21769,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130250367</v>
+        <v>130250254</v>
       </c>
       <c r="B212" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21764,21 +21780,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21788,10 +21804,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>445376</v>
+        <v>445194</v>
       </c>
       <c r="R212" t="n">
-        <v>6811581</v>
+        <v>6811426</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21850,10 +21866,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130250280</v>
+        <v>130250258</v>
       </c>
       <c r="B213" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21861,42 +21877,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>445179</v>
+        <v>445470</v>
       </c>
       <c r="R213" t="n">
-        <v>6811467</v>
+        <v>6811435</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21955,10 +21963,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130250310</v>
+        <v>130250249</v>
       </c>
       <c r="B214" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21966,42 +21974,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>445339</v>
+        <v>445200</v>
       </c>
       <c r="R214" t="n">
-        <v>6811359</v>
+        <v>6811598</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22060,7 +22060,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130250305</v>
+        <v>130250310</v>
       </c>
       <c r="B215" t="n">
         <v>57851</v>
@@ -22103,10 +22103,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>445448</v>
+        <v>445339</v>
       </c>
       <c r="R215" t="n">
-        <v>6811432</v>
+        <v>6811359</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22165,7 +22165,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130250283</v>
+        <v>130250305</v>
       </c>
       <c r="B216" t="n">
         <v>57851</v>
@@ -22208,10 +22208,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>445303</v>
+        <v>445448</v>
       </c>
       <c r="R216" t="n">
-        <v>6811621</v>
+        <v>6811432</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23070,10 +23070,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130250334</v>
+        <v>130250285</v>
       </c>
       <c r="B225" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23081,34 +23081,42 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>445266</v>
+        <v>445439</v>
       </c>
       <c r="R225" t="n">
-        <v>6811642</v>
+        <v>6811539</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23167,7 +23175,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130250400</v>
+        <v>130250358</v>
       </c>
       <c r="B226" t="n">
         <v>79211</v>
@@ -23202,10 +23210,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>445401</v>
+        <v>445154</v>
       </c>
       <c r="R226" t="n">
-        <v>6811451</v>
+        <v>6811359</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23264,7 +23272,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130250358</v>
+        <v>130250382</v>
       </c>
       <c r="B227" t="n">
         <v>79211</v>
@@ -23299,10 +23307,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>445154</v>
+        <v>445218</v>
       </c>
       <c r="R227" t="n">
-        <v>6811359</v>
+        <v>6811435</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23361,10 +23369,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130250263</v>
+        <v>130250334</v>
       </c>
       <c r="B228" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23372,21 +23380,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23396,10 +23404,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>445321</v>
+        <v>445266</v>
       </c>
       <c r="R228" t="n">
-        <v>6811263</v>
+        <v>6811642</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23458,7 +23466,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130250382</v>
+        <v>130250400</v>
       </c>
       <c r="B229" t="n">
         <v>79211</v>
@@ -23493,10 +23501,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>445218</v>
+        <v>445401</v>
       </c>
       <c r="R229" t="n">
-        <v>6811435</v>
+        <v>6811451</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23555,10 +23563,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130250372</v>
+        <v>130250263</v>
       </c>
       <c r="B230" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23566,37 +23574,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>445578</v>
+        <v>445321</v>
       </c>
       <c r="R230" t="n">
-        <v>6811455</v>
+        <v>6811263</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -23637,7 +23642,6 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
@@ -23656,10 +23660,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>130250285</v>
+        <v>130250372</v>
       </c>
       <c r="B231" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -23667,31 +23671,26 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
@@ -23699,10 +23698,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>445439</v>
+        <v>445578</v>
       </c>
       <c r="R231" t="n">
-        <v>6811539</v>
+        <v>6811455</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -23743,6 +23742,7 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -23761,10 +23761,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130250301</v>
+        <v>130250393</v>
       </c>
       <c r="B232" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -23772,42 +23772,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>445222</v>
+        <v>445477</v>
       </c>
       <c r="R232" t="n">
-        <v>6811352</v>
+        <v>6811356</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -23866,10 +23858,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130250288</v>
+        <v>130250408</v>
       </c>
       <c r="B233" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -23877,42 +23869,34 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>445564</v>
+        <v>445323</v>
       </c>
       <c r="R233" t="n">
-        <v>6811446</v>
+        <v>6811251</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -23971,10 +23955,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130250316</v>
+        <v>130250246</v>
       </c>
       <c r="B234" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -23982,42 +23966,34 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>445524</v>
+        <v>445182</v>
       </c>
       <c r="R234" t="n">
-        <v>6811486</v>
+        <v>6811329</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24076,7 +24052,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130250393</v>
+        <v>130250405</v>
       </c>
       <c r="B235" t="n">
         <v>79211</v>
@@ -24111,10 +24087,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>445477</v>
+        <v>445324</v>
       </c>
       <c r="R235" t="n">
-        <v>6811356</v>
+        <v>6811291</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24173,7 +24149,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130250380</v>
+        <v>130250397</v>
       </c>
       <c r="B236" t="n">
         <v>79211</v>
@@ -24208,10 +24184,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>445369</v>
+        <v>445441</v>
       </c>
       <c r="R236" t="n">
-        <v>6811486</v>
+        <v>6811411</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24270,10 +24246,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130250408</v>
+        <v>130250288</v>
       </c>
       <c r="B237" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -24281,34 +24257,42 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>445323</v>
+        <v>445564</v>
       </c>
       <c r="R237" t="n">
-        <v>6811251</v>
+        <v>6811446</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24367,10 +24351,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130250246</v>
+        <v>130250301</v>
       </c>
       <c r="B238" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24378,34 +24362,42 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>445182</v>
+        <v>445222</v>
       </c>
       <c r="R238" t="n">
-        <v>6811329</v>
+        <v>6811352</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24464,10 +24456,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130250405</v>
+        <v>130250316</v>
       </c>
       <c r="B239" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24475,34 +24467,42 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>445324</v>
+        <v>445524</v>
       </c>
       <c r="R239" t="n">
-        <v>6811291</v>
+        <v>6811486</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24561,7 +24561,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130250397</v>
+        <v>130250380</v>
       </c>
       <c r="B240" t="n">
         <v>79211</v>
@@ -24596,10 +24596,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>445441</v>
+        <v>445369</v>
       </c>
       <c r="R240" t="n">
-        <v>6811411</v>
+        <v>6811486</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24755,10 +24755,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130250337</v>
+        <v>130250295</v>
       </c>
       <c r="B242" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -24766,34 +24766,42 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>445441</v>
+        <v>445263</v>
       </c>
       <c r="R242" t="n">
-        <v>6811531</v>
+        <v>6811480</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25240,7 +25248,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130250403</v>
+        <v>130250359</v>
       </c>
       <c r="B247" t="n">
         <v>79211</v>
@@ -25275,10 +25283,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>445337</v>
+        <v>445161</v>
       </c>
       <c r="R247" t="n">
-        <v>6811372</v>
+        <v>6811404</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25337,10 +25345,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130250359</v>
+        <v>130250337</v>
       </c>
       <c r="B248" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -25348,21 +25356,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25372,10 +25380,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>445161</v>
+        <v>445441</v>
       </c>
       <c r="R248" t="n">
-        <v>6811404</v>
+        <v>6811531</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25434,10 +25442,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>130250295</v>
+        <v>130250403</v>
       </c>
       <c r="B249" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -25445,42 +25453,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
           <t>Gumpersbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>445263</v>
+        <v>445337</v>
       </c>
       <c r="R249" t="n">
-        <v>6811480</v>
+        <v>6811372</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -25542,7 +25542,7 @@
         <v>130250353</v>
       </c>
       <c r="B250" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>

--- a/artfynd/A 56939-2025 artfynd.xlsx
+++ b/artfynd/A 56939-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY250"/>
+  <dimension ref="A1:AZ250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250267</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237758</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237759</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237760</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237761</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237762</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237763</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237764</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237765</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237766</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237767</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237768</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237769</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237770</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237771</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237772</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237773</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237774</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237775</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2737,6 +2842,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237776</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237777</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2931,6 +3046,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237778</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3028,6 +3148,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237779</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3125,6 +3250,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237780</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3222,6 +3352,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250356</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3319,6 +3454,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250357</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250358</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3513,6 +3658,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250359</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3610,6 +3760,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250360</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3707,6 +3862,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250361</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3804,6 +3964,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250362</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3901,6 +4066,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250363</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3998,6 +4168,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250364</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4095,6 +4270,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250366</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4192,6 +4372,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250367</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4289,6 +4474,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250368</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4386,6 +4576,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250369</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4483,6 +4678,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250370</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4580,6 +4780,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250371</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4681,6 +4886,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250372</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4778,6 +4988,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250373</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4875,6 +5090,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250374</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4972,6 +5192,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250375</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5073,6 +5298,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250376</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5170,6 +5400,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250377</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5267,6 +5502,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250378</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5364,6 +5604,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250379</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5461,6 +5706,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250380</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5558,6 +5808,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250381</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5655,6 +5910,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250382</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5752,6 +6012,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250383</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5849,6 +6114,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250384</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5946,6 +6216,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250385</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6043,6 +6318,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250386</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6140,6 +6420,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250387</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6237,6 +6522,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250388</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6334,6 +6624,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250389</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6431,6 +6726,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250390</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6528,6 +6828,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250391</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6625,6 +6930,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250392</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6722,6 +7032,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250393</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6823,6 +7138,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250394</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6920,6 +7240,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250395</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7017,6 +7342,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250396</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7114,6 +7444,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250397</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7211,6 +7546,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250398</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7308,6 +7648,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250399</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7405,6 +7750,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250400</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7502,6 +7852,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250401</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7599,6 +7954,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250402</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7696,6 +8056,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250403</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7793,6 +8158,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250404</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7890,6 +8260,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250405</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7987,6 +8362,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250406</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8084,6 +8464,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250407</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8181,6 +8566,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250408</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8278,6 +8668,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250409</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8375,6 +8770,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237743</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8472,6 +8872,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237744</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8569,6 +8974,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237745</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8666,6 +9076,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237746</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8763,6 +9178,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237747</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8860,6 +9280,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237748</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8957,6 +9382,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237749</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9054,6 +9484,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250333</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9151,6 +9586,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250334</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9248,6 +9688,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250335</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9345,6 +9790,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250336</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9442,6 +9892,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250337</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9539,6 +9994,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250338</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9636,6 +10096,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250339</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9733,6 +10198,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250340</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9830,6 +10300,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250341</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9927,6 +10402,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250342</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10024,6 +10504,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250343</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10121,6 +10606,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250344</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10218,6 +10708,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250345</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10315,6 +10810,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250346</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10412,6 +10912,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250347</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10509,6 +11014,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250348</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10606,6 +11116,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237658</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10703,6 +11218,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237659</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10800,6 +11320,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237660</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10897,6 +11422,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237661</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10994,6 +11524,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237662</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11091,6 +11626,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237663</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11188,6 +11728,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237664</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11285,6 +11830,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237665</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11382,6 +11932,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237666</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11479,6 +12034,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237667</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11576,6 +12136,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237668</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11673,6 +12238,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237669</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11770,6 +12340,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237670</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11867,6 +12442,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237671</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11964,6 +12544,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250246</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12061,6 +12646,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250247</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12158,6 +12748,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250248</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12255,6 +12850,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250249</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12352,6 +12952,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250250</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12449,6 +13054,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250251</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12546,6 +13156,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250252</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12643,6 +13258,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250253</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12740,6 +13360,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250254</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12837,6 +13462,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250255</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12934,6 +13564,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250256</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13031,6 +13666,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250257</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13128,6 +13768,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250258</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13225,6 +13870,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250259</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13322,6 +13972,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250260</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13419,6 +14074,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250261</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13516,6 +14176,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250262</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13613,6 +14278,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250263</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13710,6 +14380,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250264</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13815,6 +14490,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237690</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13920,6 +14600,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237691</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14025,6 +14710,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237692</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14130,6 +14820,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237693</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14235,6 +14930,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237694</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14340,6 +15040,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237695</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14445,6 +15150,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237696</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14550,6 +15260,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237697</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14655,6 +15370,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237698</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14760,6 +15480,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237699</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14865,6 +15590,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237700</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14970,6 +15700,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237701</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15075,6 +15810,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237702</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15180,6 +15920,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237703</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15285,6 +16030,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237704</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15390,6 +16140,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237705</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15495,6 +16250,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237706</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15600,6 +16360,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237707</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15705,6 +16470,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237708</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15810,6 +16580,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237709</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15915,6 +16690,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237710</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16020,6 +16800,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237711</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16125,6 +16910,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237712</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16230,6 +17020,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237713</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16335,6 +17130,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237714</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16440,6 +17240,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237715</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16545,6 +17350,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237716</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16650,6 +17460,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237717</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16755,6 +17570,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237718</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16860,6 +17680,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237719</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16965,6 +17790,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237720</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17070,6 +17900,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237721</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17175,6 +18010,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237722</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17280,6 +18120,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237723</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17385,6 +18230,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237724</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17490,6 +18340,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237725</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17595,6 +18450,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250279</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17700,6 +18560,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250280</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17805,6 +18670,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250281</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17910,6 +18780,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250282</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18015,6 +18890,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250283</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18120,6 +19000,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250284</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18225,6 +19110,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250285</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18330,6 +19220,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250286</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18435,6 +19330,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250287</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18540,6 +19440,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250288</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18645,6 +19550,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250289</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18750,6 +19660,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250290</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18855,6 +19770,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250291</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18960,6 +19880,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250292</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19065,6 +19990,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250293</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19170,6 +20100,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250294</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19275,6 +20210,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250295</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19380,6 +20320,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250296</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19485,6 +20430,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250297</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19590,6 +20540,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250298</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19695,6 +20650,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250299</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19800,6 +20760,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250300</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19905,6 +20870,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250301</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20010,6 +20980,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250302</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20115,6 +21090,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250303</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20220,6 +21200,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250304</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20325,6 +21310,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250305</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20430,6 +21420,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250306</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20535,6 +21530,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250307</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20640,6 +21640,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250308</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20745,6 +21750,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250309</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20850,6 +21860,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250310</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20955,6 +21970,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250311</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21060,6 +22080,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250312</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21165,6 +22190,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250313</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21270,6 +22300,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250314</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21375,6 +22410,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250315</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21480,6 +22520,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250316</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21585,6 +22630,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250317</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21690,6 +22740,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250268</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21795,6 +22850,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250353</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21900,6 +22960,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250355</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22005,6 +23070,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237675</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22110,6 +23180,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237676</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22215,6 +23290,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237677</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22320,6 +23400,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237679</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22425,6 +23510,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250269</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22530,6 +23620,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250270</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22635,6 +23730,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250271</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22740,6 +23840,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250272</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22845,6 +23950,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250273</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22950,6 +24060,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250274</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23055,6 +24170,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250275</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23160,6 +24280,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250276</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23265,6 +24390,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250277</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23372,6 +24502,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250330</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23479,6 +24614,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237782</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23586,6 +24726,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237750</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23688,6 +24833,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250319</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23790,6 +24940,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237726</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23887,6 +25042,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237727</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23984,6 +25144,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250318</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24081,6 +25246,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237733</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24182,6 +25352,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237734</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24279,6 +25454,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237735</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24376,6 +25556,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237736</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24473,6 +25658,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237737</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24570,6 +25760,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237738</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24671,6 +25866,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130237739</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24768,6 +25968,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250321</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24865,6 +26070,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250323</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24962,6 +26172,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250324</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25059,6 +26274,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250325</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25156,6 +26376,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250326</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25253,6 +26478,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250327</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25350,6 +26580,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250328</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25447,6 +26682,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250329</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25544,6 +26784,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250265</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25641,8 +26886,264 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130250266</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>